--- a/RNR_수입원가_2026_20260424.xlsx
+++ b/RNR_수입원가_2026_20260424.xlsx
@@ -3489,24 +3489,20 @@
       <c r="H19" s="7" t="n">
         <v>11000</v>
       </c>
-      <c r="I19" s="119">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I19" s="119" t="n">
+        <v>1482.8</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>16310800</v>
       </c>
-      <c r="K19" s="9">
-        <f>IFERROR(ROUND(H19*I19,0),0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="9">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="9">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+      <c r="K19" s="9" t="n">
+        <v>16310800</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>462</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>296</v>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
@@ -3560,16 +3556,14 @@
         <f>S19+T19+W19</f>
         <v/>
       </c>
-      <c r="AA19" s="10">
-        <f>K19+L19+M19+IFERROR(VLOOKUP(B19,RemitTable2,9,FALSE()),0)+Y19+Z19</f>
-        <v/>
+      <c r="AA19" s="10" t="n">
+        <v>20915590</v>
       </c>
       <c r="AB19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="AC19" s="10">
-        <f>ROUND(AA19/AB19,0)</f>
-        <v/>
+      <c r="AC19" s="10" t="n">
+        <v>10457795</v>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
@@ -3620,24 +3614,20 @@
       <c r="H20" s="7" t="n">
         <v>286580</v>
       </c>
-      <c r="I20" s="119">
-        <f>IFERROR(VLOOKUP(B20,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I20" s="119" t="n">
+        <v>1482.8</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>424990980</v>
       </c>
-      <c r="K20" s="9">
-        <f>IFERROR(ROUND(H20*I20,0),0)</f>
-        <v/>
-      </c>
-      <c r="L20" s="9">
-        <f>IFERROR(VLOOKUP(B20,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="9">
-        <f>IFERROR(VLOOKUP(B20,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+      <c r="K20" s="9" t="n">
+        <v>424990980</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>12038</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>7704</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
@@ -3691,16 +3681,14 @@
         <f>S20+T20+W20</f>
         <v/>
       </c>
-      <c r="AA20" s="10">
-        <f>K20+L20+M20+IFERROR(VLOOKUP(B20,RemitTable2,9,FALSE()),0)+Y20+Z20</f>
-        <v/>
+      <c r="AA20" s="10" t="n">
+        <v>473718807</v>
       </c>
       <c r="AB20" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="AC20" s="10">
-        <f>ROUND(AA20/AB20,0)</f>
-        <v/>
+      <c r="AC20" s="10" t="n">
+        <v>16918529</v>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
@@ -5031,24 +5019,20 @@
       <c r="H31" s="125" t="n">
         <v>4388.4</v>
       </c>
-      <c r="I31" s="126">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I31" s="126" t="n">
+        <v>1741.08</v>
       </c>
       <c r="J31" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="127">
-        <f>IFERROR(ROUND(H31*I31,0),0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="127">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M31" s="127">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>7702082</v>
+      </c>
+      <c r="K31" s="127" t="n">
+        <v>7702082</v>
+      </c>
+      <c r="L31" s="127" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M31" s="127" t="n">
+        <v>8000</v>
       </c>
       <c r="N31" s="123" t="inlineStr">
         <is>
@@ -5100,16 +5084,14 @@
         <f>S31+T31+W31</f>
         <v/>
       </c>
-      <c r="AA31" s="128">
-        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
-        <v/>
+      <c r="AA31" s="128" t="n">
+        <v>7763609</v>
       </c>
       <c r="AB31" s="129" t="n">
         <v>60</v>
       </c>
-      <c r="AC31" s="128">
-        <f>ROUND(AA31/AB31,0)</f>
-        <v/>
+      <c r="AC31" s="128" t="n">
+        <v>129393</v>
       </c>
       <c r="AD31" s="123" t="inlineStr">
         <is>
@@ -10535,7 +10517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="107" min="1" max="1"/>
@@ -13770,19 +13752,9 @@
         <v>7763609</v>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="M76" s="56" t="n"/>
     </row>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A33:L33"/>

--- a/RNR_수입원가_2026_20260424.xlsx
+++ b/RNR_수입원가_2026_20260424.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="168" formatCode="0&quot;일&quot;"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="170" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="171" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -406,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -927,6 +928,39 @@
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8435,7 +8469,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="21" t="n">
         <v>1</v>
       </c>
@@ -8462,25 +8496,17 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="I3" s="21" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
+      <c r="G3" s="190" t="n">
+        <v>45925</v>
+      </c>
+      <c r="H3" s="190" t="n">
+        <v>46080</v>
+      </c>
+      <c r="I3" s="190" t="n">
+        <v>45913</v>
+      </c>
+      <c r="J3" s="190" t="n">
+        <v>46262</v>
       </c>
       <c r="K3" s="21" t="inlineStr">
         <is>
@@ -8488,7 +8514,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="21" t="n">
         <v>2</v>
       </c>
@@ -8515,25 +8541,17 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="I4" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
+      <c r="G4" s="190" t="n">
+        <v>45982</v>
+      </c>
+      <c r="H4" s="190" t="n">
+        <v>46014</v>
+      </c>
+      <c r="I4" s="190" t="n">
+        <v>45992</v>
+      </c>
+      <c r="J4" s="190" t="n">
+        <v>46356</v>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
@@ -8541,7 +8559,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="21" t="n">
         <v>3</v>
       </c>
@@ -8568,25 +8586,17 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
+      <c r="G5" s="190" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H5" s="190" t="n">
+        <v>46064</v>
+      </c>
+      <c r="I5" s="190" t="n">
+        <v>46013</v>
+      </c>
+      <c r="J5" s="190" t="n">
+        <v>46377</v>
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
@@ -8594,7 +8604,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="21" t="n">
         <v>4</v>
       </c>
@@ -8621,25 +8631,17 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G6" s="190" t="n">
+        <v>46007</v>
+      </c>
+      <c r="H6" s="190" t="n">
+        <v>46043</v>
+      </c>
+      <c r="I6" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J6" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K6" s="21" t="inlineStr">
         <is>
@@ -8647,7 +8649,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="21" t="n">
         <v>5</v>
       </c>
@@ -8674,25 +8676,17 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
+      <c r="G7" s="190" t="n">
+        <v>46007</v>
+      </c>
+      <c r="H7" s="190" t="n">
+        <v>46043</v>
+      </c>
+      <c r="I7" s="190" t="n">
+        <v>45962</v>
+      </c>
+      <c r="J7" s="190" t="n">
+        <v>46325</v>
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
@@ -8700,7 +8694,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="21" t="n">
         <v>6</v>
       </c>
@@ -8727,25 +8721,17 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G8" s="190" t="n">
+        <v>46010</v>
+      </c>
+      <c r="H8" s="190" t="n">
+        <v>46080</v>
+      </c>
+      <c r="I8" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J8" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K8" s="21" t="inlineStr">
         <is>
@@ -8753,7 +8739,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="21" t="n">
         <v>7</v>
       </c>
@@ -8780,25 +8766,19 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
+      <c r="G9" s="190" t="n">
+        <v>46015</v>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="I9" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J9" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
@@ -8806,7 +8786,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="21" t="n">
         <v>8</v>
       </c>
@@ -8833,25 +8813,17 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t>2027-01-29</t>
-        </is>
+      <c r="G10" s="190" t="n">
+        <v>46029</v>
+      </c>
+      <c r="H10" s="190" t="n">
+        <v>46072</v>
+      </c>
+      <c r="I10" s="190" t="n">
+        <v>46052</v>
+      </c>
+      <c r="J10" s="190" t="n">
+        <v>46416</v>
       </c>
       <c r="K10" s="21" t="inlineStr">
         <is>
@@ -8859,7 +8831,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="21" t="n">
         <v>9</v>
       </c>
@@ -8886,10 +8858,8 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
+      <c r="G11" s="190" t="n">
+        <v>46029</v>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
@@ -8912,7 +8882,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="21" t="n">
         <v>10</v>
       </c>
@@ -8939,25 +8909,17 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G12" s="190" t="n">
+        <v>46042</v>
+      </c>
+      <c r="H12" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="I12" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J12" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K12" s="21" t="inlineStr">
         <is>
@@ -8965,7 +8927,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="21" t="n">
         <v>11</v>
       </c>
@@ -8992,25 +8954,17 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G13" s="190" t="n">
+        <v>46042</v>
+      </c>
+      <c r="H13" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="I13" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J13" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K13" s="21" t="inlineStr">
         <is>
@@ -9018,7 +8972,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="21" t="n">
         <v>12</v>
       </c>
@@ -9045,25 +8999,17 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G14" s="190" t="n">
+        <v>46042</v>
+      </c>
+      <c r="H14" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="I14" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J14" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>
@@ -9071,7 +9017,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" s="21" t="n">
         <v>13</v>
       </c>
@@ -9098,25 +9044,17 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J15" s="95" t="inlineStr">
-        <is>
-          <t>2027-02-28</t>
-        </is>
+      <c r="G15" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="H15" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I15" s="190" t="n">
+        <v>46082</v>
+      </c>
+      <c r="J15" s="191" t="n">
+        <v>46446</v>
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
@@ -9124,7 +9062,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="16" customHeight="1">
       <c r="A16" s="21" t="n">
         <v>14</v>
       </c>
@@ -9151,25 +9089,17 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J16" s="95" t="inlineStr">
-        <is>
-          <t>2027-02-22</t>
-        </is>
+      <c r="G16" s="190" t="n">
+        <v>46060</v>
+      </c>
+      <c r="H16" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I16" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J16" s="191" t="n">
+        <v>46440</v>
       </c>
       <c r="K16" s="21" t="inlineStr">
         <is>
@@ -9177,7 +9107,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" s="21" t="n">
         <v>15</v>
       </c>
@@ -9204,25 +9134,17 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J17" s="95" t="inlineStr">
-        <is>
-          <t>2027-02-28</t>
-        </is>
+      <c r="G17" s="190" t="n">
+        <v>46080</v>
+      </c>
+      <c r="H17" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I17" s="190" t="n">
+        <v>46082</v>
+      </c>
+      <c r="J17" s="191" t="n">
+        <v>46446</v>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
@@ -9230,60 +9152,56 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="39" t="n">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="95" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="95" t="inlineStr">
         <is>
           <t>GPO471</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="181" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="D18" s="181" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="E18" s="94" t="n">
+      <c r="E18" s="182" t="n">
         <v>500</v>
       </c>
-      <c r="F18" s="39" t="inlineStr">
+      <c r="F18" s="95" t="inlineStr">
         <is>
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="G18" s="39" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="H18" s="39" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
+      <c r="G18" s="191" t="n">
+        <v>46088</v>
+      </c>
+      <c r="H18" s="191" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I18" s="95" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
-      <c r="J18" s="96" t="inlineStr">
+      <c r="J18" s="95" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
-      <c r="K18" s="21" t="inlineStr">
+      <c r="K18" s="95" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="21" t="n">
         <v>17</v>
       </c>
@@ -9310,25 +9228,19 @@
           <t>EW (CGV 동백 외 Warranty Extension)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
+      <c r="G19" s="190" t="n">
+        <v>46109</v>
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="J19" s="95" t="inlineStr">
-        <is>
-          <t>2027-03-31</t>
-        </is>
+      <c r="I19" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="J19" s="191" t="n">
+        <v>46477</v>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
@@ -9336,95 +9248,95 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="150" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="150" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="183" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="183" t="inlineStr">
         <is>
           <t>CPO697</t>
         </is>
       </c>
-      <c r="C20" s="151" t="inlineStr">
+      <c r="C20" s="184" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D20" s="151" t="inlineStr">
+      <c r="D20" s="184" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="E20" s="152" t="n">
+      <c r="E20" s="185" t="n">
         <v>15289</v>
       </c>
-      <c r="F20" s="150" t="inlineStr">
+      <c r="F20" s="183" t="inlineStr">
         <is>
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대</t>
         </is>
       </c>
-      <c r="G20" s="153" t="n">
+      <c r="G20" s="186" t="n">
         <v>46136</v>
       </c>
-      <c r="H20" s="150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="153" t="n">
+      <c r="H20" s="186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="186" t="n">
         <v>46168</v>
       </c>
-      <c r="J20" s="153" t="n">
+      <c r="J20" s="186" t="n">
         <v>46532</v>
       </c>
-      <c r="K20" s="150" t="inlineStr">
+      <c r="K20" s="183" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="150" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="150" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="183" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="183" t="inlineStr">
         <is>
           <t>CPO693-2</t>
         </is>
       </c>
-      <c r="C21" s="151" t="inlineStr">
+      <c r="C21" s="184" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D21" s="151" t="inlineStr">
+      <c r="D21" s="184" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="E21" s="152" t="n">
+      <c r="E21" s="185" t="n">
         <v>2550</v>
       </c>
-      <c r="F21" s="150" t="inlineStr">
+      <c r="F21" s="183" t="inlineStr">
         <is>
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="G21" s="153" t="n">
+      <c r="G21" s="186" t="n">
         <v>46133</v>
       </c>
-      <c r="H21" s="150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="153" t="n">
+      <c r="H21" s="186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="186" t="n">
         <v>46142</v>
       </c>
-      <c r="J21" s="153" t="n">
+      <c r="J21" s="186" t="n">
         <v>46872</v>
       </c>
-      <c r="K21" s="150" t="inlineStr">
+      <c r="K21" s="183" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
@@ -10614,185 +10526,185 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="39" t="n">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>2025.12.01</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D3" s="39" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>CPO668-3, CPO673</t>
         </is>
       </c>
-      <c r="E3" s="40" t="n">
+      <c r="E3" s="44" t="n">
         <v>35563</v>
       </c>
-      <c r="F3" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="39" t="n">
+      <c r="F3" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H3" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="42">
+      <c r="H3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
         <f>ROUND((E3+G3)*F3+H3+I3,0)</f>
         <v/>
       </c>
-      <c r="L3" s="43">
+      <c r="L3" s="46">
         <f>J3-K3</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="39" t="n">
+      <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>2025.12.02</t>
         </is>
       </c>
-      <c r="C4" s="92" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>GPO-445, 446-1, 447, 448</t>
         </is>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="44" t="n">
         <v>55830</v>
       </c>
-      <c r="F4" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="39" t="n">
+      <c r="F4" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="42">
+      <c r="H4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
         <f>ROUND((E4+G4)*F4+H4+I4,0)</f>
         <v/>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="46">
         <f>J4-K4</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="39" t="n">
+      <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>2025.12.02</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Thali Consulting</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>(PO미기재)</t>
         </is>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="44" t="n">
         <v>9247.690000000001</v>
       </c>
-      <c r="F5" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="39" t="n">
+      <c r="F5" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H5" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="42">
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
         <f>ROUND((E5+G5)*F5+H5+I5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="46">
         <f>J5-K5</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="39" t="n">
+      <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2025.12.02</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CPO-669</t>
         </is>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="44" t="n">
         <v>7410</v>
       </c>
-      <c r="F6" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="39" t="n">
+      <c r="F6" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="42">
+      <c r="H6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
         <f>ROUND((E6+G6)*F6+H6+I6,0)</f>
         <v/>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="46">
         <f>J6-K6</f>
         <v/>
       </c>
@@ -10982,47 +10894,47 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>2025.12.19</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>GDC(라이센스)</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>/ROC/라이센스</t>
         </is>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="44" t="n">
         <v>1200</v>
       </c>
-      <c r="F11" s="163" t="n">
+      <c r="F11" s="162" t="n">
         <v>1464.9</v>
       </c>
-      <c r="G11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="19">
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
         <f>ROUND((E11+G11)*F11+H11+I11,0)</f>
         <v/>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="46">
         <f>J11-K11</f>
         <v/>
       </c>
@@ -11718,277 +11630,277 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="n">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026.04.14</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>GPO468-1, 472, 468-2</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="n">
+        <v>57650</v>
+      </c>
+      <c r="F27" s="162" t="n">
+        <v>1481.9</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>85481673</v>
+      </c>
+      <c r="K27" s="9">
+        <f>ROUND((E27+G27)*F27+H27+I27,0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="46">
+        <f>J27-K27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="171" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>2026.04.14</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>GPO468-1, 472, 468-2</t>
-        </is>
-      </c>
-      <c r="E27" s="47" t="n">
-        <v>57650</v>
-      </c>
-      <c r="F27" s="163" t="n">
-        <v>1481.9</v>
-      </c>
-      <c r="G27" s="13" t="n">
+      <c r="B28" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C28" s="172" t="inlineStr">
+        <is>
+          <t>Swank</t>
+        </is>
+      </c>
+      <c r="D28" s="171" t="inlineStr">
+        <is>
+          <t>(영화 라이센스)</t>
+        </is>
+      </c>
+      <c r="E28" s="173" t="n">
+        <v>814</v>
+      </c>
+      <c r="F28" s="187" t="n">
+        <v>1505</v>
+      </c>
+      <c r="G28" s="171" t="n">
         <v>20</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H28" s="176" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I28" s="176" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J28" s="176" t="n">
+        <v>1268170</v>
+      </c>
+      <c r="K28" s="176">
+        <f>ROUND((E28+G28)*F28+H28+I28,0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="177">
+        <f>J28-K28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="27.75" customHeight="1">
+      <c r="A29" s="171" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.02</t>
+        </is>
+      </c>
+      <c r="C29" s="172" t="inlineStr">
+        <is>
+          <t>Monoplex</t>
+        </is>
+      </c>
+      <c r="D29" s="171" t="inlineStr">
+        <is>
+          <t>(영업)</t>
+        </is>
+      </c>
+      <c r="E29" s="173" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F29" s="187" t="n">
+        <v>1520.1</v>
+      </c>
+      <c r="G29" s="171" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" s="176" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I29" s="176" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J29" s="176" t="n">
+        <v>45666402</v>
+      </c>
+      <c r="K29" s="176">
+        <f>ROUND((E29+G29)*F29+H29+I29,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="177">
+        <f>J29-K29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="171" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.21</t>
+        </is>
+      </c>
+      <c r="C30" s="172" t="inlineStr">
+        <is>
+          <t>Ferco</t>
+        </is>
+      </c>
+      <c r="D30" s="171" t="inlineStr">
+        <is>
+          <t>MONOPLEX20260126-01</t>
+        </is>
+      </c>
+      <c r="E30" s="173" t="n">
+        <v>25976</v>
+      </c>
+      <c r="F30" s="187" t="n">
+        <v>1473.3</v>
+      </c>
+      <c r="G30" s="171" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" s="176" t="n">
         <v>12500</v>
       </c>
-      <c r="I27" s="19" t="n">
+      <c r="I30" s="176" t="n">
         <v>8000</v>
       </c>
-      <c r="J27" s="19" t="n">
-        <v>85481673</v>
-      </c>
-      <c r="K27" s="19">
-        <f>ROUND((E27+G27)*F27+H27+I27,0)</f>
-        <v/>
-      </c>
-      <c r="L27" s="49">
-        <f>J27-K27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="164" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C28" s="165" t="inlineStr">
-        <is>
-          <t>Swank</t>
-        </is>
-      </c>
-      <c r="D28" s="164" t="inlineStr">
-        <is>
-          <t>(영화 라이센스)</t>
-        </is>
-      </c>
-      <c r="E28" s="166" t="n">
-        <v>814</v>
-      </c>
-      <c r="F28" s="167" t="n">
-        <v>1505</v>
-      </c>
-      <c r="G28" s="164" t="n">
+      <c r="J30" s="176" t="n">
+        <v>38320406</v>
+      </c>
+      <c r="K30" s="176">
+        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="177">
+        <f>J30-K30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="171" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C31" s="172" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D31" s="171" t="inlineStr">
+        <is>
+          <t>CPO692(692-1, 692-2)</t>
+        </is>
+      </c>
+      <c r="E31" s="173" t="n">
+        <v>297580</v>
+      </c>
+      <c r="F31" s="187" t="n">
+        <v>1482.8</v>
+      </c>
+      <c r="G31" s="171" t="n">
         <v>20</v>
       </c>
-      <c r="H28" s="168" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I28" s="168" t="n">
+      <c r="H31" s="176" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I31" s="176" t="n">
         <v>8000</v>
       </c>
-      <c r="J28" s="168" t="n">
-        <v>1268170</v>
-      </c>
-      <c r="K28" s="168">
-        <f>ROUND((E28+G28)*F28+H28+I28,0)</f>
-        <v/>
-      </c>
-      <c r="L28" s="169">
-        <f>J28-K28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="27.75" customHeight="1">
-      <c r="A29" s="164" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.02</t>
-        </is>
-      </c>
-      <c r="C29" s="165" t="inlineStr">
-        <is>
-          <t>Monoplex</t>
-        </is>
-      </c>
-      <c r="D29" s="164" t="inlineStr">
-        <is>
-          <t>(영업)</t>
-        </is>
-      </c>
-      <c r="E29" s="166" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F29" s="167" t="n">
-        <v>1520.1</v>
-      </c>
-      <c r="G29" s="164" t="n">
-        <v>20</v>
-      </c>
-      <c r="H29" s="168" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I29" s="168" t="n">
+      <c r="J31" s="176" t="n">
+        <v>441301780</v>
+      </c>
+      <c r="K31" s="176">
+        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="177">
+        <f>J31-K31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="171" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C32" s="172" t="inlineStr">
+        <is>
+          <t>Elicent (EUR)</t>
+        </is>
+      </c>
+      <c r="D32" s="171" t="inlineStr">
+        <is>
+          <t>EPO18</t>
+        </is>
+      </c>
+      <c r="E32" s="173" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="F32" s="187" t="n">
+        <v>1741.08</v>
+      </c>
+      <c r="G32" s="171" t="n">
+        <v>25</v>
+      </c>
+      <c r="H32" s="176" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I32" s="176" t="n">
         <v>8000</v>
       </c>
-      <c r="J29" s="168" t="n">
-        <v>45666402</v>
-      </c>
-      <c r="K29" s="168">
-        <f>ROUND((E29+G29)*F29+H29+I29,0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="169">
-        <f>J29-K29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="164" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.21</t>
-        </is>
-      </c>
-      <c r="C30" s="165" t="inlineStr">
-        <is>
-          <t>Ferco</t>
-        </is>
-      </c>
-      <c r="D30" s="164" t="inlineStr">
-        <is>
-          <t>MONOPLEX20260126-01</t>
-        </is>
-      </c>
-      <c r="E30" s="166" t="n">
-        <v>25976</v>
-      </c>
-      <c r="F30" s="167" t="n">
-        <v>1473.3</v>
-      </c>
-      <c r="G30" s="164" t="n">
-        <v>20</v>
-      </c>
-      <c r="H30" s="168" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I30" s="168" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J30" s="168" t="n">
-        <v>38320406</v>
-      </c>
-      <c r="K30" s="168">
-        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="169">
-        <f>J30-K30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="164" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C31" s="165" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D31" s="164" t="inlineStr">
-        <is>
-          <t>CPO692(692-1, 692-2)</t>
-        </is>
-      </c>
-      <c r="E31" s="166" t="n">
-        <v>297580</v>
-      </c>
-      <c r="F31" s="167" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="G31" s="164" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" s="168" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I31" s="168" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J31" s="168" t="n">
-        <v>441301780</v>
-      </c>
-      <c r="K31" s="168">
-        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="169">
-        <f>J31-K31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="164" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C32" s="165" t="inlineStr">
-        <is>
-          <t>Elicent (EUR)</t>
-        </is>
-      </c>
-      <c r="D32" s="164" t="inlineStr">
-        <is>
-          <t>EPO18</t>
-        </is>
-      </c>
-      <c r="E32" s="166" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="F32" s="167" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="G32" s="164" t="n">
-        <v>25</v>
-      </c>
-      <c r="H32" s="168" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I32" s="168" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J32" s="168" t="n">
+      <c r="J32" s="176" t="n">
         <v>7702082</v>
       </c>
-      <c r="K32" s="168">
+      <c r="K32" s="176">
         <f>ROUND((E32+G32)*F32+H32+I32,0)</f>
         <v/>
       </c>
-      <c r="L32" s="169">
+      <c r="L32" s="177">
         <f>J32-K32</f>
         <v/>
       </c>
@@ -12095,31 +12007,32 @@
       <c r="E35" s="44" t="n">
         <v>143557</v>
       </c>
-      <c r="F35" s="170">
-        <f>D30/E30</f>
-        <v/>
-      </c>
-      <c r="G35" s="119" t="n">
-        <v>1479.7</v>
+      <c r="F35" s="188">
+        <f>D35/E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="44">
+        <f>F10</f>
+        <v/>
       </c>
       <c r="H35" s="9">
-        <f>ROUND(D30*G30,0)</f>
+        <f>ROUND(D35*G35,0)</f>
         <v/>
       </c>
       <c r="I35" s="9">
-        <f>ROUND(20*G30*F30,0)</f>
+        <f>ROUND(G10*F35*G35,0)</f>
         <v/>
       </c>
       <c r="J35" s="9">
-        <f>ROUND(H10*F30,0)</f>
+        <f>ROUND(H10*F35,0)</f>
         <v/>
       </c>
       <c r="K35" s="9">
-        <f>ROUND(I10*F30,0)</f>
+        <f>ROUND(I10*F35,0)</f>
         <v/>
       </c>
       <c r="L35" s="46">
-        <f>H30+I30+J30+K30</f>
+        <f>H35+I35+J35+K35</f>
         <v/>
       </c>
     </row>
@@ -12145,31 +12058,32 @@
       <c r="E36" s="44" t="n">
         <v>143557</v>
       </c>
-      <c r="F36" s="170">
-        <f>D31/E31</f>
-        <v/>
-      </c>
-      <c r="G36" s="119" t="n">
-        <v>1479.7</v>
+      <c r="F36" s="188">
+        <f>D36/E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="44">
+        <f>F10</f>
+        <v/>
       </c>
       <c r="H36" s="9">
-        <f>ROUND(D31*G31,0)</f>
+        <f>ROUND(D36*G36,0)</f>
         <v/>
       </c>
       <c r="I36" s="9">
-        <f>ROUND(20*G31*F31,0)</f>
+        <f>ROUND(G10*F36*G36,0)</f>
         <v/>
       </c>
       <c r="J36" s="9">
-        <f>ROUND(H10*F31,0)</f>
+        <f>ROUND(H10*F36,0)</f>
         <v/>
       </c>
       <c r="K36" s="9">
-        <f>ROUND(I10*F31,0)</f>
+        <f>ROUND(I10*F36,0)</f>
         <v/>
       </c>
       <c r="L36" s="46">
-        <f>H31+I31+J31+K31</f>
+        <f>H36+I36+J36+K36</f>
         <v/>
       </c>
     </row>
@@ -12195,31 +12109,32 @@
       <c r="E37" s="44" t="n">
         <v>15040</v>
       </c>
-      <c r="F37" s="170">
-        <f>D32/E32</f>
-        <v/>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>1480</v>
+      <c r="F37" s="188">
+        <f>D37/E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="44">
+        <f>F9</f>
+        <v/>
       </c>
       <c r="H37" s="9">
-        <f>ROUND(D32*G32,0)</f>
+        <f>ROUND(D37*G37,0)</f>
         <v/>
       </c>
       <c r="I37" s="9">
-        <f>ROUND(20*G32*F32,0)</f>
+        <f>ROUND(G9*F37*G37,0)</f>
         <v/>
       </c>
       <c r="J37" s="9">
-        <f>ROUND(H9*F32,0)</f>
+        <f>ROUND(H9*F37,0)</f>
         <v/>
       </c>
       <c r="K37" s="9">
-        <f>ROUND(I9*F32,0)</f>
+        <f>ROUND(I9*F37,0)</f>
         <v/>
       </c>
       <c r="L37" s="46">
-        <f>H32+I32+J32+K32</f>
+        <f>H37+I37+J37+K37</f>
         <v/>
       </c>
     </row>
@@ -12245,31 +12160,32 @@
       <c r="E38" s="44" t="n">
         <v>13860</v>
       </c>
-      <c r="F38" s="170">
-        <f>D33/E33</f>
-        <v/>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>1439.1</v>
+      <c r="F38" s="188">
+        <f>D38/E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="44">
+        <f>F12</f>
+        <v/>
       </c>
       <c r="H38" s="9">
-        <f>ROUND(D33*G33,0)</f>
+        <f>ROUND(D38*G38,0)</f>
         <v/>
       </c>
       <c r="I38" s="9">
-        <f>ROUND(20*G33*F33,0)</f>
+        <f>ROUND(G12*F38*G38,0)</f>
         <v/>
       </c>
       <c r="J38" s="9">
-        <f>ROUND(H12*F33,0)</f>
+        <f>ROUND(H12*F38,0)</f>
         <v/>
       </c>
       <c r="K38" s="9">
-        <f>ROUND(I12*F33,0)</f>
+        <f>ROUND(I12*F38,0)</f>
         <v/>
       </c>
       <c r="L38" s="46">
-        <f>H33+I33+J33+K33</f>
+        <f>H38+I38+J38+K38</f>
         <v/>
       </c>
     </row>
@@ -12295,31 +12211,32 @@
       <c r="E39" s="44" t="n">
         <v>13860</v>
       </c>
-      <c r="F39" s="170">
-        <f>D34/E34</f>
-        <v/>
-      </c>
-      <c r="G39" s="119" t="n">
-        <v>1439.1</v>
+      <c r="F39" s="188">
+        <f>D39/E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="44">
+        <f>F12</f>
+        <v/>
       </c>
       <c r="H39" s="9">
-        <f>ROUND(D34*G34,0)</f>
+        <f>ROUND(D39*G39,0)</f>
         <v/>
       </c>
       <c r="I39" s="9">
-        <f>ROUND(20*G34*F34,0)</f>
+        <f>ROUND(G12*F39*G39,0)</f>
         <v/>
       </c>
       <c r="J39" s="9">
-        <f>ROUND(H12*F34,0)</f>
+        <f>ROUND(H12*F39,0)</f>
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>ROUND(I12*F34,0)</f>
+        <f>ROUND(I12*F39,0)</f>
         <v/>
       </c>
       <c r="L39" s="46">
-        <f>H34+I34+J34+K34</f>
+        <f>H39+I39+J39+K39</f>
         <v/>
       </c>
     </row>
@@ -12345,31 +12262,32 @@
       <c r="E40" s="44" t="n">
         <v>252</v>
       </c>
-      <c r="F40" s="170">
-        <f>D35/E35</f>
-        <v/>
-      </c>
-      <c r="G40" s="119" t="n">
-        <v>1479</v>
+      <c r="F40" s="188">
+        <f>D40/E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="44">
+        <f>F14</f>
+        <v/>
       </c>
       <c r="H40" s="9">
-        <f>ROUND(D35*G35,0)</f>
+        <f>ROUND(D40*G40,0)</f>
         <v/>
       </c>
       <c r="I40" s="9">
-        <f>ROUND(20*G35*F35,0)</f>
+        <f>ROUND(G14*F40*G40,0)</f>
         <v/>
       </c>
       <c r="J40" s="9">
-        <f>ROUND(H14*F35,0)</f>
+        <f>ROUND(H14*F40,0)</f>
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>ROUND(I14*F35,0)</f>
+        <f>ROUND(I14*F40,0)</f>
         <v/>
       </c>
       <c r="L40" s="46">
-        <f>H35+I35+J35+K35</f>
+        <f>H40+I40+J40+K40</f>
         <v/>
       </c>
     </row>
@@ -12395,31 +12313,32 @@
       <c r="E41" s="44" t="n">
         <v>3700</v>
       </c>
-      <c r="F41" s="170">
-        <f>D36/E36</f>
-        <v/>
-      </c>
-      <c r="G41" s="119" t="n">
-        <v>1475.7</v>
+      <c r="F41" s="188">
+        <f>D41/E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="44">
+        <f>F15</f>
+        <v/>
       </c>
       <c r="H41" s="9">
-        <f>ROUND(D36*G36,0)</f>
+        <f>ROUND(D41*G41,0)</f>
         <v/>
       </c>
       <c r="I41" s="9">
-        <f>ROUND(20*G36*F36,0)</f>
+        <f>ROUND(G15*F41*G41,0)</f>
         <v/>
       </c>
       <c r="J41" s="9">
-        <f>ROUND(H15*F36,0)</f>
+        <f>ROUND(H15*F41,0)</f>
         <v/>
       </c>
       <c r="K41" s="9">
-        <f>ROUND(I15*F36,0)</f>
+        <f>ROUND(I15*F41,0)</f>
         <v/>
       </c>
       <c r="L41" s="46">
-        <f>H36+I36+J36+K36</f>
+        <f>H41+I41+J41+K41</f>
         <v/>
       </c>
     </row>
@@ -12445,31 +12364,32 @@
       <c r="E42" s="44" t="n">
         <v>3700</v>
       </c>
-      <c r="F42" s="170">
-        <f>D37/E37</f>
-        <v/>
-      </c>
-      <c r="G42" s="119" t="n">
-        <v>1475.7</v>
+      <c r="F42" s="188">
+        <f>D42/E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="44">
+        <f>F15</f>
+        <v/>
       </c>
       <c r="H42" s="9">
-        <f>ROUND(D37*G37,0)</f>
+        <f>ROUND(D42*G42,0)</f>
         <v/>
       </c>
       <c r="I42" s="9">
-        <f>ROUND(20*G37*F37,0)</f>
+        <f>ROUND(G15*F42*G42,0)</f>
         <v/>
       </c>
       <c r="J42" s="9">
-        <f>ROUND(H15*F37,0)</f>
+        <f>ROUND(H15*F42,0)</f>
         <v/>
       </c>
       <c r="K42" s="9">
-        <f>ROUND(I15*F37,0)</f>
+        <f>ROUND(I15*F42,0)</f>
         <v/>
       </c>
       <c r="L42" s="46">
-        <f>H37+I37+J37+K37</f>
+        <f>H42+I42+J42+K42</f>
         <v/>
       </c>
     </row>
@@ -12495,31 +12415,32 @@
       <c r="E43" s="44" t="n">
         <v>3700</v>
       </c>
-      <c r="F43" s="170">
-        <f>D38/E38</f>
-        <v/>
-      </c>
-      <c r="G43" s="119" t="n">
-        <v>1475.7</v>
+      <c r="F43" s="188">
+        <f>D43/E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="44">
+        <f>F15</f>
+        <v/>
       </c>
       <c r="H43" s="9">
-        <f>ROUND(D38*G38,0)</f>
+        <f>ROUND(D43*G43,0)</f>
         <v/>
       </c>
       <c r="I43" s="9">
-        <f>ROUND(20*G38*F38,0)</f>
+        <f>ROUND(G15*F43*G43,0)</f>
         <v/>
       </c>
       <c r="J43" s="9">
-        <f>ROUND(H15*F38,0)</f>
+        <f>ROUND(H15*F43,0)</f>
         <v/>
       </c>
       <c r="K43" s="9">
-        <f>ROUND(I15*F38,0)</f>
+        <f>ROUND(I15*F43,0)</f>
         <v/>
       </c>
       <c r="L43" s="46">
-        <f>H38+I38+J38+K38</f>
+        <f>H43+I43+J43+K43</f>
         <v/>
       </c>
     </row>
@@ -12545,31 +12466,32 @@
       <c r="E44" s="44" t="n">
         <v>9626.35</v>
       </c>
-      <c r="F44" s="170">
-        <f>D39/E39</f>
-        <v/>
-      </c>
-      <c r="G44" s="119" t="n">
-        <v>1476</v>
+      <c r="F44" s="188">
+        <f>D44/E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="44">
+        <f>F16</f>
+        <v/>
       </c>
       <c r="H44" s="9">
-        <f>ROUND(D39*G39,0)</f>
+        <f>ROUND(D44*G44,0)</f>
         <v/>
       </c>
       <c r="I44" s="9">
-        <f>ROUND(20*G39*F39,0)</f>
+        <f>ROUND(G16*F44*G44,0)</f>
         <v/>
       </c>
       <c r="J44" s="9">
-        <f>ROUND(H16*F39,0)</f>
+        <f>ROUND(H16*F44,0)</f>
         <v/>
       </c>
       <c r="K44" s="9">
-        <f>ROUND(I16*F39,0)</f>
+        <f>ROUND(I16*F44,0)</f>
         <v/>
       </c>
       <c r="L44" s="46">
-        <f>H39+I39+J39+K39</f>
+        <f>H44+I44+J44+K44</f>
         <v/>
       </c>
     </row>
@@ -12595,31 +12517,32 @@
       <c r="E45" s="44" t="n">
         <v>5056.8</v>
       </c>
-      <c r="F45" s="170">
-        <f>D40/E40</f>
-        <v/>
-      </c>
-      <c r="G45" s="119" t="n">
-        <v>1445.5</v>
+      <c r="F45" s="188">
+        <f>D45/E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="44">
+        <f>F17</f>
+        <v/>
       </c>
       <c r="H45" s="9">
-        <f>ROUND(D40*G40,0)</f>
+        <f>ROUND(D45*G45,0)</f>
         <v/>
       </c>
       <c r="I45" s="9">
-        <f>ROUND(20*G40*F40,0)</f>
+        <f>ROUND(G17*F45*G45,0)</f>
         <v/>
       </c>
       <c r="J45" s="9">
-        <f>ROUND(H17*F40,0)</f>
+        <f>ROUND(H17*F45,0)</f>
         <v/>
       </c>
       <c r="K45" s="9">
-        <f>ROUND(I17*F40,0)</f>
+        <f>ROUND(I17*F45,0)</f>
         <v/>
       </c>
       <c r="L45" s="46">
-        <f>H40+I40+J40+K40</f>
+        <f>H45+I45+J45+K45</f>
         <v/>
       </c>
     </row>
@@ -12645,31 +12568,32 @@
       <c r="E46" s="44" t="n">
         <v>24794</v>
       </c>
-      <c r="F46" s="170">
-        <f>D41/E41</f>
-        <v/>
-      </c>
-      <c r="G46" s="119" t="n">
-        <v>1454.7</v>
+      <c r="F46" s="188">
+        <f>D46/E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="44">
+        <f>F19</f>
+        <v/>
       </c>
       <c r="H46" s="9">
-        <f>ROUND(D41*G41,0)</f>
+        <f>ROUND(D46*G46,0)</f>
         <v/>
       </c>
       <c r="I46" s="9">
-        <f>ROUND(20*G41*F41,0)</f>
+        <f>ROUND(G19*F46*G46,0)</f>
         <v/>
       </c>
       <c r="J46" s="9">
-        <f>ROUND(H19*F41,0)</f>
+        <f>ROUND(H19*F46,0)</f>
         <v/>
       </c>
       <c r="K46" s="9">
-        <f>ROUND(I19*F41,0)</f>
+        <f>ROUND(I19*F46,0)</f>
         <v/>
       </c>
       <c r="L46" s="46">
-        <f>H41+I41+J41+K41</f>
+        <f>H46+I46+J46+K46</f>
         <v/>
       </c>
     </row>
@@ -12695,31 +12619,32 @@
       <c r="E47" s="44" t="n">
         <v>24794</v>
       </c>
-      <c r="F47" s="170">
-        <f>D42/E42</f>
-        <v/>
-      </c>
-      <c r="G47" s="119" t="n">
-        <v>1454.7</v>
+      <c r="F47" s="188">
+        <f>D47/E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="44">
+        <f>F19</f>
+        <v/>
       </c>
       <c r="H47" s="9">
-        <f>ROUND(D42*G42,0)</f>
+        <f>ROUND(D47*G47,0)</f>
         <v/>
       </c>
       <c r="I47" s="9">
-        <f>ROUND(20*G42*F42,0)</f>
+        <f>ROUND(G19*F47*G47,0)</f>
         <v/>
       </c>
       <c r="J47" s="9">
-        <f>ROUND(H19*F42,0)</f>
+        <f>ROUND(H19*F47,0)</f>
         <v/>
       </c>
       <c r="K47" s="9">
-        <f>ROUND(I19*F42,0)</f>
+        <f>ROUND(I19*F47,0)</f>
         <v/>
       </c>
       <c r="L47" s="46">
-        <f>H42+I42+J42+K42</f>
+        <f>H47+I47+J47+K47</f>
         <v/>
       </c>
     </row>
@@ -12745,31 +12670,32 @@
       <c r="E48" s="44" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F48" s="170">
-        <f>D43/E43</f>
-        <v/>
-      </c>
-      <c r="G48" s="119" t="n">
-        <v>1453.6</v>
+      <c r="F48" s="188">
+        <f>D48/E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="44">
+        <f>F20</f>
+        <v/>
       </c>
       <c r="H48" s="9">
-        <f>ROUND(D43*G43,0)</f>
+        <f>ROUND(D48*G48,0)</f>
         <v/>
       </c>
       <c r="I48" s="9">
-        <f>ROUND(20*G43*F43,0)</f>
+        <f>ROUND(G20*F48*G48,0)</f>
         <v/>
       </c>
       <c r="J48" s="9">
-        <f>ROUND(H20*F43,0)</f>
+        <f>ROUND(H20*F48,0)</f>
         <v/>
       </c>
       <c r="K48" s="9">
-        <f>ROUND(I20*F43,0)</f>
+        <f>ROUND(I20*F48,0)</f>
         <v/>
       </c>
       <c r="L48" s="46">
-        <f>H43+I43+J43+K43</f>
+        <f>H48+I48+J48+K48</f>
         <v/>
       </c>
     </row>
@@ -12795,31 +12721,32 @@
       <c r="E49" s="44" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F49" s="170">
-        <f>D44/E44</f>
-        <v/>
-      </c>
-      <c r="G49" s="119" t="n">
-        <v>1453.6</v>
+      <c r="F49" s="188">
+        <f>D49/E49</f>
+        <v/>
+      </c>
+      <c r="G49" s="44">
+        <f>F20</f>
+        <v/>
       </c>
       <c r="H49" s="9">
-        <f>ROUND(D44*G44,0)</f>
+        <f>ROUND(D49*G49,0)</f>
         <v/>
       </c>
       <c r="I49" s="9">
-        <f>ROUND(20*G44*F44,0)</f>
+        <f>ROUND(G20*F49*G49,0)</f>
         <v/>
       </c>
       <c r="J49" s="9">
-        <f>ROUND(H20*F44,0)</f>
+        <f>ROUND(H20*F49,0)</f>
         <v/>
       </c>
       <c r="K49" s="9">
-        <f>ROUND(I20*F44,0)</f>
+        <f>ROUND(I20*F49,0)</f>
         <v/>
       </c>
       <c r="L49" s="46">
-        <f>H44+I44+J44+K44</f>
+        <f>H49+I49+J49+K49</f>
         <v/>
       </c>
     </row>
@@ -12845,31 +12772,32 @@
       <c r="E50" s="44" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F50" s="170">
-        <f>D45/E45</f>
-        <v/>
-      </c>
-      <c r="G50" s="119" t="n">
-        <v>1453.6</v>
+      <c r="F50" s="188">
+        <f>D50/E50</f>
+        <v/>
+      </c>
+      <c r="G50" s="44">
+        <f>F20</f>
+        <v/>
       </c>
       <c r="H50" s="9">
-        <f>ROUND(D45*G45,0)</f>
+        <f>ROUND(D50*G50,0)</f>
         <v/>
       </c>
       <c r="I50" s="9">
-        <f>ROUND(20*G45*F45,0)</f>
+        <f>ROUND(G20*F50*G50,0)</f>
         <v/>
       </c>
       <c r="J50" s="9">
-        <f>ROUND(H20*F45,0)</f>
+        <f>ROUND(H20*F50,0)</f>
         <v/>
       </c>
       <c r="K50" s="9">
-        <f>ROUND(I20*F45,0)</f>
+        <f>ROUND(I20*F50,0)</f>
         <v/>
       </c>
       <c r="L50" s="46">
-        <f>H45+I45+J45+K45</f>
+        <f>H50+I50+J50+K50</f>
         <v/>
       </c>
     </row>
@@ -12895,31 +12823,32 @@
       <c r="E51" s="44" t="n">
         <v>26358</v>
       </c>
-      <c r="F51" s="170">
-        <f>D46/E46</f>
-        <v/>
-      </c>
-      <c r="G51" s="119" t="n">
-        <v>1460.7</v>
+      <c r="F51" s="188">
+        <f>D51/E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="44">
+        <f>F21</f>
+        <v/>
       </c>
       <c r="H51" s="9">
-        <f>ROUND(D46*G46,0)</f>
+        <f>ROUND(D51*G51,0)</f>
         <v/>
       </c>
       <c r="I51" s="9">
-        <f>ROUND(20*G46*F46,0)</f>
+        <f>ROUND(G21*F51*G51,0)</f>
         <v/>
       </c>
       <c r="J51" s="9">
-        <f>ROUND(H21*F46,0)</f>
+        <f>ROUND(H21*F51,0)</f>
         <v/>
       </c>
       <c r="K51" s="9">
-        <f>ROUND(I21*F46,0)</f>
+        <f>ROUND(I21*F51,0)</f>
         <v/>
       </c>
       <c r="L51" s="46">
-        <f>H46+I46+J46+K46</f>
+        <f>H51+I51+J51+K51</f>
         <v/>
       </c>
     </row>
@@ -12945,31 +12874,32 @@
       <c r="E52" s="44" t="n">
         <v>17538</v>
       </c>
-      <c r="F52" s="170">
-        <f>D47/E47</f>
-        <v/>
-      </c>
-      <c r="G52" s="119" t="n">
-        <v>1451.7</v>
+      <c r="F52" s="188">
+        <f>D52/E52</f>
+        <v/>
+      </c>
+      <c r="G52" s="44">
+        <f>F22</f>
+        <v/>
       </c>
       <c r="H52" s="9">
-        <f>ROUND(D47*G47,0)</f>
+        <f>ROUND(D52*G52,0)</f>
         <v/>
       </c>
       <c r="I52" s="9">
-        <f>ROUND(20*G47*F47,0)</f>
+        <f>ROUND(G22*F52*G52,0)</f>
         <v/>
       </c>
       <c r="J52" s="9">
-        <f>ROUND(H22*F47,0)</f>
+        <f>ROUND(H22*F52,0)</f>
         <v/>
       </c>
       <c r="K52" s="9">
-        <f>ROUND(I22*F47,0)</f>
+        <f>ROUND(I22*F52,0)</f>
         <v/>
       </c>
       <c r="L52" s="46">
-        <f>H47+I47+J47+K47</f>
+        <f>H52+I52+J52+K52</f>
         <v/>
       </c>
     </row>
@@ -12995,30 +12925,34 @@
       <c r="E53" s="44" t="n">
         <v>17538</v>
       </c>
-      <c r="F53" s="170">
-        <f>D48/E48</f>
-        <v/>
-      </c>
-      <c r="G53" s="119" t="n">
-        <v>1451.7</v>
+      <c r="F53" s="188">
+        <f>D53/E53</f>
+        <v/>
+      </c>
+      <c r="G53" s="44">
+        <f>F22</f>
+        <v/>
       </c>
       <c r="H53" s="9">
-        <f>ROUND(D48*G48,0)</f>
+        <f>ROUND(D53*G53,0)</f>
         <v/>
       </c>
       <c r="I53" s="9">
-        <f>ROUND(20*G48*F48,0)</f>
+        <f>ROUND(G22*F53*G53,0)</f>
         <v/>
       </c>
       <c r="J53" s="9">
-        <f>ROUND(H22*F48,0)</f>
+        <f>ROUND(H22*F53,0)</f>
         <v/>
       </c>
       <c r="K53" s="9">
-        <f>ROUND(I22*F48,0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="46" t="n"/>
+        <f>ROUND(I22*F53,0)</f>
+        <v/>
+      </c>
+      <c r="L53" s="46">
+        <f>H53+I53+J53+K53</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -13042,31 +12976,32 @@
       <c r="E54" s="44" t="n">
         <v>142189</v>
       </c>
-      <c r="F54" s="170">
-        <f>D49/E49</f>
-        <v/>
-      </c>
-      <c r="G54" s="119" t="n">
-        <v>1441.6</v>
+      <c r="F54" s="188">
+        <f>D54/E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="44">
+        <f>F23</f>
+        <v/>
       </c>
       <c r="H54" s="9">
-        <f>ROUND(D49*G49,0)</f>
+        <f>ROUND(D54*G54,0)</f>
         <v/>
       </c>
       <c r="I54" s="9">
-        <f>ROUND(20*G49*F49,0)</f>
+        <f>ROUND(G23*F54*G54,0)</f>
         <v/>
       </c>
       <c r="J54" s="9">
-        <f>ROUND(H23*F49,0)</f>
+        <f>ROUND(H23*F54,0)</f>
         <v/>
       </c>
       <c r="K54" s="9">
-        <f>ROUND(I23*F49,0)</f>
+        <f>ROUND(I23*F54,0)</f>
         <v/>
       </c>
       <c r="L54" s="46">
-        <f>H49+I49+J49+K49</f>
+        <f>H54+I54+J54+K54</f>
         <v/>
       </c>
     </row>
@@ -13092,31 +13027,32 @@
       <c r="E55" s="44" t="n">
         <v>142189</v>
       </c>
-      <c r="F55" s="170">
-        <f>D50/E50</f>
-        <v/>
-      </c>
-      <c r="G55" s="119" t="n">
-        <v>1441.6</v>
+      <c r="F55" s="188">
+        <f>D55/E55</f>
+        <v/>
+      </c>
+      <c r="G55" s="44">
+        <f>F23</f>
+        <v/>
       </c>
       <c r="H55" s="9">
-        <f>ROUND(D50*G50,0)</f>
+        <f>ROUND(D55*G55,0)</f>
         <v/>
       </c>
       <c r="I55" s="9">
-        <f>ROUND(20*G50*F50,0)</f>
+        <f>ROUND(G23*F55*G55,0)</f>
         <v/>
       </c>
       <c r="J55" s="9">
-        <f>ROUND(H23*F50,0)</f>
+        <f>ROUND(H23*F55,0)</f>
         <v/>
       </c>
       <c r="K55" s="9">
-        <f>ROUND(I23*F50,0)</f>
+        <f>ROUND(I23*F55,0)</f>
         <v/>
       </c>
       <c r="L55" s="46">
-        <f>H50+I50+J50+K50</f>
+        <f>H55+I55+J55+K55</f>
         <v/>
       </c>
     </row>
@@ -13142,31 +13078,32 @@
       <c r="E56" s="44" t="n">
         <v>137850</v>
       </c>
-      <c r="F56" s="170">
-        <f>D51/E51</f>
-        <v/>
-      </c>
-      <c r="G56" s="119" t="n">
-        <v>1477.6</v>
+      <c r="F56" s="188">
+        <f>D56/E56</f>
+        <v/>
+      </c>
+      <c r="G56" s="44">
+        <f>F24</f>
+        <v/>
       </c>
       <c r="H56" s="9">
-        <f>ROUND(D51*G51,0)</f>
+        <f>ROUND(D56*G56,0)</f>
         <v/>
       </c>
       <c r="I56" s="9">
-        <f>ROUND(20*G51*F51,0)</f>
+        <f>ROUND(G24*F56*G56,0)</f>
         <v/>
       </c>
       <c r="J56" s="9">
-        <f>ROUND(H24*F51,0)</f>
+        <f>ROUND(H24*F56,0)</f>
         <v/>
       </c>
       <c r="K56" s="9">
-        <f>ROUND(I24*F51,0)</f>
+        <f>ROUND(I24*F56,0)</f>
         <v/>
       </c>
       <c r="L56" s="46">
-        <f>H51+I51+J51+K51</f>
+        <f>H56+I56+J56+K56</f>
         <v/>
       </c>
     </row>
@@ -13192,31 +13129,32 @@
       <c r="E57" s="44" t="n">
         <v>34354</v>
       </c>
-      <c r="F57" s="170">
-        <f>D52/E52</f>
-        <v/>
-      </c>
-      <c r="G57" s="119" t="n">
-        <v>1505.7</v>
+      <c r="F57" s="188">
+        <f>D57/E57</f>
+        <v/>
+      </c>
+      <c r="G57" s="44">
+        <f>F25</f>
+        <v/>
       </c>
       <c r="H57" s="9">
-        <f>ROUND(D52*G52,0)</f>
+        <f>ROUND(D57*G57,0)</f>
         <v/>
       </c>
       <c r="I57" s="9">
-        <f>ROUND(20*G52*F52,0)</f>
+        <f>ROUND(G25*F57*G57,0)</f>
         <v/>
       </c>
       <c r="J57" s="9">
-        <f>ROUND(H25*F52,0)</f>
+        <f>ROUND(H25*F57,0)</f>
         <v/>
       </c>
       <c r="K57" s="9">
-        <f>ROUND(I25*F52,0)</f>
+        <f>ROUND(I25*F57,0)</f>
         <v/>
       </c>
       <c r="L57" s="46">
-        <f>H52+I52+J52+K52</f>
+        <f>H57+I57+J57+K57</f>
         <v/>
       </c>
     </row>
@@ -13242,31 +13180,32 @@
       <c r="E58" s="44" t="n">
         <v>34354</v>
       </c>
-      <c r="F58" s="170">
-        <f>D53/E53</f>
-        <v/>
-      </c>
-      <c r="G58" s="119" t="n">
-        <v>1505.7</v>
+      <c r="F58" s="188">
+        <f>D58/E58</f>
+        <v/>
+      </c>
+      <c r="G58" s="44">
+        <f>F25</f>
+        <v/>
       </c>
       <c r="H58" s="9">
-        <f>ROUND(D53*G53,0)</f>
+        <f>ROUND(D58*G58,0)</f>
         <v/>
       </c>
       <c r="I58" s="9">
-        <f>ROUND(20*G53*F53,0)</f>
+        <f>ROUND(G25*F58*G58,0)</f>
         <v/>
       </c>
       <c r="J58" s="9">
-        <f>ROUND(H25*F53,0)</f>
+        <f>ROUND(H25*F58,0)</f>
         <v/>
       </c>
       <c r="K58" s="9">
-        <f>ROUND(I25*F53,0)</f>
+        <f>ROUND(I25*F58,0)</f>
         <v/>
       </c>
       <c r="L58" s="46">
-        <f>H53+I53+J53+K53</f>
+        <f>H58+I58+J58+K58</f>
         <v/>
       </c>
     </row>
@@ -13292,31 +13231,32 @@
       <c r="E59" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F59" s="170">
-        <f>D54/E54</f>
-        <v/>
-      </c>
-      <c r="G59" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F59" s="188">
+        <f>D59/E59</f>
+        <v/>
+      </c>
+      <c r="G59" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H59" s="9">
-        <f>ROUND(D54*G54,0)</f>
+        <f>ROUND(D59*G59,0)</f>
         <v/>
       </c>
       <c r="I59" s="9">
-        <f>ROUND(20*G54*F54,0)</f>
+        <f>ROUND(G26*F59*G59,0)</f>
         <v/>
       </c>
       <c r="J59" s="9">
-        <f>ROUND(H26*F54,0)</f>
+        <f>ROUND(H26*F59,0)</f>
         <v/>
       </c>
       <c r="K59" s="9">
-        <f>ROUND(I26*F54,0)</f>
+        <f>ROUND(I26*F59,0)</f>
         <v/>
       </c>
       <c r="L59" s="46">
-        <f>H54+I54+J54+K54</f>
+        <f>H59+I59+J59+K59</f>
         <v/>
       </c>
     </row>
@@ -13342,31 +13282,32 @@
       <c r="E60" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F60" s="170">
-        <f>D55/E55</f>
-        <v/>
-      </c>
-      <c r="G60" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F60" s="188">
+        <f>D60/E60</f>
+        <v/>
+      </c>
+      <c r="G60" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H60" s="9">
-        <f>ROUND(D55*G55,0)</f>
+        <f>ROUND(D60*G60,0)</f>
         <v/>
       </c>
       <c r="I60" s="9">
-        <f>ROUND(20*G55*F55,0)</f>
+        <f>ROUND(G26*F60*G60,0)</f>
         <v/>
       </c>
       <c r="J60" s="9">
-        <f>ROUND(H26*F55,0)</f>
+        <f>ROUND(H26*F60,0)</f>
         <v/>
       </c>
       <c r="K60" s="9">
-        <f>ROUND(I26*F55,0)</f>
+        <f>ROUND(I26*F60,0)</f>
         <v/>
       </c>
       <c r="L60" s="46">
-        <f>H55+I55+J55+K55</f>
+        <f>H60+I60+J60+K60</f>
         <v/>
       </c>
     </row>
@@ -13392,31 +13333,32 @@
       <c r="E61" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F61" s="170">
-        <f>D56/E56</f>
-        <v/>
-      </c>
-      <c r="G61" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F61" s="188">
+        <f>D61/E61</f>
+        <v/>
+      </c>
+      <c r="G61" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H61" s="9">
-        <f>ROUND(D56*G56,0)</f>
+        <f>ROUND(D61*G61,0)</f>
         <v/>
       </c>
       <c r="I61" s="9">
-        <f>ROUND(20*G56*F56,0)</f>
+        <f>ROUND(G26*F61*G61,0)</f>
         <v/>
       </c>
       <c r="J61" s="9">
-        <f>ROUND(H26*F56,0)</f>
+        <f>ROUND(H26*F61,0)</f>
         <v/>
       </c>
       <c r="K61" s="9">
-        <f>ROUND(I26*F56,0)</f>
+        <f>ROUND(I26*F61,0)</f>
         <v/>
       </c>
       <c r="L61" s="46">
-        <f>H56+I56+J56+K56</f>
+        <f>H61+I61+J61+K61</f>
         <v/>
       </c>
     </row>
@@ -13442,31 +13384,32 @@
       <c r="E62" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F62" s="170">
-        <f>D57/E57</f>
-        <v/>
-      </c>
-      <c r="G62" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F62" s="188">
+        <f>D62/E62</f>
+        <v/>
+      </c>
+      <c r="G62" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H62" s="9">
-        <f>ROUND(D57*G57,0)</f>
+        <f>ROUND(D62*G62,0)</f>
         <v/>
       </c>
       <c r="I62" s="9">
-        <f>ROUND(20*G57*F57,0)</f>
+        <f>ROUND(G26*F62*G62,0)</f>
         <v/>
       </c>
       <c r="J62" s="9">
-        <f>ROUND(H26*F57,0)</f>
+        <f>ROUND(H26*F62,0)</f>
         <v/>
       </c>
       <c r="K62" s="9">
-        <f>ROUND(I26*F57,0)</f>
+        <f>ROUND(I26*F62,0)</f>
         <v/>
       </c>
       <c r="L62" s="46">
-        <f>H57+I57+J57+K57</f>
+        <f>H62+I62+J62+K62</f>
         <v/>
       </c>
     </row>
@@ -13492,31 +13435,32 @@
       <c r="E63" s="44" t="n">
         <v>57650</v>
       </c>
-      <c r="F63" s="170">
-        <f>D58/E58</f>
-        <v/>
-      </c>
-      <c r="G63" s="119" t="n">
-        <v>1481.9</v>
+      <c r="F63" s="188">
+        <f>D63/E63</f>
+        <v/>
+      </c>
+      <c r="G63" s="44">
+        <f>F27</f>
+        <v/>
       </c>
       <c r="H63" s="9">
-        <f>ROUND(D58*G58,0)</f>
+        <f>ROUND(D63*G63,0)</f>
         <v/>
       </c>
       <c r="I63" s="9">
-        <f>ROUND(20*G58*F58,0)</f>
+        <f>ROUND(G27*F63*G63,0)</f>
         <v/>
       </c>
       <c r="J63" s="9">
-        <f>ROUND(H27*F58,0)</f>
+        <f>ROUND(H27*F63,0)</f>
         <v/>
       </c>
       <c r="K63" s="9">
-        <f>ROUND(I27*F58,0)</f>
+        <f>ROUND(I27*F63,0)</f>
         <v/>
       </c>
       <c r="L63" s="46">
-        <f>H58+I58+J58+K58</f>
+        <f>H63+I63+J63+K63</f>
         <v/>
       </c>
     </row>
@@ -13542,31 +13486,32 @@
       <c r="E64" s="44" t="n">
         <v>57650</v>
       </c>
-      <c r="F64" s="170">
-        <f>D59/E59</f>
-        <v/>
-      </c>
-      <c r="G64" s="119" t="n">
-        <v>1481.9</v>
+      <c r="F64" s="188">
+        <f>D64/E64</f>
+        <v/>
+      </c>
+      <c r="G64" s="44">
+        <f>F27</f>
+        <v/>
       </c>
       <c r="H64" s="9">
-        <f>ROUND(D59*G59,0)</f>
+        <f>ROUND(D64*G64,0)</f>
         <v/>
       </c>
       <c r="I64" s="9">
-        <f>ROUND(20*G59*F59,0)</f>
+        <f>ROUND(G27*F64*G64,0)</f>
         <v/>
       </c>
       <c r="J64" s="9">
-        <f>ROUND(H27*F59,0)</f>
+        <f>ROUND(H27*F64,0)</f>
         <v/>
       </c>
       <c r="K64" s="9">
-        <f>ROUND(I27*F59,0)</f>
+        <f>ROUND(I27*F64,0)</f>
         <v/>
       </c>
       <c r="L64" s="46">
-        <f>H59+I59+J59+K59</f>
+        <f>H64+I64+J64+K64</f>
         <v/>
       </c>
     </row>
@@ -13592,31 +13537,32 @@
       <c r="E65" s="44" t="n">
         <v>57650</v>
       </c>
-      <c r="F65" s="170">
-        <f>D60/E60</f>
-        <v/>
-      </c>
-      <c r="G65" s="119" t="n">
-        <v>1481.9</v>
+      <c r="F65" s="188">
+        <f>D65/E65</f>
+        <v/>
+      </c>
+      <c r="G65" s="44">
+        <f>F27</f>
+        <v/>
       </c>
       <c r="H65" s="9">
-        <f>ROUND(D60*G60,0)</f>
+        <f>ROUND(D65*G65,0)</f>
         <v/>
       </c>
       <c r="I65" s="9">
-        <f>ROUND(20*G60*F60,0)</f>
+        <f>ROUND(G27*F65*G65,0)</f>
         <v/>
       </c>
       <c r="J65" s="9">
-        <f>ROUND(H27*F60,0)</f>
+        <f>ROUND(H27*F65,0)</f>
         <v/>
       </c>
       <c r="K65" s="9">
-        <f>ROUND(I27*F60,0)</f>
+        <f>ROUND(I27*F65,0)</f>
         <v/>
       </c>
       <c r="L65" s="46">
-        <f>H60+I60+J60+K60</f>
+        <f>H65+I65+J65+K65</f>
         <v/>
       </c>
     </row>
@@ -13642,26 +13588,33 @@
       <c r="E66" s="173" t="n">
         <v>297580</v>
       </c>
-      <c r="F66" s="174" t="n">
-        <v>0.03696484978829222</v>
-      </c>
-      <c r="G66" s="175" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="H66" s="176" t="n">
-        <v>16310800</v>
-      </c>
-      <c r="I66" s="176" t="n">
-        <v>1096</v>
-      </c>
-      <c r="J66" s="176" t="n">
-        <v>462</v>
-      </c>
-      <c r="K66" s="176" t="n">
-        <v>296</v>
-      </c>
-      <c r="L66" s="177" t="n">
-        <v>16312654</v>
+      <c r="F66" s="189">
+        <f>D66/E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="173">
+        <f>F31</f>
+        <v/>
+      </c>
+      <c r="H66" s="176">
+        <f>ROUND(D66*G66,0)</f>
+        <v/>
+      </c>
+      <c r="I66" s="176">
+        <f>ROUND(G31*F66*G66,0)</f>
+        <v/>
+      </c>
+      <c r="J66" s="176">
+        <f>ROUND(H31*F66,0)</f>
+        <v/>
+      </c>
+      <c r="K66" s="176">
+        <f>ROUND(I31*F66,0)</f>
+        <v/>
+      </c>
+      <c r="L66" s="177">
+        <f>H66+I66+J66+K66</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -13686,26 +13639,33 @@
       <c r="E67" s="173" t="n">
         <v>297580</v>
       </c>
-      <c r="F67" s="174" t="n">
-        <v>0.9630351502117078</v>
-      </c>
-      <c r="G67" s="175" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="H67" s="176" t="n">
-        <v>424990980</v>
-      </c>
-      <c r="I67" s="176" t="n">
-        <v>28560</v>
-      </c>
-      <c r="J67" s="176" t="n">
-        <v>12038</v>
-      </c>
-      <c r="K67" s="176" t="n">
-        <v>7704</v>
-      </c>
-      <c r="L67" s="177" t="n">
-        <v>425039282</v>
+      <c r="F67" s="189">
+        <f>D67/E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="173">
+        <f>F31</f>
+        <v/>
+      </c>
+      <c r="H67" s="176">
+        <f>ROUND(D67*G67,0)</f>
+        <v/>
+      </c>
+      <c r="I67" s="176">
+        <f>ROUND(G31*F67*G67,0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="176">
+        <f>ROUND(H31*F67,0)</f>
+        <v/>
+      </c>
+      <c r="K67" s="176">
+        <f>ROUND(I31*F67,0)</f>
+        <v/>
+      </c>
+      <c r="L67" s="177">
+        <f>H67+I67+J67+K67</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -13730,26 +13690,33 @@
       <c r="E68" s="173" t="n">
         <v>4388.4</v>
       </c>
-      <c r="F68" s="174" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="175" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="H68" s="176" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="I68" s="176" t="n">
-        <v>43527</v>
-      </c>
-      <c r="J68" s="176" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K68" s="176" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L68" s="177" t="n">
-        <v>7763609</v>
+      <c r="F68" s="189">
+        <f>D68/E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="173">
+        <f>F32</f>
+        <v/>
+      </c>
+      <c r="H68" s="176">
+        <f>ROUND(D68*G68,0)</f>
+        <v/>
+      </c>
+      <c r="I68" s="176">
+        <f>ROUND(G32*F68*G68,0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="176">
+        <f>ROUND(H32*F68,0)</f>
+        <v/>
+      </c>
+      <c r="K68" s="176">
+        <f>ROUND(I32*F68,0)</f>
+        <v/>
+      </c>
+      <c r="L68" s="177">
+        <f>H68+I68+J68+K68</f>
+        <v/>
       </c>
     </row>
     <row r="76">

--- a/RNR_수입원가_2026_20260424.xlsx
+++ b/RNR_수입원가_2026_20260424.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18000" yWindow="780" windowWidth="18000" windowHeight="22600" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0&quot;일&quot;"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="22">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -65,12 +65,6 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="나눔명조"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -171,27 +165,20 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
       <b val="1"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="13">
@@ -411,9 +398,9 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -520,15 +507,15 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -537,101 +524,101 @@
     <xf numFmtId="4" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -640,89 +627,89 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="18" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="19" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="18" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="18" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -731,36 +718,45 @@
     <xf numFmtId="4" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -768,47 +764,41 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -830,13 +820,13 @@
     <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -848,26 +838,19 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -876,30 +859,24 @@
     <xf numFmtId="166" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1280,194 +1257,194 @@
   <dimension ref="A1:AF76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
-    <col width="5" customWidth="1" style="130" min="1" max="1"/>
-    <col width="12" customWidth="1" style="130" min="2" max="2"/>
-    <col width="10.83203125" customWidth="1" style="130" min="3" max="3"/>
-    <col width="12.6640625" customWidth="1" style="130" min="4" max="4"/>
-    <col width="12" customWidth="1" style="130" min="5" max="5"/>
-    <col width="13.33203125" customWidth="1" style="130" min="6" max="7"/>
-    <col width="12" customWidth="1" style="130" min="8" max="8"/>
-    <col width="10.6640625" customWidth="1" style="130" min="9" max="9"/>
-    <col width="15.6640625" customWidth="1" style="130" min="10" max="13"/>
-    <col width="24" customWidth="1" style="130" min="14" max="14"/>
-    <col width="11.83203125" customWidth="1" style="130" min="15" max="15"/>
-    <col width="15.1640625" customWidth="1" style="130" min="16" max="16"/>
-    <col width="13.1640625" customWidth="1" style="130" min="17" max="23"/>
+    <col width="5" customWidth="1" style="135" min="1" max="1"/>
+    <col width="12" customWidth="1" style="135" min="2" max="2"/>
+    <col width="10.83203125" customWidth="1" style="135" min="3" max="3"/>
+    <col width="12.6640625" customWidth="1" style="135" min="4" max="4"/>
+    <col width="12" customWidth="1" style="135" min="5" max="5"/>
+    <col width="13.33203125" customWidth="1" style="135" min="6" max="7"/>
+    <col width="12" customWidth="1" style="135" min="8" max="8"/>
+    <col width="10.6640625" customWidth="1" style="135" min="9" max="9"/>
+    <col width="15.6640625" customWidth="1" style="135" min="10" max="13"/>
+    <col width="36.83203125" customWidth="1" style="135" min="14" max="14"/>
+    <col width="11.83203125" customWidth="1" style="135" min="15" max="15"/>
+    <col width="16.83203125" customWidth="1" style="135" min="16" max="16"/>
+    <col width="13.1640625" customWidth="1" style="135" min="17" max="23"/>
     <col width="10.83203125" customWidth="1" style="73" min="24" max="24"/>
-    <col width="15" customWidth="1" style="130" min="25" max="27"/>
-    <col width="5.6640625" customWidth="1" style="130" min="28" max="28"/>
-    <col width="15" customWidth="1" style="130" min="29" max="29"/>
-    <col width="13.33203125" customWidth="1" style="130" min="30" max="32"/>
-    <col width="8.6640625" customWidth="1" style="130" min="33" max="35"/>
-    <col width="8.6640625" customWidth="1" style="130" min="36" max="16384"/>
+    <col width="15" customWidth="1" style="135" min="25" max="27"/>
+    <col width="5.6640625" customWidth="1" style="135" min="28" max="28"/>
+    <col width="15" customWidth="1" style="135" min="29" max="29"/>
+    <col width="13.33203125" customWidth="1" style="135" min="30" max="32"/>
+    <col width="8.6640625" customWidth="1" style="135" min="33" max="36"/>
+    <col width="8.6640625" customWidth="1" style="135" min="37" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="123" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>RNR 2026년 PO별 수입원가 산출표 (Master)</t>
         </is>
       </c>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="118" t="n"/>
-      <c r="K1" s="118" t="n"/>
-      <c r="L1" s="118" t="n"/>
-      <c r="M1" s="118" t="n"/>
-      <c r="N1" s="118" t="n"/>
-      <c r="O1" s="118" t="n"/>
-      <c r="P1" s="118" t="n"/>
-      <c r="Q1" s="118" t="n"/>
-      <c r="R1" s="118" t="n"/>
-      <c r="S1" s="118" t="n"/>
-      <c r="T1" s="118" t="n"/>
-      <c r="U1" s="118" t="n"/>
-      <c r="V1" s="118" t="n"/>
-      <c r="W1" s="118" t="n"/>
-      <c r="X1" s="118" t="n"/>
-      <c r="Y1" s="118" t="n"/>
-      <c r="Z1" s="118" t="n"/>
-      <c r="AA1" s="118" t="n"/>
-      <c r="AB1" s="118" t="n"/>
-      <c r="AC1" s="118" t="n"/>
-      <c r="AD1" s="118" t="n"/>
-      <c r="AE1" s="118" t="n"/>
-      <c r="AF1" s="119" t="n"/>
+      <c r="B1" s="123" t="n"/>
+      <c r="C1" s="123" t="n"/>
+      <c r="D1" s="123" t="n"/>
+      <c r="E1" s="123" t="n"/>
+      <c r="F1" s="123" t="n"/>
+      <c r="G1" s="123" t="n"/>
+      <c r="H1" s="123" t="n"/>
+      <c r="I1" s="123" t="n"/>
+      <c r="J1" s="123" t="n"/>
+      <c r="K1" s="123" t="n"/>
+      <c r="L1" s="123" t="n"/>
+      <c r="M1" s="123" t="n"/>
+      <c r="N1" s="123" t="n"/>
+      <c r="O1" s="123" t="n"/>
+      <c r="P1" s="123" t="n"/>
+      <c r="Q1" s="123" t="n"/>
+      <c r="R1" s="123" t="n"/>
+      <c r="S1" s="123" t="n"/>
+      <c r="T1" s="123" t="n"/>
+      <c r="U1" s="123" t="n"/>
+      <c r="V1" s="123" t="n"/>
+      <c r="W1" s="123" t="n"/>
+      <c r="X1" s="123" t="n"/>
+      <c r="Y1" s="123" t="n"/>
+      <c r="Z1" s="123" t="n"/>
+      <c r="AA1" s="123" t="n"/>
+      <c r="AB1" s="123" t="n"/>
+      <c r="AC1" s="123" t="n"/>
+      <c r="AD1" s="123" t="n"/>
+      <c r="AE1" s="123" t="n"/>
+      <c r="AF1" s="124" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="126" t="inlineStr">
+      <c r="A2" s="131" t="inlineStr">
         <is>
           <t>회계처리용 통합 데이터  |  기준일: 2026-04-24  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
-      <c r="B2" s="118" t="n"/>
-      <c r="C2" s="118" t="n"/>
-      <c r="D2" s="118" t="n"/>
-      <c r="E2" s="118" t="n"/>
-      <c r="F2" s="118" t="n"/>
-      <c r="G2" s="118" t="n"/>
-      <c r="H2" s="118" t="n"/>
-      <c r="I2" s="118" t="n"/>
-      <c r="J2" s="118" t="n"/>
-      <c r="K2" s="118" t="n"/>
-      <c r="L2" s="118" t="n"/>
-      <c r="M2" s="118" t="n"/>
-      <c r="N2" s="118" t="n"/>
-      <c r="O2" s="118" t="n"/>
-      <c r="P2" s="118" t="n"/>
-      <c r="Q2" s="118" t="n"/>
-      <c r="R2" s="118" t="n"/>
-      <c r="S2" s="118" t="n"/>
-      <c r="T2" s="118" t="n"/>
-      <c r="U2" s="118" t="n"/>
-      <c r="V2" s="118" t="n"/>
-      <c r="W2" s="118" t="n"/>
-      <c r="X2" s="118" t="n"/>
-      <c r="Y2" s="118" t="n"/>
-      <c r="Z2" s="118" t="n"/>
-      <c r="AA2" s="118" t="n"/>
-      <c r="AB2" s="118" t="n"/>
-      <c r="AC2" s="118" t="n"/>
-      <c r="AD2" s="118" t="n"/>
-      <c r="AE2" s="118" t="n"/>
-      <c r="AF2" s="119" t="n"/>
+      <c r="B2" s="123" t="n"/>
+      <c r="C2" s="123" t="n"/>
+      <c r="D2" s="123" t="n"/>
+      <c r="E2" s="123" t="n"/>
+      <c r="F2" s="123" t="n"/>
+      <c r="G2" s="123" t="n"/>
+      <c r="H2" s="123" t="n"/>
+      <c r="I2" s="123" t="n"/>
+      <c r="J2" s="123" t="n"/>
+      <c r="K2" s="123" t="n"/>
+      <c r="L2" s="123" t="n"/>
+      <c r="M2" s="123" t="n"/>
+      <c r="N2" s="123" t="n"/>
+      <c r="O2" s="123" t="n"/>
+      <c r="P2" s="123" t="n"/>
+      <c r="Q2" s="123" t="n"/>
+      <c r="R2" s="123" t="n"/>
+      <c r="S2" s="123" t="n"/>
+      <c r="T2" s="123" t="n"/>
+      <c r="U2" s="123" t="n"/>
+      <c r="V2" s="123" t="n"/>
+      <c r="W2" s="123" t="n"/>
+      <c r="X2" s="123" t="n"/>
+      <c r="Y2" s="123" t="n"/>
+      <c r="Z2" s="123" t="n"/>
+      <c r="AA2" s="123" t="n"/>
+      <c r="AB2" s="123" t="n"/>
+      <c r="AC2" s="123" t="n"/>
+      <c r="AD2" s="123" t="n"/>
+      <c r="AE2" s="123" t="n"/>
+      <c r="AF2" s="124" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="117" t="inlineStr">
+      <c r="A3" s="122" t="inlineStr">
         <is>
           <t>① 기본정보</t>
         </is>
       </c>
-      <c r="B3" s="118" t="n"/>
-      <c r="C3" s="118" t="n"/>
-      <c r="D3" s="118" t="n"/>
-      <c r="E3" s="118" t="n"/>
-      <c r="F3" s="119" t="n"/>
-      <c r="G3" s="117" t="inlineStr">
+      <c r="B3" s="123" t="n"/>
+      <c r="C3" s="123" t="n"/>
+      <c r="D3" s="123" t="n"/>
+      <c r="E3" s="123" t="n"/>
+      <c r="F3" s="124" t="n"/>
+      <c r="G3" s="122" t="inlineStr">
         <is>
           <t>② 송금/장비대금</t>
         </is>
       </c>
-      <c r="H3" s="118" t="n"/>
-      <c r="I3" s="118" t="n"/>
-      <c r="J3" s="118" t="n"/>
-      <c r="K3" s="118" t="n"/>
-      <c r="L3" s="118" t="n"/>
-      <c r="M3" s="118" t="n"/>
-      <c r="N3" s="119" t="n"/>
-      <c r="O3" s="117" t="inlineStr">
+      <c r="H3" s="123" t="n"/>
+      <c r="I3" s="123" t="n"/>
+      <c r="J3" s="123" t="n"/>
+      <c r="K3" s="123" t="n"/>
+      <c r="L3" s="123" t="n"/>
+      <c r="M3" s="123" t="n"/>
+      <c r="N3" s="124" t="n"/>
+      <c r="O3" s="122" t="inlineStr">
         <is>
           <t>③ 수입신고</t>
         </is>
       </c>
-      <c r="P3" s="118" t="n"/>
-      <c r="Q3" s="118" t="n"/>
-      <c r="R3" s="118" t="n"/>
-      <c r="S3" s="118" t="n"/>
-      <c r="T3" s="118" t="n"/>
-      <c r="U3" s="118" t="n"/>
-      <c r="V3" s="118" t="n"/>
-      <c r="W3" s="119" t="n"/>
-      <c r="X3" s="117" t="inlineStr">
+      <c r="P3" s="123" t="n"/>
+      <c r="Q3" s="123" t="n"/>
+      <c r="R3" s="123" t="n"/>
+      <c r="S3" s="123" t="n"/>
+      <c r="T3" s="123" t="n"/>
+      <c r="U3" s="123" t="n"/>
+      <c r="V3" s="123" t="n"/>
+      <c r="W3" s="124" t="n"/>
+      <c r="X3" s="122" t="inlineStr">
         <is>
           <t>④ 통관/운송</t>
         </is>
       </c>
-      <c r="Y3" s="118" t="n"/>
-      <c r="Z3" s="119" t="n"/>
-      <c r="AA3" s="125" t="inlineStr">
+      <c r="Y3" s="123" t="n"/>
+      <c r="Z3" s="124" t="n"/>
+      <c r="AA3" s="130" t="inlineStr">
         <is>
           <t>⑤ 원가산출</t>
         </is>
       </c>
-      <c r="AB3" s="118" t="n"/>
-      <c r="AC3" s="119" t="n"/>
-      <c r="AD3" s="117" t="inlineStr">
+      <c r="AB3" s="123" t="n"/>
+      <c r="AC3" s="124" t="n"/>
+      <c r="AD3" s="122" t="inlineStr">
         <is>
           <t>⑥ 계약기간</t>
         </is>
       </c>
-      <c r="AE3" s="118" t="n"/>
-      <c r="AF3" s="119" t="n"/>
+      <c r="AE3" s="123" t="n"/>
+      <c r="AF3" s="124" t="n"/>
     </row>
     <row r="4" ht="27.75" customHeight="1">
-      <c r="A4" s="117" t="inlineStr">
+      <c r="A4" s="122" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B4" s="117" t="inlineStr">
+      <c r="B4" s="122" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="C4" s="117" t="inlineStr">
+      <c r="C4" s="122" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D4" s="117" t="inlineStr">
+      <c r="D4" s="122" t="inlineStr">
         <is>
           <t>지불조건</t>
         </is>
       </c>
-      <c r="E4" s="117" t="inlineStr">
+      <c r="E4" s="122" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="F4" s="117" t="inlineStr">
+      <c r="F4" s="122" t="inlineStr">
         <is>
           <t>PO일자</t>
         </is>
       </c>
-      <c r="G4" s="117" t="inlineStr">
+      <c r="G4" s="122" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
@@ -1477,122 +1454,122 @@
           <t>Invoice(USD)</t>
         </is>
       </c>
-      <c r="I4" s="143" t="inlineStr">
+      <c r="I4" s="142" t="inlineStr">
         <is>
           <t>적용환율</t>
         </is>
       </c>
-      <c r="J4" s="125" t="inlineStr">
+      <c r="J4" s="130" t="inlineStr">
         <is>
           <t>장비대금(KRW)</t>
         </is>
       </c>
-      <c r="K4" s="125" t="inlineStr">
+      <c r="K4" s="130" t="inlineStr">
         <is>
           <t>원화환산액</t>
         </is>
       </c>
-      <c r="L4" s="125" t="inlineStr">
+      <c r="L4" s="130" t="inlineStr">
         <is>
           <t>수수료(안분)</t>
         </is>
       </c>
-      <c r="M4" s="125" t="inlineStr">
+      <c r="M4" s="130" t="inlineStr">
         <is>
           <t>전신료(안분)</t>
         </is>
       </c>
-      <c r="N4" s="117" t="inlineStr">
+      <c r="N4" s="122" t="inlineStr">
         <is>
           <t>품명/수량</t>
         </is>
       </c>
-      <c r="O4" s="117" t="inlineStr">
+      <c r="O4" s="122" t="inlineStr">
         <is>
           <t>수입신고일</t>
         </is>
       </c>
-      <c r="P4" s="117" t="inlineStr">
+      <c r="P4" s="122" t="inlineStr">
         <is>
           <t>수입신고번호</t>
         </is>
       </c>
-      <c r="Q4" s="117" t="inlineStr">
+      <c r="Q4" s="122" t="inlineStr">
         <is>
           <t>신고환율</t>
         </is>
       </c>
-      <c r="R4" s="117" t="inlineStr">
+      <c r="R4" s="122" t="inlineStr">
         <is>
           <t>과세가격(USD)</t>
         </is>
       </c>
-      <c r="S4" s="125" t="inlineStr">
+      <c r="S4" s="130" t="inlineStr">
         <is>
           <t>관세(KRW)</t>
         </is>
       </c>
-      <c r="T4" s="125" t="inlineStr">
+      <c r="T4" s="130" t="inlineStr">
         <is>
           <t>부가세(KRW)</t>
         </is>
       </c>
-      <c r="U4" s="117" t="inlineStr">
+      <c r="U4" s="122" t="inlineStr">
         <is>
           <t>세금계산서일</t>
         </is>
       </c>
-      <c r="V4" s="117" t="inlineStr">
+      <c r="V4" s="122" t="inlineStr">
         <is>
           <t>관세사</t>
         </is>
       </c>
-      <c r="W4" s="125" t="inlineStr">
+      <c r="W4" s="130" t="inlineStr">
         <is>
           <t>관세사비(KRW)</t>
         </is>
       </c>
-      <c r="X4" s="117" t="inlineStr">
+      <c r="X4" s="122" t="inlineStr">
         <is>
           <t>운송사</t>
         </is>
       </c>
-      <c r="Y4" s="125" t="inlineStr">
+      <c r="Y4" s="130" t="inlineStr">
         <is>
           <t>수입운송료(KRW)</t>
         </is>
       </c>
-      <c r="Z4" s="125" t="inlineStr">
+      <c r="Z4" s="130" t="inlineStr">
         <is>
           <t>소계:관부가세+통관(KRW)</t>
         </is>
       </c>
-      <c r="AA4" s="125" t="inlineStr">
+      <c r="AA4" s="130" t="inlineStr">
         <is>
           <t>총 수입원가(KRW)</t>
         </is>
       </c>
-      <c r="AB4" s="117" t="inlineStr">
+      <c r="AB4" s="122" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="AC4" s="125" t="inlineStr">
+      <c r="AC4" s="130" t="inlineStr">
         <is>
           <t>개당 원가(KRW)</t>
         </is>
       </c>
-      <c r="AD4" s="117" t="inlineStr">
+      <c r="AD4" s="122" t="inlineStr">
         <is>
           <t>귀속월</t>
         </is>
       </c>
-      <c r="AE4" s="117" t="inlineStr">
+      <c r="AE4" s="122" t="inlineStr">
         <is>
           <t>계약시작일</t>
         </is>
       </c>
-      <c r="AF4" s="117" t="inlineStr">
+      <c r="AF4" s="122" t="inlineStr">
         <is>
           <t>계약종료일</t>
         </is>
@@ -1622,16 +1599,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F5" s="144" t="n">
+      <c r="F5" s="143" t="n">
         <v>45965</v>
       </c>
-      <c r="G5" s="145" t="n">
+      <c r="G5" s="144" t="n">
         <v>46007</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>139083</v>
       </c>
-      <c r="I5" s="146">
+      <c r="I5" s="145">
         <f>IFERROR(VLOOKUP(B5,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -1655,7 +1632,7 @@
           <t>Projector</t>
         </is>
       </c>
-      <c r="O5" s="145" t="n">
+      <c r="O5" s="144" t="n">
         <v>46002</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
@@ -1677,7 +1654,7 @@
       <c r="T5" s="9" t="n">
         <v>20784342</v>
       </c>
-      <c r="U5" s="144" t="inlineStr">
+      <c r="U5" s="143" t="inlineStr">
         <is>
           <t>2025-12-26</t>
         </is>
@@ -1753,16 +1730,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F6" s="144" t="n">
+      <c r="F6" s="143" t="n">
         <v>45982</v>
       </c>
-      <c r="G6" s="145" t="n">
+      <c r="G6" s="144" t="n">
         <v>46020</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>9060</v>
       </c>
-      <c r="I6" s="146">
+      <c r="I6" s="145">
         <f>IFERROR(VLOOKUP(B6,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -1786,7 +1763,7 @@
           <t>IMB/Server</t>
         </is>
       </c>
-      <c r="O6" s="145" t="n">
+      <c r="O6" s="144" t="n">
         <v>45996</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1808,7 +1785,7 @@
       <c r="T6" s="9" t="n">
         <v>1352610</v>
       </c>
-      <c r="U6" s="144" t="inlineStr">
+      <c r="U6" s="143" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
@@ -1884,16 +1861,16 @@
           <t>부품</t>
         </is>
       </c>
-      <c r="F7" s="144" t="n">
+      <c r="F7" s="143" t="n">
         <v>45987</v>
       </c>
-      <c r="G7" s="145" t="n">
+      <c r="G7" s="144" t="n">
         <v>46007</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>4474</v>
       </c>
-      <c r="I7" s="146">
+      <c r="I7" s="145">
         <f>IFERROR(VLOOKUP(B7,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -1914,10 +1891,10 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Parts</t>
-        </is>
-      </c>
-      <c r="O7" s="145" t="n">
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="O7" s="144" t="n">
         <v>45989</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1939,7 +1916,7 @@
       <c r="T7" s="9" t="n">
         <v>756850</v>
       </c>
-      <c r="U7" s="144" t="inlineStr">
+      <c r="U7" s="143" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
@@ -2015,10 +1992,10 @@
           <t>부품</t>
         </is>
       </c>
-      <c r="F8" s="147" t="n">
+      <c r="F8" s="146" t="n">
         <v>45993</v>
       </c>
-      <c r="G8" s="148" t="inlineStr">
+      <c r="G8" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2026,7 +2003,7 @@
       <c r="H8" s="16" t="n">
         <v>362.25</v>
       </c>
-      <c r="I8" s="149">
+      <c r="I8" s="148">
         <f>IFERROR(VLOOKUP(B8,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2142,16 +2119,16 @@
           <t>부품</t>
         </is>
       </c>
-      <c r="F9" s="144" t="n">
+      <c r="F9" s="143" t="n">
         <v>45995</v>
       </c>
-      <c r="G9" s="145" t="n">
+      <c r="G9" s="144" t="n">
         <v>46035</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>252</v>
       </c>
-      <c r="I9" s="146">
+      <c r="I9" s="145">
         <f>IFERROR(VLOOKUP(B9,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2175,7 +2152,7 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="O9" s="145" t="n">
+      <c r="O9" s="144" t="n">
         <v>46002</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -2197,7 +2174,7 @@
       <c r="T9" s="9" t="n">
         <v>37658</v>
       </c>
-      <c r="U9" s="144" t="inlineStr">
+      <c r="U9" s="143" t="inlineStr">
         <is>
           <t>2025-12-26</t>
         </is>
@@ -2273,16 +2250,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F10" s="144" t="n">
+      <c r="F10" s="143" t="n">
         <v>46007</v>
       </c>
-      <c r="G10" s="145" t="n">
+      <c r="G10" s="144" t="n">
         <v>46043</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>2710</v>
       </c>
-      <c r="I10" s="146">
+      <c r="I10" s="145">
         <f>IFERROR(VLOOKUP(B10,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2306,7 +2283,7 @@
           <t>SR-1000</t>
         </is>
       </c>
-      <c r="O10" s="145" t="n">
+      <c r="O10" s="144" t="n">
         <v>46023</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -2328,7 +2305,7 @@
       <c r="T10" s="9" t="n">
         <v>399770</v>
       </c>
-      <c r="U10" s="144" t="inlineStr">
+      <c r="U10" s="143" t="inlineStr">
         <is>
           <t>2026-01-16</t>
         </is>
@@ -2404,16 +2381,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F11" s="144" t="n">
+      <c r="F11" s="143" t="n">
         <v>46007</v>
       </c>
-      <c r="G11" s="145" t="n">
+      <c r="G11" s="144" t="n">
         <v>46052</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>5056.8</v>
       </c>
-      <c r="I11" s="146">
+      <c r="I11" s="145">
         <f>IFERROR(VLOOKUP(B11,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2437,7 +2414,7 @@
           <t>ICP+TPC (6EA)</t>
         </is>
       </c>
-      <c r="O11" s="145" t="n">
+      <c r="O11" s="144" t="n">
         <v>46090</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -2459,7 +2436,7 @@
       <c r="T11" s="9" t="n">
         <v>831820</v>
       </c>
-      <c r="U11" s="144" t="inlineStr">
+      <c r="U11" s="143" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
@@ -2535,16 +2512,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F12" s="144" t="n">
+      <c r="F12" s="143" t="n">
         <v>46009</v>
       </c>
-      <c r="G12" s="145" t="n">
+      <c r="G12" s="144" t="n">
         <v>46087</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>137850</v>
       </c>
-      <c r="I12" s="146">
+      <c r="I12" s="145">
         <f>IFERROR(VLOOKUP(B12,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2568,7 +2545,7 @@
           <t>CP4425-RGB Projector (3EA)</t>
         </is>
       </c>
-      <c r="O12" s="145" t="n">
+      <c r="O12" s="144" t="n">
         <v>46030</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -2590,7 +2567,7 @@
       <c r="T12" s="9" t="n">
         <v>19976300</v>
       </c>
-      <c r="U12" s="144" t="inlineStr">
+      <c r="U12" s="143" t="inlineStr">
         <is>
           <t>2026-01-20</t>
         </is>
@@ -2666,16 +2643,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F13" s="144" t="n">
+      <c r="F13" s="143" t="n">
         <v>46010</v>
       </c>
-      <c r="G13" s="145" t="n">
+      <c r="G13" s="144" t="n">
         <v>46057</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>20174</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="145">
         <f>IFERROR(VLOOKUP(B13,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2696,10 +2673,10 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Projector/Parts</t>
-        </is>
-      </c>
-      <c r="O13" s="145" t="n">
+          <t>Projector + Touch Screen (2EA)</t>
+        </is>
+      </c>
+      <c r="O13" s="144" t="n">
         <v>46015</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
@@ -2716,12 +2693,12 @@
         <v/>
       </c>
       <c r="S13" s="9" t="n">
-        <v>0</v>
+        <v>84170</v>
       </c>
       <c r="T13" s="9" t="n">
         <v>3156262</v>
       </c>
-      <c r="U13" s="144" t="inlineStr">
+      <c r="U13" s="143" t="inlineStr">
         <is>
           <t>2026-01-08</t>
         </is>
@@ -2797,16 +2774,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F14" s="144" t="n">
+      <c r="F14" s="143" t="n">
         <v>46010</v>
       </c>
-      <c r="G14" s="145" t="n">
+      <c r="G14" s="144" t="n">
         <v>46057</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>4620</v>
       </c>
-      <c r="I14" s="146">
+      <c r="I14" s="145">
         <f>IFERROR(VLOOKUP(B14,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2827,10 +2804,10 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="O14" s="145" t="n">
+          <t>Fan (15EA)</t>
+        </is>
+      </c>
+      <c r="O14" s="144" t="n">
         <v>46015</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2847,12 +2824,12 @@
         <v/>
       </c>
       <c r="S14" s="9" t="n">
-        <v>84170</v>
+        <v>0</v>
       </c>
       <c r="T14" s="9" t="n">
         <v>722808</v>
       </c>
-      <c r="U14" s="144" t="inlineStr">
+      <c r="U14" s="143" t="inlineStr">
         <is>
           <t>2026-01-08</t>
         </is>
@@ -2928,16 +2905,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F15" s="144" t="n">
+      <c r="F15" s="143" t="n">
         <v>46011</v>
       </c>
-      <c r="G15" s="145" t="n">
+      <c r="G15" s="144" t="n">
         <v>46043</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>9626.35</v>
       </c>
-      <c r="I15" s="146">
+      <c r="I15" s="145">
         <f>IFERROR(VLOOKUP(B15,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -2961,7 +2938,7 @@
           <t>DCO-16000/L-SUB (13EA)</t>
         </is>
       </c>
-      <c r="O15" s="145" t="n">
+      <c r="O15" s="144" t="n">
         <v>46072</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2983,7 +2960,7 @@
       <c r="T15" s="9" t="n">
         <v>1704871</v>
       </c>
-      <c r="U15" s="144" t="inlineStr">
+      <c r="U15" s="143" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
@@ -3059,16 +3036,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F16" s="144" t="n">
+      <c r="F16" s="143" t="n">
         <v>46011</v>
       </c>
-      <c r="G16" s="145" t="n">
+      <c r="G16" s="144" t="n">
         <v>46007</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>4936</v>
       </c>
-      <c r="I16" s="146">
+      <c r="I16" s="145">
         <f>IFERROR(VLOOKUP(B16,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -3092,7 +3069,7 @@
           <t>Audio Amp</t>
         </is>
       </c>
-      <c r="O16" s="145" t="n">
+      <c r="O16" s="144" t="n">
         <v>46072</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -3114,7 +3091,7 @@
       <c r="T16" s="9" t="n">
         <v>874189</v>
       </c>
-      <c r="U16" s="144" t="inlineStr">
+      <c r="U16" s="143" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
@@ -3190,16 +3167,16 @@
           <t>부품</t>
         </is>
       </c>
-      <c r="F17" s="144" t="n">
+      <c r="F17" s="143" t="n">
         <v>46025</v>
       </c>
-      <c r="G17" s="145" t="n">
+      <c r="G17" s="144" t="n">
         <v>46072</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>2745</v>
       </c>
-      <c r="I17" s="146">
+      <c r="I17" s="145">
         <f>IFERROR(VLOOKUP(B17,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -3223,7 +3200,7 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="O17" s="145" t="n">
+      <c r="O17" s="144" t="n">
         <v>46042</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -3245,7 +3222,7 @@
       <c r="T17" s="9" t="n">
         <v>409790</v>
       </c>
-      <c r="U17" s="144" t="inlineStr">
+      <c r="U17" s="143" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
@@ -3321,16 +3298,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F18" s="144" t="n">
+      <c r="F18" s="143" t="n">
         <v>46029</v>
       </c>
-      <c r="G18" s="145" t="n">
+      <c r="G18" s="144" t="n">
         <v>46113</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>1700</v>
       </c>
-      <c r="I18" s="146">
+      <c r="I18" s="145">
         <f>IFERROR(VLOOKUP(B18,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -3351,10 +3328,10 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>IMB Parts</t>
-        </is>
-      </c>
-      <c r="O18" s="145" t="n">
+          <t>SR-1000 Face Plate(20)+Security Gate(10)</t>
+        </is>
+      </c>
+      <c r="O18" s="144" t="n">
         <v>46056</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -3376,7 +3353,7 @@
       <c r="T18" s="9" t="n">
         <v>250080</v>
       </c>
-      <c r="U18" s="144" t="inlineStr">
+      <c r="U18" s="143" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
@@ -3406,7 +3383,7 @@
         <v/>
       </c>
       <c r="AB18" s="11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AC18" s="10">
         <f>ROUND(AA18/AB18,0)</f>
@@ -3452,16 +3429,16 @@
           <t>부품(렌즈)</t>
         </is>
       </c>
-      <c r="F19" s="144" t="n">
+      <c r="F19" s="143" t="n">
         <v>46035</v>
       </c>
-      <c r="G19" s="145" t="n">
+      <c r="G19" s="144" t="n">
         <v>46134</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>11000</v>
       </c>
-      <c r="I19" s="146" t="n">
+      <c r="I19" s="145" t="n">
         <v>1482.8</v>
       </c>
       <c r="J19" s="9" t="n">
@@ -3481,7 +3458,7 @@
           <t>Lens (2EA)</t>
         </is>
       </c>
-      <c r="O19" s="145" t="n">
+      <c r="O19" s="144" t="n">
         <v>46064</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3503,7 +3480,7 @@
       <c r="T19" s="9" t="n">
         <v>1752040</v>
       </c>
-      <c r="U19" s="144" t="inlineStr">
+      <c r="U19" s="143" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
@@ -3577,16 +3554,16 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F20" s="144" t="n">
+      <c r="F20" s="143" t="n">
         <v>46035</v>
       </c>
-      <c r="G20" s="145" t="n">
+      <c r="G20" s="144" t="n">
         <v>46134</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>286580</v>
       </c>
-      <c r="I20" s="146" t="n">
+      <c r="I20" s="145" t="n">
         <v>1482.8</v>
       </c>
       <c r="J20" s="9" t="n">
@@ -3606,7 +3583,7 @@
           <t>Projector+Lens+ASSY (28EA)</t>
         </is>
       </c>
-      <c r="O20" s="145" t="n">
+      <c r="O20" s="144" t="n">
         <v>46073</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
@@ -3628,7 +3605,7 @@
       <c r="T20" s="9" t="n">
         <v>42329590</v>
       </c>
-      <c r="U20" s="144" t="inlineStr">
+      <c r="U20" s="143" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
@@ -3702,16 +3679,16 @@
           <t>부품</t>
         </is>
       </c>
-      <c r="F21" s="144" t="n">
+      <c r="F21" s="143" t="n">
         <v>46050</v>
       </c>
-      <c r="G21" s="145" t="n">
+      <c r="G21" s="144" t="n">
         <v>46113</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>9740</v>
       </c>
-      <c r="I21" s="146">
+      <c r="I21" s="145">
         <f>IFERROR(VLOOKUP(B21,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -3735,7 +3712,7 @@
           <t>ASSY Liquid Cooling (20EA)</t>
         </is>
       </c>
-      <c r="O21" s="145" t="n">
+      <c r="O21" s="144" t="n">
         <v>46053</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -3757,7 +3734,7 @@
       <c r="T21" s="9" t="n">
         <v>1493440</v>
       </c>
-      <c r="U21" s="144" t="inlineStr">
+      <c r="U21" s="143" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
@@ -3833,10 +3810,10 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F22" s="147" t="n">
+      <c r="F22" s="146" t="n">
         <v>46071</v>
       </c>
-      <c r="G22" s="148" t="inlineStr">
+      <c r="G22" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3844,7 +3821,7 @@
       <c r="H22" s="16" t="n">
         <v>35674</v>
       </c>
-      <c r="I22" s="149">
+      <c r="I22" s="148">
         <f>IFERROR(VLOOKUP(B22,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -3960,10 +3937,10 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F23" s="144" t="n">
+      <c r="F23" s="143" t="n">
         <v>46080</v>
       </c>
-      <c r="G23" s="145" t="inlineStr">
+      <c r="G23" s="144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3971,7 +3948,7 @@
       <c r="H23" s="7" t="n">
         <v>36190</v>
       </c>
-      <c r="I23" s="146">
+      <c r="I23" s="145">
         <f>IFERROR(VLOOKUP(B23,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -3995,7 +3972,7 @@
           <t>SR-1000 IMB (10EA)</t>
         </is>
       </c>
-      <c r="O23" s="145" t="n">
+      <c r="O23" s="144" t="n">
         <v>46095</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -4017,7 +3994,7 @@
       <c r="T23" s="9" t="n">
         <v>5395574</v>
       </c>
-      <c r="U23" s="144" t="inlineStr">
+      <c r="U23" s="143" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
@@ -4093,10 +4070,10 @@
           <t>부품</t>
         </is>
       </c>
-      <c r="F24" s="144" t="n">
+      <c r="F24" s="143" t="n">
         <v>46088</v>
       </c>
-      <c r="G24" s="145" t="inlineStr">
+      <c r="G24" s="144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4104,7 +4081,7 @@
       <c r="H24" s="7" t="n">
         <v>180</v>
       </c>
-      <c r="I24" s="146">
+      <c r="I24" s="145">
         <f>IFERROR(VLOOKUP(B24,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -4125,10 +4102,10 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>TMS Parts</t>
-        </is>
-      </c>
-      <c r="O24" s="145" t="n">
+          <t>SR-1000 Coverplate (3EA)</t>
+        </is>
+      </c>
+      <c r="O24" s="144" t="n">
         <v>46095</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -4150,7 +4127,7 @@
       <c r="T24" s="9" t="n">
         <v>26836</v>
       </c>
-      <c r="U24" s="144" t="inlineStr">
+      <c r="U24" s="143" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
@@ -4180,7 +4157,7 @@
         <v/>
       </c>
       <c r="AB24" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC24" s="10">
         <f>ROUND(AA24/AB24,0)</f>
@@ -4226,10 +4203,10 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F25" s="144" t="n">
+      <c r="F25" s="143" t="n">
         <v>46088</v>
       </c>
-      <c r="G25" s="145" t="inlineStr">
+      <c r="G25" s="144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4237,7 +4214,7 @@
       <c r="H25" s="7" t="n">
         <v>21280</v>
       </c>
-      <c r="I25" s="146">
+      <c r="I25" s="145">
         <f>IFERROR(VLOOKUP(B25,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -4261,7 +4238,7 @@
           <t>IMB</t>
         </is>
       </c>
-      <c r="O25" s="145" t="n">
+      <c r="O25" s="144" t="n">
         <v>46104</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -4283,7 +4260,7 @@
       <c r="T25" s="9" t="n">
         <v>4747530</v>
       </c>
-      <c r="U25" s="144" t="inlineStr">
+      <c r="U25" s="143" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
@@ -4359,10 +4336,10 @@
           <t>부품(Fan)</t>
         </is>
       </c>
-      <c r="F26" s="144" t="n">
+      <c r="F26" s="143" t="n">
         <v>46098</v>
       </c>
-      <c r="G26" s="145" t="inlineStr">
+      <c r="G26" s="144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4370,7 +4347,7 @@
       <c r="H26" s="7" t="n">
         <v>2058</v>
       </c>
-      <c r="I26" s="146">
+      <c r="I26" s="145">
         <f>IFERROR(VLOOKUP(B26,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -4394,7 +4371,7 @@
           <t>Fan (7EA)</t>
         </is>
       </c>
-      <c r="O26" s="145" t="n">
+      <c r="O26" s="144" t="n">
         <v>46105</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4416,7 +4393,7 @@
       <c r="T26" s="9" t="n">
         <v>350480</v>
       </c>
-      <c r="U26" s="144" t="inlineStr">
+      <c r="U26" s="143" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
@@ -4492,10 +4469,10 @@
           <t>부품(Filter)</t>
         </is>
       </c>
-      <c r="F27" s="144" t="n">
+      <c r="F27" s="143" t="n">
         <v>46098</v>
       </c>
-      <c r="G27" s="145" t="inlineStr">
+      <c r="G27" s="144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4503,7 +4480,7 @@
       <c r="H27" s="7" t="n">
         <v>1977</v>
       </c>
-      <c r="I27" s="146">
+      <c r="I27" s="145">
         <f>IFERROR(VLOOKUP(B27,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -4524,10 +4501,10 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Filter+Fan (15EA)</t>
-        </is>
-      </c>
-      <c r="O27" s="145" t="n">
+          <t>Filter(11EA)+Fan(5EA)</t>
+        </is>
+      </c>
+      <c r="O27" s="144" t="n">
         <v>46104</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4549,7 +4526,7 @@
       <c r="T27" s="9" t="n">
         <v>317310</v>
       </c>
-      <c r="U27" s="144" t="inlineStr">
+      <c r="U27" s="143" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
@@ -4579,7 +4556,7 @@
         <v/>
       </c>
       <c r="AB27" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC27" s="10">
         <f>ROUND(AA27/AB27,0)</f>
@@ -4625,14 +4602,14 @@
           <t>부품(렌즈)</t>
         </is>
       </c>
-      <c r="F28" s="144" t="n">
+      <c r="F28" s="143" t="n">
         <v>46106</v>
       </c>
-      <c r="G28" s="145" t="n"/>
+      <c r="G28" s="144" t="n"/>
       <c r="H28" s="7" t="n">
         <v>4290</v>
       </c>
-      <c r="I28" s="146">
+      <c r="I28" s="145">
         <f>IFERROR(VLOOKUP(B28,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -4654,7 +4631,7 @@
           <t>Lens 1.62-2.7 (2EA)</t>
         </is>
       </c>
-      <c r="O28" s="145" t="n">
+      <c r="O28" s="144" t="n">
         <v>46122</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
@@ -4676,7 +4653,7 @@
       <c r="T28" s="9" t="n">
         <v>707830</v>
       </c>
-      <c r="U28" s="144" t="n"/>
+      <c r="U28" s="143" t="n"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
           <t>운서합동</t>
@@ -4740,10 +4717,10 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F29" s="150" t="n">
+      <c r="F29" s="149" t="n">
         <v>46113</v>
       </c>
-      <c r="G29" s="150" t="inlineStr">
+      <c r="G29" s="149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4751,7 +4728,7 @@
       <c r="H29" s="80" t="n">
         <v>78209</v>
       </c>
-      <c r="I29" s="151">
+      <c r="I29" s="150">
         <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -4775,7 +4752,7 @@
           <t>CP4445-RGB Projector 외 (렌탈용)</t>
         </is>
       </c>
-      <c r="O29" s="150" t="n">
+      <c r="O29" s="149" t="n">
         <v>46129</v>
       </c>
       <c r="P29" s="78" t="inlineStr">
@@ -4783,7 +4760,7 @@
           <t>14008-26-101125M</t>
         </is>
       </c>
-      <c r="Q29" s="152">
+      <c r="Q29" s="151">
         <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
         <v/>
       </c>
@@ -4797,7 +4774,7 @@
       <c r="T29" s="82" t="n">
         <v>12073120</v>
       </c>
-      <c r="U29" s="150" t="n"/>
+      <c r="U29" s="149" t="n"/>
       <c r="V29" s="78" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -4861,10 +4838,10 @@
           <t>장비</t>
         </is>
       </c>
-      <c r="F30" s="150" t="n">
+      <c r="F30" s="149" t="n">
         <v>46113</v>
       </c>
-      <c r="G30" s="150" t="inlineStr">
+      <c r="G30" s="149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4872,7 +4849,7 @@
       <c r="H30" s="80" t="n">
         <v>8140</v>
       </c>
-      <c r="I30" s="151">
+      <c r="I30" s="150">
         <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -4896,7 +4873,7 @@
           <t>SMC Chiller HRS-040 외</t>
         </is>
       </c>
-      <c r="O30" s="150" t="n">
+      <c r="O30" s="149" t="n">
         <v>46132</v>
       </c>
       <c r="P30" s="78" t="inlineStr">
@@ -4904,7 +4881,7 @@
           <t>14008-26-101129M</t>
         </is>
       </c>
-      <c r="Q30" s="152">
+      <c r="Q30" s="151">
         <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
         <v/>
       </c>
@@ -4918,7 +4895,7 @@
       <c r="T30" s="82" t="n">
         <v>1376760</v>
       </c>
-      <c r="U30" s="150" t="n"/>
+      <c r="U30" s="149" t="n"/>
       <c r="V30" s="78" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -4982,16 +4959,16 @@
           <t>부품</t>
         </is>
       </c>
-      <c r="F31" s="150" t="n">
+      <c r="F31" s="149" t="n">
         <v>46132</v>
       </c>
-      <c r="G31" s="150" t="n">
+      <c r="G31" s="149" t="n">
         <v>46134</v>
       </c>
       <c r="H31" s="80" t="n">
         <v>4388.4</v>
       </c>
-      <c r="I31" s="151" t="n">
+      <c r="I31" s="150" t="n">
         <v>1741.08</v>
       </c>
       <c r="J31" s="82" t="n">
@@ -5011,7 +4988,7 @@
           <t>AXC 200 ELICENT 60ea (EUR / 재고)</t>
         </is>
       </c>
-      <c r="O31" s="150" t="inlineStr">
+      <c r="O31" s="149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5021,7 +4998,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q31" s="152">
+      <c r="Q31" s="151">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
         <v/>
       </c>
@@ -5035,7 +5012,7 @@
       <c r="T31" s="82" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="150" t="n"/>
+      <c r="U31" s="149" t="n"/>
       <c r="V31" s="78" t="inlineStr">
         <is>
           <t>-</t>
@@ -5097,16 +5074,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F32" s="153" t="n">
+      <c r="F32" s="152" t="n">
         <v>45925</v>
       </c>
-      <c r="G32" s="154" t="n">
+      <c r="G32" s="153" t="n">
         <v>46080</v>
       </c>
       <c r="H32" s="24" t="n">
         <v>5673</v>
       </c>
-      <c r="I32" s="155">
+      <c r="I32" s="154">
         <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -5193,12 +5170,12 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="AE32" s="154" t="inlineStr">
+      <c r="AE32" s="153" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AF32" s="153" t="inlineStr">
+      <c r="AF32" s="152" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -5228,16 +5205,16 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F33" s="153" t="n">
+      <c r="F33" s="152" t="n">
         <v>45982</v>
       </c>
-      <c r="G33" s="154" t="n">
+      <c r="G33" s="153" t="n">
         <v>46020</v>
       </c>
       <c r="H33" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="I33" s="155">
+      <c r="I33" s="154">
         <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -5324,12 +5301,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE33" s="154" t="inlineStr">
+      <c r="AE33" s="153" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AF33" s="153" t="inlineStr">
+      <c r="AF33" s="152" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
@@ -5359,16 +5336,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F34" s="153" t="n">
+      <c r="F34" s="152" t="n">
         <v>45993</v>
       </c>
-      <c r="G34" s="154" t="n">
+      <c r="G34" s="153" t="n">
         <v>46064</v>
       </c>
       <c r="H34" s="24" t="n">
         <v>26358</v>
       </c>
-      <c r="I34" s="155">
+      <c r="I34" s="154">
         <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -5455,12 +5432,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE34" s="154" t="inlineStr">
+      <c r="AE34" s="153" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AF34" s="153" t="inlineStr">
+      <c r="AF34" s="152" t="inlineStr">
         <is>
           <t>2026-12-21</t>
         </is>
@@ -5490,16 +5467,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F35" s="153" t="n">
+      <c r="F35" s="152" t="n">
         <v>46007</v>
       </c>
-      <c r="G35" s="154" t="n">
+      <c r="G35" s="153" t="n">
         <v>46043</v>
       </c>
       <c r="H35" s="24" t="n">
         <v>450</v>
       </c>
-      <c r="I35" s="155">
+      <c r="I35" s="154">
         <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -5586,12 +5563,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE35" s="154" t="inlineStr">
+      <c r="AE35" s="153" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF35" s="153" t="inlineStr">
+      <c r="AF35" s="152" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
@@ -5621,16 +5598,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F36" s="153" t="n">
+      <c r="F36" s="152" t="n">
         <v>46007</v>
       </c>
-      <c r="G36" s="154" t="n">
+      <c r="G36" s="153" t="n">
         <v>46043</v>
       </c>
       <c r="H36" s="24" t="n">
         <v>540</v>
       </c>
-      <c r="I36" s="155">
+      <c r="I36" s="154">
         <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -5717,12 +5694,12 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="AE36" s="154" t="inlineStr">
+      <c r="AE36" s="153" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AF36" s="153" t="inlineStr">
+      <c r="AF36" s="152" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
@@ -5752,16 +5729,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F37" s="153" t="n">
+      <c r="F37" s="152" t="n">
         <v>46010</v>
       </c>
-      <c r="G37" s="154" t="n">
+      <c r="G37" s="153" t="n">
         <v>46080</v>
       </c>
       <c r="H37" s="24" t="n">
         <v>136516</v>
       </c>
-      <c r="I37" s="155">
+      <c r="I37" s="154">
         <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -5848,12 +5825,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE37" s="154" t="inlineStr">
+      <c r="AE37" s="153" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF37" s="153" t="inlineStr">
+      <c r="AF37" s="152" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
@@ -5883,10 +5860,10 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F38" s="153" t="n">
+      <c r="F38" s="152" t="n">
         <v>46015</v>
       </c>
-      <c r="G38" s="154" t="inlineStr">
+      <c r="G38" s="153" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5894,7 +5871,7 @@
       <c r="H38" s="24" t="n">
         <v>76054</v>
       </c>
-      <c r="I38" s="155">
+      <c r="I38" s="154">
         <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -5981,12 +5958,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE38" s="154" t="inlineStr">
+      <c r="AE38" s="153" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF38" s="153" t="inlineStr">
+      <c r="AF38" s="152" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
@@ -6016,16 +5993,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F39" s="153" t="n">
+      <c r="F39" s="152" t="n">
         <v>46029</v>
       </c>
-      <c r="G39" s="154" t="n">
+      <c r="G39" s="153" t="n">
         <v>46072</v>
       </c>
       <c r="H39" s="24" t="n">
         <v>14793</v>
       </c>
-      <c r="I39" s="155">
+      <c r="I39" s="154">
         <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -6112,12 +6089,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE39" s="154" t="inlineStr">
+      <c r="AE39" s="153" t="inlineStr">
         <is>
           <t>2026-01-30</t>
         </is>
       </c>
-      <c r="AF39" s="153" t="inlineStr">
+      <c r="AF39" s="152" t="inlineStr">
         <is>
           <t>2027-01-29</t>
         </is>
@@ -6147,10 +6124,10 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F40" s="153" t="n">
+      <c r="F40" s="152" t="n">
         <v>46029</v>
       </c>
-      <c r="G40" s="154" t="inlineStr">
+      <c r="G40" s="153" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6158,7 +6135,7 @@
       <c r="H40" s="24" t="n">
         <v>26656</v>
       </c>
-      <c r="I40" s="155">
+      <c r="I40" s="154">
         <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -6245,12 +6222,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE40" s="154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF40" s="153" t="inlineStr">
+      <c r="AE40" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF40" s="152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6280,16 +6257,16 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F41" s="153" t="n">
+      <c r="F41" s="152" t="n">
         <v>46042</v>
       </c>
-      <c r="G41" s="154" t="n">
+      <c r="G41" s="153" t="n">
         <v>46057</v>
       </c>
       <c r="H41" s="24" t="n">
         <v>1440</v>
       </c>
-      <c r="I41" s="155">
+      <c r="I41" s="154">
         <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -6376,12 +6353,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE41" s="154" t="inlineStr">
+      <c r="AE41" s="153" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF41" s="153" t="inlineStr">
+      <c r="AF41" s="152" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
@@ -6411,16 +6388,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F42" s="153" t="n">
+      <c r="F42" s="152" t="n">
         <v>46042</v>
       </c>
-      <c r="G42" s="154" t="n">
+      <c r="G42" s="153" t="n">
         <v>46057</v>
       </c>
       <c r="H42" s="24" t="n">
         <v>4489</v>
       </c>
-      <c r="I42" s="155">
+      <c r="I42" s="154">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -6507,12 +6484,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE42" s="154" t="inlineStr">
+      <c r="AE42" s="153" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF42" s="153" t="inlineStr">
+      <c r="AF42" s="152" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
@@ -6542,16 +6519,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F43" s="153" t="n">
+      <c r="F43" s="152" t="n">
         <v>46042</v>
       </c>
-      <c r="G43" s="154" t="n">
+      <c r="G43" s="153" t="n">
         <v>46057</v>
       </c>
       <c r="H43" s="24" t="n">
         <v>5670.57</v>
       </c>
-      <c r="I43" s="155">
+      <c r="I43" s="154">
         <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -6638,12 +6615,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE43" s="154" t="inlineStr">
+      <c r="AE43" s="153" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF43" s="153" t="inlineStr">
+      <c r="AF43" s="152" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
@@ -6673,16 +6650,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F44" s="153" t="n">
+      <c r="F44" s="152" t="n">
         <v>46057</v>
       </c>
-      <c r="G44" s="154" t="n">
+      <c r="G44" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H44" s="24" t="n">
         <v>24614</v>
       </c>
-      <c r="I44" s="155">
+      <c r="I44" s="154">
         <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -6769,12 +6746,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE44" s="154" t="inlineStr">
+      <c r="AE44" s="153" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AF44" s="153" t="inlineStr">
+      <c r="AF44" s="152" t="inlineStr">
         <is>
           <t>2027-02-28</t>
         </is>
@@ -6804,16 +6781,16 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F45" s="153" t="n">
+      <c r="F45" s="152" t="n">
         <v>46060</v>
       </c>
-      <c r="G45" s="154" t="n">
+      <c r="G45" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H45" s="24" t="n">
         <v>3993.05</v>
       </c>
-      <c r="I45" s="155">
+      <c r="I45" s="154">
         <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -6900,12 +6877,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE45" s="154" t="inlineStr">
+      <c r="AE45" s="153" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF45" s="153" t="inlineStr">
+      <c r="AF45" s="152" t="inlineStr">
         <is>
           <t>2027-02-22</t>
         </is>
@@ -6935,16 +6912,16 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F46" s="153" t="n">
+      <c r="F46" s="152" t="n">
         <v>46080</v>
       </c>
-      <c r="G46" s="154" t="n">
+      <c r="G46" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H46" s="24" t="n">
         <v>360</v>
       </c>
-      <c r="I46" s="155">
+      <c r="I46" s="154">
         <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -7031,12 +7008,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE46" s="154" t="inlineStr">
+      <c r="AE46" s="153" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AF46" s="153" t="inlineStr">
+      <c r="AF46" s="152" t="inlineStr">
         <is>
           <t>2027-02-28</t>
         </is>
@@ -7066,16 +7043,16 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F47" s="153" t="n">
+      <c r="F47" s="152" t="n">
         <v>46088</v>
       </c>
-      <c r="G47" s="154" t="n">
+      <c r="G47" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H47" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="I47" s="155">
+      <c r="I47" s="154">
         <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -7162,12 +7139,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE47" s="154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF47" s="153" t="inlineStr">
+      <c r="AE47" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF47" s="152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7197,10 +7174,10 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F48" s="153" t="n">
+      <c r="F48" s="152" t="n">
         <v>46109</v>
       </c>
-      <c r="G48" s="154" t="inlineStr">
+      <c r="G48" s="153" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7208,7 +7185,7 @@
       <c r="H48" s="24" t="n">
         <v>17404</v>
       </c>
-      <c r="I48" s="155">
+      <c r="I48" s="154">
         <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -7295,12 +7272,12 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE48" s="154" t="inlineStr">
+      <c r="AE48" s="153" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF48" s="153" t="inlineStr">
+      <c r="AF48" s="152" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
@@ -7330,10 +7307,10 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F49" s="156" t="n">
+      <c r="F49" s="155" t="n">
         <v>46136</v>
       </c>
-      <c r="G49" s="156" t="inlineStr">
+      <c r="G49" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7341,7 +7318,7 @@
       <c r="H49" s="87" t="n">
         <v>15289</v>
       </c>
-      <c r="I49" s="157">
+      <c r="I49" s="156">
         <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -7365,7 +7342,7 @@
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O49" s="156" t="inlineStr">
+      <c r="O49" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7375,7 +7352,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q49" s="158">
+      <c r="Q49" s="157">
         <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE()),""))</f>
         <v/>
       </c>
@@ -7389,7 +7366,7 @@
       <c r="T49" s="89" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="156" t="n"/>
+      <c r="U49" s="155" t="n"/>
       <c r="V49" s="85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7426,8 +7403,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE49" s="156" t="n"/>
-      <c r="AF49" s="156" t="n"/>
+      <c r="AE49" s="155" t="n"/>
+      <c r="AF49" s="155" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="85" t="n">
@@ -7453,10 +7430,10 @@
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F50" s="156" t="n">
+      <c r="F50" s="155" t="n">
         <v>46133</v>
       </c>
-      <c r="G50" s="156" t="inlineStr">
+      <c r="G50" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7464,7 +7441,7 @@
       <c r="H50" s="87" t="n">
         <v>2550</v>
       </c>
-      <c r="I50" s="157">
+      <c r="I50" s="156">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -7488,7 +7465,7 @@
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O50" s="156" t="inlineStr">
+      <c r="O50" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7498,7 +7475,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q50" s="158">
+      <c r="Q50" s="157">
         <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE()),""))</f>
         <v/>
       </c>
@@ -7512,7 +7489,7 @@
       <c r="T50" s="89" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="156" t="n"/>
+      <c r="U50" s="155" t="n"/>
       <c r="V50" s="85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7549,8 +7526,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE50" s="156" t="n"/>
-      <c r="AF50" s="156" t="n"/>
+      <c r="AE50" s="155" t="n"/>
+      <c r="AF50" s="155" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="12" t="n">
@@ -7576,10 +7553,10 @@
           <t>Inspection</t>
         </is>
       </c>
-      <c r="F51" s="147" t="n">
+      <c r="F51" s="146" t="n">
         <v>46037</v>
       </c>
-      <c r="G51" s="148" t="inlineStr">
+      <c r="G51" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7587,7 +7564,7 @@
       <c r="H51" s="16" t="n">
         <v>4180</v>
       </c>
-      <c r="I51" s="149">
+      <c r="I51" s="148">
         <f>IFERROR(VLOOKUP(B46,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -7674,12 +7651,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE51" s="148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF51" s="147" t="inlineStr">
+      <c r="AE51" s="147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF51" s="146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7709,12 +7686,12 @@
           <t>수리반환</t>
         </is>
       </c>
-      <c r="F52" s="147" t="n"/>
-      <c r="G52" s="148" t="n"/>
+      <c r="F52" s="146" t="n"/>
+      <c r="G52" s="147" t="n"/>
       <c r="H52" s="16" t="n">
         <v>400</v>
       </c>
-      <c r="I52" s="149">
+      <c r="I52" s="148">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
@@ -7797,8 +7774,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE52" s="148" t="n"/>
-      <c r="AF52" s="147" t="n"/>
+      <c r="AE52" s="147" t="n"/>
+      <c r="AF52" s="146" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="39" t="n"/>
@@ -7835,17 +7812,17 @@
       <c r="AF53" s="39" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="120" t="inlineStr">
+      <c r="A54" s="125" t="inlineStr">
         <is>
           <t>장비/부품 합계</t>
         </is>
       </c>
-      <c r="B54" s="121" t="n"/>
-      <c r="C54" s="121" t="n"/>
-      <c r="D54" s="121" t="n"/>
-      <c r="E54" s="121" t="n"/>
-      <c r="F54" s="121" t="n"/>
-      <c r="G54" s="122" t="n"/>
+      <c r="B54" s="126" t="n"/>
+      <c r="C54" s="126" t="n"/>
+      <c r="D54" s="126" t="n"/>
+      <c r="E54" s="126" t="n"/>
+      <c r="F54" s="126" t="n"/>
+      <c r="G54" s="127" t="n"/>
       <c r="H54" s="91">
         <f>SUBTOTAL(9,H5:H31)</f>
         <v/>
@@ -7906,17 +7883,17 @@
       <c r="AF54" s="92" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="120" t="inlineStr">
+      <c r="A55" s="125" t="inlineStr">
         <is>
           <t>라이센스/워런티 합계</t>
         </is>
       </c>
-      <c r="B55" s="121" t="n"/>
-      <c r="C55" s="121" t="n"/>
-      <c r="D55" s="121" t="n"/>
-      <c r="E55" s="121" t="n"/>
-      <c r="F55" s="121" t="n"/>
-      <c r="G55" s="122" t="n"/>
+      <c r="B55" s="126" t="n"/>
+      <c r="C55" s="126" t="n"/>
+      <c r="D55" s="126" t="n"/>
+      <c r="E55" s="126" t="n"/>
+      <c r="F55" s="126" t="n"/>
+      <c r="G55" s="127" t="n"/>
       <c r="H55" s="91">
         <f>SUBTOTAL(9,H32:H50)</f>
         <v/>
@@ -7977,17 +7954,17 @@
       <c r="AF55" s="92" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="120" t="inlineStr">
+      <c r="A56" s="125" t="inlineStr">
         <is>
           <t>기타 합계</t>
         </is>
       </c>
-      <c r="B56" s="121" t="n"/>
-      <c r="C56" s="121" t="n"/>
-      <c r="D56" s="121" t="n"/>
-      <c r="E56" s="121" t="n"/>
-      <c r="F56" s="121" t="n"/>
-      <c r="G56" s="122" t="n"/>
+      <c r="B56" s="126" t="n"/>
+      <c r="C56" s="126" t="n"/>
+      <c r="D56" s="126" t="n"/>
+      <c r="E56" s="126" t="n"/>
+      <c r="F56" s="126" t="n"/>
+      <c r="G56" s="127" t="n"/>
       <c r="H56" s="91">
         <f>H51+H52</f>
         <v/>
@@ -8048,17 +8025,17 @@
       <c r="AF56" s="92" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="124" t="inlineStr">
+      <c r="A57" s="129" t="inlineStr">
         <is>
           <t>총 합계</t>
         </is>
       </c>
-      <c r="B57" s="121" t="n"/>
-      <c r="C57" s="121" t="n"/>
-      <c r="D57" s="121" t="n"/>
-      <c r="E57" s="121" t="n"/>
-      <c r="F57" s="121" t="n"/>
-      <c r="G57" s="122" t="n"/>
+      <c r="B57" s="126" t="n"/>
+      <c r="C57" s="126" t="n"/>
+      <c r="D57" s="126" t="n"/>
+      <c r="E57" s="126" t="n"/>
+      <c r="F57" s="126" t="n"/>
+      <c r="G57" s="127" t="n"/>
       <c r="H57" s="94">
         <f>SUBTOTAL(9,H5:H52)</f>
         <v/>
@@ -8321,95 +8298,95 @@
   <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
-    <col width="5" customWidth="1" style="130" min="1" max="1"/>
-    <col width="12" customWidth="1" style="130" min="2" max="2"/>
+    <col width="5" customWidth="1" style="135" min="1" max="1"/>
+    <col width="12" customWidth="1" style="135" min="2" max="2"/>
     <col width="9" customWidth="1" style="73" min="3" max="3"/>
     <col width="12" customWidth="1" style="73" min="4" max="4"/>
-    <col width="14" customWidth="1" style="130" min="5" max="5"/>
+    <col width="14" customWidth="1" style="135" min="5" max="5"/>
     <col width="28" customWidth="1" style="73" min="6" max="6"/>
     <col width="12.5" customWidth="1" style="73" min="7" max="10"/>
     <col width="10.6640625" customWidth="1" style="73" min="11" max="11"/>
-    <col width="8.6640625" customWidth="1" style="130" min="12" max="14"/>
-    <col width="8.6640625" customWidth="1" style="130" min="15" max="16384"/>
+    <col width="8.6640625" customWidth="1" style="135" min="12" max="15"/>
+    <col width="8.6640625" customWidth="1" style="135" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="123" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>라이센스 / 워런티 계약 현황</t>
         </is>
       </c>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="118" t="n"/>
-      <c r="K1" s="119" t="n"/>
-      <c r="L1" s="163" t="n"/>
-      <c r="M1" s="163" t="n"/>
+      <c r="B1" s="123" t="n"/>
+      <c r="C1" s="123" t="n"/>
+      <c r="D1" s="123" t="n"/>
+      <c r="E1" s="123" t="n"/>
+      <c r="F1" s="123" t="n"/>
+      <c r="G1" s="123" t="n"/>
+      <c r="H1" s="123" t="n"/>
+      <c r="I1" s="123" t="n"/>
+      <c r="J1" s="123" t="n"/>
+      <c r="K1" s="124" t="n"/>
+      <c r="L1" s="119" t="n"/>
+      <c r="M1" s="119" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="122" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="117" t="inlineStr">
+      <c r="B2" s="122" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="C2" s="117" t="inlineStr">
+      <c r="C2" s="122" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D2" s="117" t="inlineStr">
+      <c r="D2" s="122" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="E2" s="117" t="inlineStr">
+      <c r="E2" s="122" t="inlineStr">
         <is>
           <t>Invoice(USD)</t>
         </is>
       </c>
-      <c r="F2" s="117" t="inlineStr">
+      <c r="F2" s="122" t="inlineStr">
         <is>
           <t>품명</t>
         </is>
       </c>
-      <c r="G2" s="117" t="inlineStr">
+      <c r="G2" s="122" t="inlineStr">
         <is>
           <t>PO일자</t>
         </is>
       </c>
-      <c r="H2" s="117" t="inlineStr">
+      <c r="H2" s="122" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
       </c>
-      <c r="I2" s="117" t="inlineStr">
+      <c r="I2" s="122" t="inlineStr">
         <is>
           <t>계약시작</t>
         </is>
       </c>
-      <c r="J2" s="117" t="inlineStr">
+      <c r="J2" s="122" t="inlineStr">
         <is>
           <t>계약종료</t>
         </is>
       </c>
-      <c r="K2" s="117" t="inlineStr">
+      <c r="K2" s="122" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="L2" s="164" t="n"/>
-      <c r="M2" s="164" t="n"/>
+      <c r="L2" s="120" t="n"/>
+      <c r="M2" s="120" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="20" t="n">
@@ -8438,16 +8415,16 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="G3" s="154" t="n">
+      <c r="G3" s="153" t="n">
         <v>45925</v>
       </c>
-      <c r="H3" s="154" t="n">
+      <c r="H3" s="153" t="n">
         <v>46080</v>
       </c>
-      <c r="I3" s="154" t="n">
+      <c r="I3" s="153" t="n">
         <v>45913</v>
       </c>
-      <c r="J3" s="154" t="n">
+      <c r="J3" s="153" t="n">
         <v>46262</v>
       </c>
       <c r="K3" s="20" t="inlineStr">
@@ -8455,8 +8432,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L3" s="165" t="n"/>
-      <c r="M3" s="165" t="n"/>
+      <c r="L3" s="121" t="n"/>
+      <c r="M3" s="121" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="20" t="n">
@@ -8485,16 +8462,16 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="G4" s="154" t="n">
+      <c r="G4" s="153" t="n">
         <v>45982</v>
       </c>
-      <c r="H4" s="154" t="n">
+      <c r="H4" s="153" t="n">
         <v>46014</v>
       </c>
-      <c r="I4" s="154" t="n">
+      <c r="I4" s="153" t="n">
         <v>45992</v>
       </c>
-      <c r="J4" s="154" t="n">
+      <c r="J4" s="153" t="n">
         <v>46356</v>
       </c>
       <c r="K4" s="20" t="inlineStr">
@@ -8502,8 +8479,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L4" s="165" t="n"/>
-      <c r="M4" s="165" t="n"/>
+      <c r="L4" s="121" t="n"/>
+      <c r="M4" s="121" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="20" t="n">
@@ -8532,16 +8509,16 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="G5" s="154" t="n">
+      <c r="G5" s="153" t="n">
         <v>45993</v>
       </c>
-      <c r="H5" s="154" t="n">
+      <c r="H5" s="153" t="n">
         <v>46064</v>
       </c>
-      <c r="I5" s="154" t="n">
+      <c r="I5" s="153" t="n">
         <v>46013</v>
       </c>
-      <c r="J5" s="154" t="n">
+      <c r="J5" s="153" t="n">
         <v>46377</v>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -8549,8 +8526,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L5" s="165" t="n"/>
-      <c r="M5" s="165" t="n"/>
+      <c r="L5" s="121" t="n"/>
+      <c r="M5" s="121" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="20" t="n">
@@ -8579,16 +8556,16 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="G6" s="154" t="n">
+      <c r="G6" s="153" t="n">
         <v>46007</v>
       </c>
-      <c r="H6" s="154" t="n">
+      <c r="H6" s="153" t="n">
         <v>46043</v>
       </c>
-      <c r="I6" s="154" t="n">
+      <c r="I6" s="153" t="n">
         <v>46023</v>
       </c>
-      <c r="J6" s="154" t="n">
+      <c r="J6" s="153" t="n">
         <v>46387</v>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -8596,8 +8573,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L6" s="165" t="n"/>
-      <c r="M6" s="165" t="n"/>
+      <c r="L6" s="121" t="n"/>
+      <c r="M6" s="121" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="20" t="n">
@@ -8626,16 +8603,16 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="G7" s="154" t="n">
+      <c r="G7" s="153" t="n">
         <v>46007</v>
       </c>
-      <c r="H7" s="154" t="n">
+      <c r="H7" s="153" t="n">
         <v>46043</v>
       </c>
-      <c r="I7" s="154" t="n">
+      <c r="I7" s="153" t="n">
         <v>45962</v>
       </c>
-      <c r="J7" s="154" t="n">
+      <c r="J7" s="153" t="n">
         <v>46325</v>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -8643,8 +8620,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L7" s="165" t="n"/>
-      <c r="M7" s="165" t="n"/>
+      <c r="L7" s="121" t="n"/>
+      <c r="M7" s="121" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="20" t="n">
@@ -8673,16 +8650,16 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="G8" s="154" t="n">
+      <c r="G8" s="153" t="n">
         <v>46010</v>
       </c>
-      <c r="H8" s="154" t="n">
+      <c r="H8" s="153" t="n">
         <v>46080</v>
       </c>
-      <c r="I8" s="154" t="n">
+      <c r="I8" s="153" t="n">
         <v>46023</v>
       </c>
-      <c r="J8" s="154" t="n">
+      <c r="J8" s="153" t="n">
         <v>46387</v>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -8690,8 +8667,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L8" s="165" t="n"/>
-      <c r="M8" s="165" t="n"/>
+      <c r="L8" s="121" t="n"/>
+      <c r="M8" s="121" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="20" t="n">
@@ -8720,7 +8697,7 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="G9" s="154" t="n">
+      <c r="G9" s="153" t="n">
         <v>46015</v>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -8728,10 +8705,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="154" t="n">
+      <c r="I9" s="153" t="n">
         <v>46023</v>
       </c>
-      <c r="J9" s="154" t="n">
+      <c r="J9" s="153" t="n">
         <v>46387</v>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -8739,8 +8716,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L9" s="165" t="n"/>
-      <c r="M9" s="165" t="n"/>
+      <c r="L9" s="121" t="n"/>
+      <c r="M9" s="121" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="20" t="n">
@@ -8769,16 +8746,16 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="G10" s="154" t="n">
+      <c r="G10" s="153" t="n">
         <v>46029</v>
       </c>
-      <c r="H10" s="154" t="n">
+      <c r="H10" s="153" t="n">
         <v>46072</v>
       </c>
-      <c r="I10" s="154" t="n">
+      <c r="I10" s="153" t="n">
         <v>46052</v>
       </c>
-      <c r="J10" s="154" t="n">
+      <c r="J10" s="153" t="n">
         <v>46416</v>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -8786,8 +8763,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L10" s="165" t="n"/>
-      <c r="M10" s="165" t="n"/>
+      <c r="L10" s="121" t="n"/>
+      <c r="M10" s="121" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="20" t="n">
@@ -8816,7 +8793,7 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="G11" s="154" t="n">
+      <c r="G11" s="153" t="n">
         <v>46029</v>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -8839,8 +8816,8 @@
           <t>홀딩</t>
         </is>
       </c>
-      <c r="L11" s="165" t="n"/>
-      <c r="M11" s="165" t="n"/>
+      <c r="L11" s="121" t="n"/>
+      <c r="M11" s="121" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="20" t="n">
@@ -8869,16 +8846,16 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="G12" s="154" t="n">
+      <c r="G12" s="153" t="n">
         <v>46042</v>
       </c>
-      <c r="H12" s="154" t="n">
+      <c r="H12" s="153" t="n">
         <v>46057</v>
       </c>
-      <c r="I12" s="154" t="n">
+      <c r="I12" s="153" t="n">
         <v>46023</v>
       </c>
-      <c r="J12" s="154" t="n">
+      <c r="J12" s="153" t="n">
         <v>46387</v>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -8886,8 +8863,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L12" s="165" t="n"/>
-      <c r="M12" s="165" t="n"/>
+      <c r="L12" s="121" t="n"/>
+      <c r="M12" s="121" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="20" t="n">
@@ -8916,16 +8893,16 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="G13" s="154" t="n">
+      <c r="G13" s="153" t="n">
         <v>46042</v>
       </c>
-      <c r="H13" s="154" t="n">
+      <c r="H13" s="153" t="n">
         <v>46057</v>
       </c>
-      <c r="I13" s="154" t="n">
+      <c r="I13" s="153" t="n">
         <v>46023</v>
       </c>
-      <c r="J13" s="154" t="n">
+      <c r="J13" s="153" t="n">
         <v>46387</v>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -8933,8 +8910,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L13" s="165" t="n"/>
-      <c r="M13" s="165" t="n"/>
+      <c r="L13" s="121" t="n"/>
+      <c r="M13" s="121" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="20" t="n">
@@ -8963,16 +8940,16 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="G14" s="154" t="n">
+      <c r="G14" s="153" t="n">
         <v>46042</v>
       </c>
-      <c r="H14" s="154" t="n">
+      <c r="H14" s="153" t="n">
         <v>46057</v>
       </c>
-      <c r="I14" s="154" t="n">
+      <c r="I14" s="153" t="n">
         <v>46023</v>
       </c>
-      <c r="J14" s="154" t="n">
+      <c r="J14" s="153" t="n">
         <v>46387</v>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -8980,8 +8957,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L14" s="165" t="n"/>
-      <c r="M14" s="165" t="n"/>
+      <c r="L14" s="121" t="n"/>
+      <c r="M14" s="121" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="20" t="n">
@@ -9010,16 +8987,16 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="G15" s="154" t="n">
+      <c r="G15" s="153" t="n">
         <v>46057</v>
       </c>
-      <c r="H15" s="154" t="n">
+      <c r="H15" s="153" t="n">
         <v>46113</v>
       </c>
-      <c r="I15" s="154" t="n">
+      <c r="I15" s="153" t="n">
         <v>46082</v>
       </c>
-      <c r="J15" s="166" t="n">
+      <c r="J15" s="158" t="n">
         <v>46446</v>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -9027,8 +9004,8 @@
           <t>홀딩</t>
         </is>
       </c>
-      <c r="L15" s="165" t="n"/>
-      <c r="M15" s="165" t="n"/>
+      <c r="L15" s="121" t="n"/>
+      <c r="M15" s="121" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="20" t="n">
@@ -9057,16 +9034,16 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="G16" s="154" t="n">
+      <c r="G16" s="153" t="n">
         <v>46060</v>
       </c>
-      <c r="H16" s="154" t="n">
+      <c r="H16" s="153" t="n">
         <v>46113</v>
       </c>
-      <c r="I16" s="154" t="n">
+      <c r="I16" s="153" t="n">
         <v>46023</v>
       </c>
-      <c r="J16" s="166" t="n">
+      <c r="J16" s="158" t="n">
         <v>46440</v>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -9074,8 +9051,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L16" s="165" t="n"/>
-      <c r="M16" s="165" t="n"/>
+      <c r="L16" s="121" t="n"/>
+      <c r="M16" s="121" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="20" t="n">
@@ -9104,16 +9081,16 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="G17" s="154" t="n">
+      <c r="G17" s="153" t="n">
         <v>46080</v>
       </c>
-      <c r="H17" s="154" t="n">
+      <c r="H17" s="153" t="n">
         <v>46113</v>
       </c>
-      <c r="I17" s="154" t="n">
+      <c r="I17" s="153" t="n">
         <v>46082</v>
       </c>
-      <c r="J17" s="166" t="n">
+      <c r="J17" s="158" t="n">
         <v>46446</v>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -9121,8 +9098,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L17" s="165" t="n"/>
-      <c r="M17" s="165" t="n"/>
+      <c r="L17" s="121" t="n"/>
+      <c r="M17" s="121" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="77" t="n">
@@ -9151,10 +9128,10 @@
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="G18" s="166" t="n">
+      <c r="G18" s="158" t="n">
         <v>46088</v>
       </c>
-      <c r="H18" s="166" t="n">
+      <c r="H18" s="158" t="n">
         <v>46113</v>
       </c>
       <c r="I18" s="77" t="inlineStr">
@@ -9172,8 +9149,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L18" s="165" t="n"/>
-      <c r="M18" s="165" t="n"/>
+      <c r="L18" s="121" t="n"/>
+      <c r="M18" s="121" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="20" t="n">
@@ -9202,7 +9179,7 @@
           <t>EW (CGV 동백 외 Warranty Extension)</t>
         </is>
       </c>
-      <c r="G19" s="154" t="n">
+      <c r="G19" s="153" t="n">
         <v>46109</v>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -9210,10 +9187,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="154" t="n">
+      <c r="I19" s="153" t="n">
         <v>46113</v>
       </c>
-      <c r="J19" s="166" t="n">
+      <c r="J19" s="158" t="n">
         <v>46477</v>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -9221,8 +9198,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L19" s="165" t="n"/>
-      <c r="M19" s="165" t="n"/>
+      <c r="L19" s="121" t="n"/>
+      <c r="M19" s="121" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="109" t="n">
@@ -9251,18 +9228,18 @@
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대</t>
         </is>
       </c>
-      <c r="G20" s="167" t="n">
+      <c r="G20" s="159" t="n">
         <v>46136</v>
       </c>
-      <c r="H20" s="167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="167" t="n">
+      <c r="H20" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="159" t="n">
         <v>46168</v>
       </c>
-      <c r="J20" s="167" t="n">
+      <c r="J20" s="159" t="n">
         <v>46532</v>
       </c>
       <c r="K20" s="109" t="inlineStr">
@@ -9270,8 +9247,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L20" s="165" t="n"/>
-      <c r="M20" s="165" t="n"/>
+      <c r="L20" s="121" t="n"/>
+      <c r="M20" s="121" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="109" t="n">
@@ -9300,18 +9277,18 @@
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="G21" s="167" t="n">
+      <c r="G21" s="159" t="n">
         <v>46133</v>
       </c>
-      <c r="H21" s="167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="167" t="n">
+      <c r="H21" s="159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="159" t="n">
         <v>46142</v>
       </c>
-      <c r="J21" s="167" t="n">
+      <c r="J21" s="159" t="n">
         <v>46872</v>
       </c>
       <c r="K21" s="109" t="inlineStr">
@@ -9319,8 +9296,8 @@
           <t>라이센스</t>
         </is>
       </c>
-      <c r="L21" s="165" t="n"/>
-      <c r="M21" s="165" t="n"/>
+      <c r="L21" s="121" t="n"/>
+      <c r="M21" s="121" t="n"/>
     </row>
     <row r="70">
       <c r="M70" s="40" t="n"/>
@@ -9343,112 +9320,112 @@
   <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
-    <col width="22" customWidth="1" style="130" min="1" max="1"/>
-    <col width="12" customWidth="1" style="130" min="2" max="2"/>
-    <col width="14" customWidth="1" style="130" min="3" max="3"/>
-    <col width="8" customWidth="1" style="130" min="4" max="4"/>
+    <col width="22" customWidth="1" style="135" min="1" max="1"/>
+    <col width="12" customWidth="1" style="135" min="2" max="2"/>
+    <col width="14" customWidth="1" style="135" min="3" max="3"/>
+    <col width="8" customWidth="1" style="135" min="4" max="4"/>
     <col width="12.33203125" customWidth="1" style="73" min="5" max="5"/>
-    <col width="14" customWidth="1" style="130" min="6" max="6"/>
+    <col width="14" customWidth="1" style="135" min="6" max="6"/>
     <col width="10.1640625" customWidth="1" style="73" min="7" max="7"/>
-    <col width="14" customWidth="1" style="130" min="8" max="8"/>
+    <col width="14" customWidth="1" style="135" min="8" max="8"/>
     <col width="10.1640625" customWidth="1" style="73" min="9" max="9"/>
     <col width="20" customWidth="1" style="73" min="10" max="10"/>
-    <col width="8.6640625" customWidth="1" style="130" min="11" max="13"/>
-    <col width="8.6640625" customWidth="1" style="130" min="14" max="16384"/>
+    <col width="8.6640625" customWidth="1" style="135" min="11" max="14"/>
+    <col width="8.6640625" customWidth="1" style="135" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="123" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>합배송 비용안분 상세</t>
         </is>
       </c>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="119" t="n"/>
-      <c r="K1" s="163" t="n"/>
-      <c r="L1" s="163" t="n"/>
-      <c r="M1" s="163" t="n"/>
+      <c r="B1" s="123" t="n"/>
+      <c r="C1" s="123" t="n"/>
+      <c r="D1" s="123" t="n"/>
+      <c r="E1" s="123" t="n"/>
+      <c r="F1" s="123" t="n"/>
+      <c r="G1" s="123" t="n"/>
+      <c r="H1" s="123" t="n"/>
+      <c r="I1" s="123" t="n"/>
+      <c r="J1" s="124" t="n"/>
+      <c r="K1" s="119" t="n"/>
+      <c r="L1" s="119" t="n"/>
+      <c r="M1" s="119" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="127" t="inlineStr">
+      <c r="A2" s="132" t="inlineStr">
         <is>
           <t>수입신고번호별 PO 그룹핑 및 비용 배분  |  오렌지 = 합배송  |  녹색 = 단독</t>
         </is>
       </c>
-      <c r="B2" s="118" t="n"/>
-      <c r="C2" s="118" t="n"/>
-      <c r="D2" s="118" t="n"/>
-      <c r="E2" s="118" t="n"/>
-      <c r="F2" s="118" t="n"/>
-      <c r="G2" s="118" t="n"/>
-      <c r="H2" s="118" t="n"/>
-      <c r="I2" s="118" t="n"/>
-      <c r="J2" s="119" t="n"/>
-      <c r="K2" s="164" t="n"/>
-      <c r="L2" s="164" t="n"/>
-      <c r="M2" s="164" t="n"/>
+      <c r="B2" s="123" t="n"/>
+      <c r="C2" s="123" t="n"/>
+      <c r="D2" s="123" t="n"/>
+      <c r="E2" s="123" t="n"/>
+      <c r="F2" s="123" t="n"/>
+      <c r="G2" s="123" t="n"/>
+      <c r="H2" s="123" t="n"/>
+      <c r="I2" s="123" t="n"/>
+      <c r="J2" s="124" t="n"/>
+      <c r="K2" s="120" t="n"/>
+      <c r="L2" s="120" t="n"/>
+      <c r="M2" s="120" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="117" t="inlineStr">
+      <c r="A3" s="122" t="inlineStr">
         <is>
           <t>수입신고번호</t>
         </is>
       </c>
-      <c r="B3" s="117" t="inlineStr">
+      <c r="B3" s="122" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="C3" s="117" t="inlineStr">
+      <c r="C3" s="122" t="inlineStr">
         <is>
           <t>Invoice(USD)</t>
         </is>
       </c>
-      <c r="D3" s="117" t="inlineStr">
+      <c r="D3" s="122" t="inlineStr">
         <is>
           <t>비율(%)</t>
         </is>
       </c>
-      <c r="E3" s="117" t="inlineStr">
+      <c r="E3" s="122" t="inlineStr">
         <is>
           <t>관세사</t>
         </is>
       </c>
-      <c r="F3" s="117" t="inlineStr">
+      <c r="F3" s="122" t="inlineStr">
         <is>
           <t>관세사비(배분)</t>
         </is>
       </c>
-      <c r="G3" s="117" t="inlineStr">
+      <c r="G3" s="122" t="inlineStr">
         <is>
           <t>운송사</t>
         </is>
       </c>
-      <c r="H3" s="117" t="inlineStr">
+      <c r="H3" s="122" t="inlineStr">
         <is>
           <t>운송료(배분)</t>
         </is>
       </c>
-      <c r="I3" s="117" t="inlineStr">
+      <c r="I3" s="122" t="inlineStr">
         <is>
           <t>합배송여부</t>
         </is>
       </c>
-      <c r="J3" s="117" t="inlineStr">
+      <c r="J3" s="122" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="K3" s="165" t="n"/>
-      <c r="L3" s="165" t="n"/>
-      <c r="M3" s="165" t="n"/>
+      <c r="K3" s="121" t="n"/>
+      <c r="L3" s="121" t="n"/>
+      <c r="M3" s="121" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="28" t="inlineStr">
@@ -9464,7 +9441,7 @@
       <c r="C4" s="41" t="n">
         <v>9060</v>
       </c>
-      <c r="D4" s="168">
+      <c r="D4" s="160">
         <f>C4/C4</f>
         <v/>
       </c>
@@ -9490,9 +9467,9 @@
         </is>
       </c>
       <c r="J4" s="28" t="n"/>
-      <c r="K4" s="165" t="n"/>
-      <c r="L4" s="165" t="n"/>
-      <c r="M4" s="165" t="n"/>
+      <c r="K4" s="121" t="n"/>
+      <c r="L4" s="121" t="n"/>
+      <c r="M4" s="121" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="28" t="inlineStr">
@@ -9508,7 +9485,7 @@
       <c r="C5" s="41" t="n">
         <v>4474</v>
       </c>
-      <c r="D5" s="168">
+      <c r="D5" s="160">
         <f>C5/C5</f>
         <v/>
       </c>
@@ -9534,9 +9511,9 @@
         </is>
       </c>
       <c r="J5" s="28" t="n"/>
-      <c r="K5" s="165" t="n"/>
-      <c r="L5" s="165" t="n"/>
-      <c r="M5" s="165" t="n"/>
+      <c r="K5" s="121" t="n"/>
+      <c r="L5" s="121" t="n"/>
+      <c r="M5" s="121" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="30" t="inlineStr">
@@ -9552,7 +9529,7 @@
       <c r="C6" s="42" t="n">
         <v>139083</v>
       </c>
-      <c r="D6" s="169">
+      <c r="D6" s="161">
         <f>C6/(C6+C7)</f>
         <v/>
       </c>
@@ -9584,9 +9561,9 @@
           <t>2건 합산</t>
         </is>
       </c>
-      <c r="K6" s="165" t="n"/>
-      <c r="L6" s="165" t="n"/>
-      <c r="M6" s="165" t="n"/>
+      <c r="K6" s="121" t="n"/>
+      <c r="L6" s="121" t="n"/>
+      <c r="M6" s="121" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="30" t="n"/>
@@ -9598,7 +9575,7 @@
       <c r="C7" s="42" t="n">
         <v>252</v>
       </c>
-      <c r="D7" s="169">
+      <c r="D7" s="161">
         <f>C7/(C6+C7)</f>
         <v/>
       </c>
@@ -9626,9 +9603,9 @@
         </is>
       </c>
       <c r="J7" s="30" t="n"/>
-      <c r="K7" s="165" t="n"/>
-      <c r="L7" s="165" t="n"/>
-      <c r="M7" s="165" t="n"/>
+      <c r="K7" s="121" t="n"/>
+      <c r="L7" s="121" t="n"/>
+      <c r="M7" s="121" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
@@ -9644,7 +9621,7 @@
       <c r="C8" s="41" t="n">
         <v>137850</v>
       </c>
-      <c r="D8" s="168">
+      <c r="D8" s="160">
         <f>C8/C8</f>
         <v/>
       </c>
@@ -9670,9 +9647,9 @@
         </is>
       </c>
       <c r="J8" s="28" t="n"/>
-      <c r="K8" s="165" t="n"/>
-      <c r="L8" s="165" t="n"/>
-      <c r="M8" s="165" t="n"/>
+      <c r="K8" s="121" t="n"/>
+      <c r="L8" s="121" t="n"/>
+      <c r="M8" s="121" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
@@ -9688,7 +9665,7 @@
       <c r="C9" s="42" t="n">
         <v>20174</v>
       </c>
-      <c r="D9" s="169">
+      <c r="D9" s="161">
         <f>C9/(C9+C10)</f>
         <v/>
       </c>
@@ -9720,9 +9697,9 @@
           <t>2건 합산</t>
         </is>
       </c>
-      <c r="K9" s="165" t="n"/>
-      <c r="L9" s="165" t="n"/>
-      <c r="M9" s="165" t="n"/>
+      <c r="K9" s="121" t="n"/>
+      <c r="L9" s="121" t="n"/>
+      <c r="M9" s="121" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="30" t="n"/>
@@ -9734,7 +9711,7 @@
       <c r="C10" s="42" t="n">
         <v>4620</v>
       </c>
-      <c r="D10" s="169">
+      <c r="D10" s="161">
         <f>C10/(C9+C10)</f>
         <v/>
       </c>
@@ -9762,9 +9739,9 @@
         </is>
       </c>
       <c r="J10" s="30" t="n"/>
-      <c r="K10" s="165" t="n"/>
-      <c r="L10" s="165" t="n"/>
-      <c r="M10" s="165" t="n"/>
+      <c r="K10" s="121" t="n"/>
+      <c r="L10" s="121" t="n"/>
+      <c r="M10" s="121" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
@@ -9780,7 +9757,7 @@
       <c r="C11" s="42" t="n">
         <v>9626.35</v>
       </c>
-      <c r="D11" s="169">
+      <c r="D11" s="161">
         <f>C11/(C11+C12)</f>
         <v/>
       </c>
@@ -9812,9 +9789,9 @@
           <t>2건 합산</t>
         </is>
       </c>
-      <c r="K11" s="165" t="n"/>
-      <c r="L11" s="165" t="n"/>
-      <c r="M11" s="165" t="n"/>
+      <c r="K11" s="121" t="n"/>
+      <c r="L11" s="121" t="n"/>
+      <c r="M11" s="121" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="30" t="n"/>
@@ -9826,7 +9803,7 @@
       <c r="C12" s="42" t="n">
         <v>4936</v>
       </c>
-      <c r="D12" s="169">
+      <c r="D12" s="161">
         <f>C12/(C11+C12)</f>
         <v/>
       </c>
@@ -9854,9 +9831,9 @@
         </is>
       </c>
       <c r="J12" s="30" t="n"/>
-      <c r="K12" s="165" t="n"/>
-      <c r="L12" s="165" t="n"/>
-      <c r="M12" s="165" t="n"/>
+      <c r="K12" s="121" t="n"/>
+      <c r="L12" s="121" t="n"/>
+      <c r="M12" s="121" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="28" t="inlineStr">
@@ -9872,7 +9849,7 @@
       <c r="C13" s="41" t="n">
         <v>1700</v>
       </c>
-      <c r="D13" s="168">
+      <c r="D13" s="160">
         <f>C13/C13</f>
         <v/>
       </c>
@@ -9896,9 +9873,9 @@
         </is>
       </c>
       <c r="J13" s="28" t="n"/>
-      <c r="K13" s="165" t="n"/>
-      <c r="L13" s="165" t="n"/>
-      <c r="M13" s="165" t="n"/>
+      <c r="K13" s="121" t="n"/>
+      <c r="L13" s="121" t="n"/>
+      <c r="M13" s="121" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
@@ -9914,7 +9891,7 @@
       <c r="C14" s="42" t="n">
         <v>180</v>
       </c>
-      <c r="D14" s="169">
+      <c r="D14" s="161">
         <f>C14/(C14+C15)</f>
         <v/>
       </c>
@@ -9946,9 +9923,9 @@
           <t>2건 합산</t>
         </is>
       </c>
-      <c r="K14" s="165" t="n"/>
-      <c r="L14" s="165" t="n"/>
-      <c r="M14" s="165" t="n"/>
+      <c r="K14" s="121" t="n"/>
+      <c r="L14" s="121" t="n"/>
+      <c r="M14" s="121" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="30" t="n"/>
@@ -9960,7 +9937,7 @@
       <c r="C15" s="42" t="n">
         <v>36190</v>
       </c>
-      <c r="D15" s="169">
+      <c r="D15" s="161">
         <f>C15/(C14+C15)</f>
         <v/>
       </c>
@@ -9988,9 +9965,9 @@
         </is>
       </c>
       <c r="J15" s="30" t="n"/>
-      <c r="K15" s="165" t="n"/>
-      <c r="L15" s="165" t="n"/>
-      <c r="M15" s="165" t="n"/>
+      <c r="K15" s="121" t="n"/>
+      <c r="L15" s="121" t="n"/>
+      <c r="M15" s="121" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="28" t="inlineStr">
@@ -10006,7 +9983,7 @@
       <c r="C16" s="41" t="n">
         <v>2710</v>
       </c>
-      <c r="D16" s="168">
+      <c r="D16" s="160">
         <f>C16/C16</f>
         <v/>
       </c>
@@ -10030,9 +10007,9 @@
         </is>
       </c>
       <c r="J16" s="28" t="n"/>
-      <c r="K16" s="165" t="n"/>
-      <c r="L16" s="165" t="n"/>
-      <c r="M16" s="165" t="n"/>
+      <c r="K16" s="121" t="n"/>
+      <c r="L16" s="121" t="n"/>
+      <c r="M16" s="121" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
@@ -10048,7 +10025,7 @@
       <c r="C17" s="41" t="n">
         <v>2745</v>
       </c>
-      <c r="D17" s="168">
+      <c r="D17" s="160">
         <f>C17/C17</f>
         <v/>
       </c>
@@ -10072,9 +10049,9 @@
         </is>
       </c>
       <c r="J17" s="28" t="n"/>
-      <c r="K17" s="165" t="n"/>
-      <c r="L17" s="165" t="n"/>
-      <c r="M17" s="165" t="n"/>
+      <c r="K17" s="121" t="n"/>
+      <c r="L17" s="121" t="n"/>
+      <c r="M17" s="121" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
@@ -10090,7 +10067,7 @@
       <c r="C18" s="41" t="n">
         <v>9740</v>
       </c>
-      <c r="D18" s="168">
+      <c r="D18" s="160">
         <f>C18/C18</f>
         <v/>
       </c>
@@ -10114,9 +10091,9 @@
         </is>
       </c>
       <c r="J18" s="28" t="n"/>
-      <c r="K18" s="165" t="n"/>
-      <c r="L18" s="165" t="n"/>
-      <c r="M18" s="165" t="n"/>
+      <c r="K18" s="121" t="n"/>
+      <c r="L18" s="121" t="n"/>
+      <c r="M18" s="121" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
@@ -10132,7 +10109,7 @@
       <c r="C19" s="41" t="n">
         <v>5056.8</v>
       </c>
-      <c r="D19" s="168">
+      <c r="D19" s="160">
         <f>C19/C19</f>
         <v/>
       </c>
@@ -10158,9 +10135,9 @@
         </is>
       </c>
       <c r="J19" s="28" t="n"/>
-      <c r="K19" s="165" t="n"/>
-      <c r="L19" s="165" t="n"/>
-      <c r="M19" s="165" t="n"/>
+      <c r="K19" s="121" t="n"/>
+      <c r="L19" s="121" t="n"/>
+      <c r="M19" s="121" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
@@ -10176,7 +10153,7 @@
       <c r="C20" s="41" t="n">
         <v>21280</v>
       </c>
-      <c r="D20" s="168">
+      <c r="D20" s="160">
         <f>C20/C20</f>
         <v/>
       </c>
@@ -10200,9 +10177,9 @@
         </is>
       </c>
       <c r="J20" s="28" t="n"/>
-      <c r="K20" s="165" t="n"/>
-      <c r="L20" s="165" t="n"/>
-      <c r="M20" s="165" t="n"/>
+      <c r="K20" s="121" t="n"/>
+      <c r="L20" s="121" t="n"/>
+      <c r="M20" s="121" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
@@ -10218,7 +10195,7 @@
       <c r="C21" s="41" t="n">
         <v>11000</v>
       </c>
-      <c r="D21" s="168">
+      <c r="D21" s="160">
         <f>C21/C21</f>
         <v/>
       </c>
@@ -10242,9 +10219,9 @@
         </is>
       </c>
       <c r="J21" s="28" t="n"/>
-      <c r="K21" s="165" t="n"/>
-      <c r="L21" s="165" t="n"/>
-      <c r="M21" s="165" t="n"/>
+      <c r="K21" s="121" t="n"/>
+      <c r="L21" s="121" t="n"/>
+      <c r="M21" s="121" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
@@ -10260,7 +10237,7 @@
       <c r="C22" s="41" t="n">
         <v>286580</v>
       </c>
-      <c r="D22" s="168">
+      <c r="D22" s="160">
         <f>C22/C22</f>
         <v/>
       </c>
@@ -10286,9 +10263,9 @@
         </is>
       </c>
       <c r="J22" s="28" t="n"/>
-      <c r="K22" s="165" t="n"/>
-      <c r="L22" s="165" t="n"/>
-      <c r="M22" s="165" t="n"/>
+      <c r="K22" s="121" t="n"/>
+      <c r="L22" s="121" t="n"/>
+      <c r="M22" s="121" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
@@ -10304,7 +10281,7 @@
       <c r="C23" s="41" t="n">
         <v>2058</v>
       </c>
-      <c r="D23" s="168">
+      <c r="D23" s="160">
         <f>C23/C23</f>
         <v/>
       </c>
@@ -10330,9 +10307,9 @@
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
-      <c r="K23" s="165" t="n"/>
-      <c r="L23" s="165" t="n"/>
-      <c r="M23" s="165" t="n"/>
+      <c r="K23" s="121" t="n"/>
+      <c r="L23" s="121" t="n"/>
+      <c r="M23" s="121" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -10348,7 +10325,7 @@
       <c r="C24" s="41" t="n">
         <v>1977</v>
       </c>
-      <c r="D24" s="168">
+      <c r="D24" s="160">
         <f>C24/C24</f>
         <v/>
       </c>
@@ -10374,9 +10351,9 @@
         </is>
       </c>
       <c r="J24" s="28" t="n"/>
-      <c r="K24" s="165" t="n"/>
-      <c r="L24" s="165" t="n"/>
-      <c r="M24" s="165" t="n"/>
+      <c r="K24" s="121" t="n"/>
+      <c r="L24" s="121" t="n"/>
+      <c r="M24" s="121" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="97" t="inlineStr">
@@ -10392,7 +10369,7 @@
       <c r="C25" s="98" t="n">
         <v>78209</v>
       </c>
-      <c r="D25" s="170" t="n">
+      <c r="D25" s="162" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="97" t="inlineStr">
@@ -10419,7 +10396,7 @@
       <c r="J25" s="97" t="n"/>
       <c r="K25" s="101" t="n"/>
       <c r="L25" s="101" t="n"/>
-      <c r="M25" s="165" t="n"/>
+      <c r="M25" s="121" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="97" t="inlineStr">
@@ -10435,7 +10412,7 @@
       <c r="C26" s="98" t="n">
         <v>8140</v>
       </c>
-      <c r="D26" s="170" t="n">
+      <c r="D26" s="162" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="97" t="inlineStr">
@@ -10462,52 +10439,52 @@
       <c r="J26" s="97" t="n"/>
       <c r="K26" s="101" t="n"/>
       <c r="L26" s="101" t="n"/>
-      <c r="M26" s="165" t="n"/>
+      <c r="M26" s="121" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="165" t="n"/>
-      <c r="B27" s="165" t="n"/>
-      <c r="C27" s="165" t="n"/>
-      <c r="D27" s="165" t="n"/>
-      <c r="E27" s="165" t="n"/>
-      <c r="F27" s="165" t="n"/>
-      <c r="G27" s="165" t="n"/>
-      <c r="H27" s="165" t="n"/>
-      <c r="I27" s="165" t="n"/>
-      <c r="J27" s="165" t="n"/>
-      <c r="K27" s="165" t="n"/>
-      <c r="L27" s="165" t="n"/>
-      <c r="M27" s="165" t="n"/>
+      <c r="A27" s="121" t="n"/>
+      <c r="B27" s="121" t="n"/>
+      <c r="C27" s="121" t="n"/>
+      <c r="D27" s="121" t="n"/>
+      <c r="E27" s="121" t="n"/>
+      <c r="F27" s="121" t="n"/>
+      <c r="G27" s="121" t="n"/>
+      <c r="H27" s="121" t="n"/>
+      <c r="I27" s="121" t="n"/>
+      <c r="J27" s="121" t="n"/>
+      <c r="K27" s="121" t="n"/>
+      <c r="L27" s="121" t="n"/>
+      <c r="M27" s="121" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="165" t="n"/>
-      <c r="B28" s="165" t="n"/>
-      <c r="C28" s="165" t="n"/>
-      <c r="D28" s="165" t="n"/>
-      <c r="E28" s="165" t="n"/>
-      <c r="F28" s="165" t="n"/>
-      <c r="G28" s="165" t="n"/>
-      <c r="H28" s="165" t="n"/>
-      <c r="I28" s="165" t="n"/>
-      <c r="J28" s="165" t="n"/>
-      <c r="K28" s="165" t="n"/>
-      <c r="L28" s="165" t="n"/>
-      <c r="M28" s="165" t="n"/>
+      <c r="A28" s="121" t="n"/>
+      <c r="B28" s="121" t="n"/>
+      <c r="C28" s="121" t="n"/>
+      <c r="D28" s="121" t="n"/>
+      <c r="E28" s="121" t="n"/>
+      <c r="F28" s="121" t="n"/>
+      <c r="G28" s="121" t="n"/>
+      <c r="H28" s="121" t="n"/>
+      <c r="I28" s="121" t="n"/>
+      <c r="J28" s="121" t="n"/>
+      <c r="K28" s="121" t="n"/>
+      <c r="L28" s="121" t="n"/>
+      <c r="M28" s="121" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="165" t="n"/>
-      <c r="B29" s="165" t="n"/>
-      <c r="C29" s="165" t="n"/>
-      <c r="D29" s="165" t="n"/>
-      <c r="E29" s="165" t="n"/>
-      <c r="F29" s="165" t="n"/>
-      <c r="G29" s="165" t="n"/>
-      <c r="H29" s="165" t="n"/>
-      <c r="I29" s="165" t="n"/>
-      <c r="J29" s="165" t="n"/>
-      <c r="K29" s="165" t="n"/>
-      <c r="L29" s="165" t="n"/>
-      <c r="M29" s="165" t="n"/>
+      <c r="A29" s="121" t="n"/>
+      <c r="B29" s="121" t="n"/>
+      <c r="C29" s="121" t="n"/>
+      <c r="D29" s="121" t="n"/>
+      <c r="E29" s="121" t="n"/>
+      <c r="F29" s="121" t="n"/>
+      <c r="G29" s="121" t="n"/>
+      <c r="H29" s="121" t="n"/>
+      <c r="I29" s="121" t="n"/>
+      <c r="J29" s="121" t="n"/>
+      <c r="K29" s="121" t="n"/>
+      <c r="L29" s="121" t="n"/>
+      <c r="M29" s="121" t="n"/>
     </row>
     <row r="71">
       <c r="M71" s="40" t="n"/>
@@ -10531,100 +10508,100 @@
   <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="12.83203125" customWidth="1" style="130" min="1" max="1"/>
-    <col width="12" customWidth="1" style="130" min="2" max="2"/>
-    <col width="16" customWidth="1" style="130" min="3" max="3"/>
-    <col width="24" customWidth="1" style="130" min="4" max="4"/>
-    <col width="14" customWidth="1" style="130" min="5" max="5"/>
-    <col width="11" customWidth="1" style="130" min="6" max="6"/>
-    <col width="15" customWidth="1" style="130" min="7" max="9"/>
-    <col width="16" customWidth="1" style="130" min="10" max="11"/>
-    <col width="12" customWidth="1" style="130" min="12" max="12"/>
-    <col width="8.83203125" customWidth="1" style="130" min="13" max="15"/>
-    <col width="8.83203125" customWidth="1" style="130" min="16" max="16384"/>
+    <col width="12.83203125" customWidth="1" style="135" min="1" max="1"/>
+    <col width="12" customWidth="1" style="135" min="2" max="2"/>
+    <col width="16" customWidth="1" style="135" min="3" max="3"/>
+    <col width="24" customWidth="1" style="135" min="4" max="4"/>
+    <col width="14" customWidth="1" style="135" min="5" max="5"/>
+    <col width="11" customWidth="1" style="135" min="6" max="6"/>
+    <col width="15" customWidth="1" style="135" min="7" max="9"/>
+    <col width="16" customWidth="1" style="135" min="10" max="11"/>
+    <col width="12" customWidth="1" style="135" min="12" max="12"/>
+    <col width="8.83203125" customWidth="1" style="135" min="13" max="16"/>
+    <col width="8.83203125" customWidth="1" style="135" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="123" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>① 송금건별 데이터 (송금확인서 기준)</t>
         </is>
       </c>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="118" t="n"/>
-      <c r="K1" s="118" t="n"/>
-      <c r="L1" s="119" t="n"/>
-      <c r="M1" s="164" t="n"/>
+      <c r="B1" s="123" t="n"/>
+      <c r="C1" s="123" t="n"/>
+      <c r="D1" s="123" t="n"/>
+      <c r="E1" s="123" t="n"/>
+      <c r="F1" s="123" t="n"/>
+      <c r="G1" s="123" t="n"/>
+      <c r="H1" s="123" t="n"/>
+      <c r="I1" s="123" t="n"/>
+      <c r="J1" s="123" t="n"/>
+      <c r="K1" s="123" t="n"/>
+      <c r="L1" s="124" t="n"/>
+      <c r="M1" s="120" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="117" t="inlineStr">
+      <c r="A2" s="122" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="117" t="inlineStr">
+      <c r="B2" s="122" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
       </c>
-      <c r="C2" s="117" t="inlineStr">
+      <c r="C2" s="122" t="inlineStr">
         <is>
           <t>수취인</t>
         </is>
       </c>
-      <c r="D2" s="117" t="inlineStr">
+      <c r="D2" s="122" t="inlineStr">
         <is>
           <t>PO참조</t>
         </is>
       </c>
-      <c r="E2" s="117" t="inlineStr">
+      <c r="E2" s="122" t="inlineStr">
         <is>
           <t>USD금액</t>
         </is>
       </c>
-      <c r="F2" s="117" t="inlineStr">
+      <c r="F2" s="122" t="inlineStr">
         <is>
           <t>적용환율</t>
         </is>
       </c>
-      <c r="G2" s="117" t="inlineStr">
+      <c r="G2" s="122" t="inlineStr">
         <is>
           <t>중개수수료(USD)</t>
         </is>
       </c>
-      <c r="H2" s="117" t="inlineStr">
+      <c r="H2" s="122" t="inlineStr">
         <is>
           <t>수수료(KRW)</t>
         </is>
       </c>
-      <c r="I2" s="117" t="inlineStr">
+      <c r="I2" s="122" t="inlineStr">
         <is>
           <t>전신료(KRW)</t>
         </is>
       </c>
-      <c r="J2" s="117" t="inlineStr">
+      <c r="J2" s="122" t="inlineStr">
         <is>
           <t>KRW총액(실제)</t>
         </is>
       </c>
-      <c r="K2" s="117" t="inlineStr">
+      <c r="K2" s="122" t="inlineStr">
         <is>
           <t>KRW총액(검증)</t>
         </is>
       </c>
-      <c r="L2" s="117" t="inlineStr">
+      <c r="L2" s="122" t="inlineStr">
         <is>
           <t>차이</t>
         </is>
       </c>
-      <c r="M2" s="164" t="n"/>
+      <c r="M2" s="120" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -10648,7 +10625,7 @@
       <c r="E3" s="33" t="n">
         <v>35563</v>
       </c>
-      <c r="F3" s="171" t="n">
+      <c r="F3" s="163" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
@@ -10671,7 +10648,7 @@
         <f>J3-K3</f>
         <v/>
       </c>
-      <c r="M3" s="165" t="n"/>
+      <c r="M3" s="121" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -10695,7 +10672,7 @@
       <c r="E4" s="33" t="n">
         <v>55830</v>
       </c>
-      <c r="F4" s="171" t="n">
+      <c r="F4" s="163" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -10718,7 +10695,7 @@
         <f>J4-K4</f>
         <v/>
       </c>
-      <c r="M4" s="165" t="n"/>
+      <c r="M4" s="121" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -10742,7 +10719,7 @@
       <c r="E5" s="33" t="n">
         <v>9247.690000000001</v>
       </c>
-      <c r="F5" s="171" t="n">
+      <c r="F5" s="163" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -10765,7 +10742,7 @@
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="M5" s="165" t="n"/>
+      <c r="M5" s="121" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -10789,7 +10766,7 @@
       <c r="E6" s="33" t="n">
         <v>7410</v>
       </c>
-      <c r="F6" s="171" t="n">
+      <c r="F6" s="163" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -10812,7 +10789,7 @@
         <f>J6-K6</f>
         <v/>
       </c>
-      <c r="M6" s="165" t="n"/>
+      <c r="M6" s="121" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -10836,7 +10813,7 @@
       <c r="E7" s="33" t="n">
         <v>6024</v>
       </c>
-      <c r="F7" s="171" t="n">
+      <c r="F7" s="163" t="n">
         <v>1473.3</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -10859,7 +10836,7 @@
         <f>J7-K7</f>
         <v/>
       </c>
-      <c r="M7" s="165" t="n"/>
+      <c r="M7" s="121" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -10883,7 +10860,7 @@
       <c r="E8" s="33" t="n">
         <v>7862</v>
       </c>
-      <c r="F8" s="171" t="n">
+      <c r="F8" s="163" t="n">
         <v>1473.2</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -10906,7 +10883,7 @@
         <f>J8-K8</f>
         <v/>
       </c>
-      <c r="M8" s="165" t="n"/>
+      <c r="M8" s="121" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -10930,7 +10907,7 @@
       <c r="E9" s="33" t="n">
         <v>15040</v>
       </c>
-      <c r="F9" s="171" t="n">
+      <c r="F9" s="163" t="n">
         <v>1480</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -10953,7 +10930,7 @@
         <f>J9-K9</f>
         <v/>
       </c>
-      <c r="M9" s="165" t="n"/>
+      <c r="M9" s="121" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -10977,7 +10954,7 @@
       <c r="E10" s="33" t="n">
         <v>143557</v>
       </c>
-      <c r="F10" s="171" t="n">
+      <c r="F10" s="163" t="n">
         <v>1479.7</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -11000,7 +10977,7 @@
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="M10" s="165" t="n"/>
+      <c r="M10" s="121" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -11024,7 +11001,7 @@
       <c r="E11" s="33" t="n">
         <v>1200</v>
       </c>
-      <c r="F11" s="171" t="n">
+      <c r="F11" s="163" t="n">
         <v>1464.9</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -11047,7 +11024,7 @@
         <f>J11-K11</f>
         <v/>
       </c>
-      <c r="M11" s="165" t="n"/>
+      <c r="M11" s="121" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -11071,7 +11048,7 @@
       <c r="E12" s="33" t="n">
         <v>13860</v>
       </c>
-      <c r="F12" s="171" t="n">
+      <c r="F12" s="163" t="n">
         <v>1439.1</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -11094,7 +11071,7 @@
         <f>J12-K12</f>
         <v/>
       </c>
-      <c r="M12" s="165" t="n"/>
+      <c r="M12" s="121" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -11118,7 +11095,7 @@
       <c r="E13" s="33" t="n">
         <v>36060</v>
       </c>
-      <c r="F13" s="171" t="n">
+      <c r="F13" s="163" t="n">
         <v>1442.7</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -11141,7 +11118,7 @@
         <f>J13-K13</f>
         <v/>
       </c>
-      <c r="M13" s="165" t="n"/>
+      <c r="M13" s="121" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -11165,7 +11142,7 @@
       <c r="E14" s="33" t="n">
         <v>252</v>
       </c>
-      <c r="F14" s="171" t="n">
+      <c r="F14" s="163" t="n">
         <v>1479</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -11188,7 +11165,7 @@
         <f>J14-K14</f>
         <v/>
       </c>
-      <c r="M14" s="165" t="n"/>
+      <c r="M14" s="121" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -11212,7 +11189,7 @@
       <c r="E15" s="33" t="n">
         <v>3700</v>
       </c>
-      <c r="F15" s="171" t="n">
+      <c r="F15" s="163" t="n">
         <v>1475.7</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -11235,7 +11212,7 @@
         <f>J15-K15</f>
         <v/>
       </c>
-      <c r="M15" s="165" t="n"/>
+      <c r="M15" s="121" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -11259,7 +11236,7 @@
       <c r="E16" s="33" t="n">
         <v>9626.35</v>
       </c>
-      <c r="F16" s="171" t="n">
+      <c r="F16" s="163" t="n">
         <v>1476</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -11282,7 +11259,7 @@
         <f>J16-K16</f>
         <v/>
       </c>
-      <c r="M16" s="165" t="n"/>
+      <c r="M16" s="121" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -11306,7 +11283,7 @@
       <c r="E17" s="33" t="n">
         <v>5056.8</v>
       </c>
-      <c r="F17" s="171" t="n">
+      <c r="F17" s="163" t="n">
         <v>1445.5</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -11329,7 +11306,7 @@
         <f>J17-K17</f>
         <v/>
       </c>
-      <c r="M17" s="165" t="n"/>
+      <c r="M17" s="121" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -11353,7 +11330,7 @@
       <c r="E18" s="33" t="n">
         <v>25976</v>
       </c>
-      <c r="F18" s="171" t="n">
+      <c r="F18" s="163" t="n">
         <v>1445.5</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -11376,7 +11353,7 @@
         <f>J18-K18</f>
         <v/>
       </c>
-      <c r="M18" s="165" t="n"/>
+      <c r="M18" s="121" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -11400,7 +11377,7 @@
       <c r="E19" s="33" t="n">
         <v>24794</v>
       </c>
-      <c r="F19" s="171" t="n">
+      <c r="F19" s="163" t="n">
         <v>1454.7</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -11423,7 +11400,7 @@
         <f>J19-K19</f>
         <v/>
       </c>
-      <c r="M19" s="165" t="n"/>
+      <c r="M19" s="121" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -11447,7 +11424,7 @@
       <c r="E20" s="33" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F20" s="171" t="n">
+      <c r="F20" s="163" t="n">
         <v>1453.6</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -11470,7 +11447,7 @@
         <f>J20-K20</f>
         <v/>
       </c>
-      <c r="M20" s="165" t="n"/>
+      <c r="M20" s="121" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -11494,7 +11471,7 @@
       <c r="E21" s="33" t="n">
         <v>26358</v>
       </c>
-      <c r="F21" s="171" t="n">
+      <c r="F21" s="163" t="n">
         <v>1460.7</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -11517,7 +11494,7 @@
         <f>J21-K21</f>
         <v/>
       </c>
-      <c r="M21" s="165" t="n"/>
+      <c r="M21" s="121" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -11541,7 +11518,7 @@
       <c r="E22" s="33" t="n">
         <v>17538</v>
       </c>
-      <c r="F22" s="171" t="n">
+      <c r="F22" s="163" t="n">
         <v>1451.7</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -11564,7 +11541,7 @@
         <f>J22-K22</f>
         <v/>
       </c>
-      <c r="M22" s="165" t="n"/>
+      <c r="M22" s="121" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -11588,7 +11565,7 @@
       <c r="E23" s="33" t="n">
         <v>142189</v>
       </c>
-      <c r="F23" s="171" t="n">
+      <c r="F23" s="163" t="n">
         <v>1441.6</v>
       </c>
       <c r="G23" s="3" t="n">
@@ -11611,7 +11588,7 @@
         <f>J23-K23</f>
         <v/>
       </c>
-      <c r="M23" s="165" t="n"/>
+      <c r="M23" s="121" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -11635,7 +11612,7 @@
       <c r="E24" s="33" t="n">
         <v>137850</v>
       </c>
-      <c r="F24" s="171" t="n">
+      <c r="F24" s="163" t="n">
         <v>1477.6</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -11658,7 +11635,7 @@
         <f>J24-K24</f>
         <v/>
       </c>
-      <c r="M24" s="165" t="n"/>
+      <c r="M24" s="121" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -11682,7 +11659,7 @@
       <c r="E25" s="33" t="n">
         <v>34354</v>
       </c>
-      <c r="F25" s="171" t="n">
+      <c r="F25" s="163" t="n">
         <v>1505.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -11705,7 +11682,7 @@
         <f>J25-K25</f>
         <v/>
       </c>
-      <c r="M25" s="165" t="n"/>
+      <c r="M25" s="121" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -11729,7 +11706,7 @@
       <c r="E26" s="33" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F26" s="171" t="n">
+      <c r="F26" s="163" t="n">
         <v>1506.4</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -11752,7 +11729,7 @@
         <f>J26-K26</f>
         <v/>
       </c>
-      <c r="M26" s="165" t="n"/>
+      <c r="M26" s="121" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -11776,7 +11753,7 @@
       <c r="E27" s="33" t="n">
         <v>57650</v>
       </c>
-      <c r="F27" s="171" t="n">
+      <c r="F27" s="163" t="n">
         <v>1481.9</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -11799,7 +11776,7 @@
         <f>J27-K27</f>
         <v/>
       </c>
-      <c r="M27" s="165" t="n"/>
+      <c r="M27" s="121" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="102" t="n">
@@ -11823,7 +11800,7 @@
       <c r="E28" s="104" t="n">
         <v>814</v>
       </c>
-      <c r="F28" s="172" t="n">
+      <c r="F28" s="164" t="n">
         <v>1505</v>
       </c>
       <c r="G28" s="102" t="n">
@@ -11846,7 +11823,7 @@
         <f>J28-K28</f>
         <v/>
       </c>
-      <c r="M28" s="165" t="n"/>
+      <c r="M28" s="121" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="102" t="n">
@@ -11870,7 +11847,7 @@
       <c r="E29" s="104" t="n">
         <v>30000</v>
       </c>
-      <c r="F29" s="172" t="n">
+      <c r="F29" s="164" t="n">
         <v>1520.1</v>
       </c>
       <c r="G29" s="102" t="n">
@@ -11893,7 +11870,7 @@
         <f>J29-K29</f>
         <v/>
       </c>
-      <c r="M29" s="165" t="n"/>
+      <c r="M29" s="121" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="102" t="n">
@@ -11917,7 +11894,7 @@
       <c r="E30" s="104" t="n">
         <v>25976</v>
       </c>
-      <c r="F30" s="172" t="n">
+      <c r="F30" s="164" t="n">
         <v>1473.3</v>
       </c>
       <c r="G30" s="102" t="n">
@@ -11940,7 +11917,7 @@
         <f>J30-K30</f>
         <v/>
       </c>
-      <c r="M30" s="165" t="n"/>
+      <c r="M30" s="121" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="102" t="n">
@@ -11964,7 +11941,7 @@
       <c r="E31" s="104" t="n">
         <v>297580</v>
       </c>
-      <c r="F31" s="172" t="n">
+      <c r="F31" s="164" t="n">
         <v>1482.8</v>
       </c>
       <c r="G31" s="102" t="n">
@@ -11987,7 +11964,7 @@
         <f>J31-K31</f>
         <v/>
       </c>
-      <c r="M31" s="165" t="n"/>
+      <c r="M31" s="121" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="102" t="n">
@@ -12011,7 +11988,7 @@
       <c r="E32" s="104" t="n">
         <v>4388.4</v>
       </c>
-      <c r="F32" s="172" t="n">
+      <c r="F32" s="164" t="n">
         <v>1741.08</v>
       </c>
       <c r="G32" s="102" t="n">
@@ -12034,89 +12011,89 @@
         <f>J32-K32</f>
         <v/>
       </c>
-      <c r="M32" s="165" t="n"/>
+      <c r="M32" s="121" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="123" t="inlineStr">
+      <c r="A33" s="128" t="inlineStr">
         <is>
           <t>② PO별 비용 안분 내역</t>
         </is>
       </c>
-      <c r="B33" s="118" t="n"/>
-      <c r="C33" s="118" t="n"/>
-      <c r="D33" s="118" t="n"/>
-      <c r="E33" s="118" t="n"/>
-      <c r="F33" s="118" t="n"/>
-      <c r="G33" s="118" t="n"/>
-      <c r="H33" s="118" t="n"/>
-      <c r="I33" s="118" t="n"/>
-      <c r="J33" s="118" t="n"/>
-      <c r="K33" s="118" t="n"/>
-      <c r="L33" s="119" t="n"/>
-      <c r="M33" s="164" t="n"/>
+      <c r="B33" s="123" t="n"/>
+      <c r="C33" s="123" t="n"/>
+      <c r="D33" s="123" t="n"/>
+      <c r="E33" s="123" t="n"/>
+      <c r="F33" s="123" t="n"/>
+      <c r="G33" s="123" t="n"/>
+      <c r="H33" s="123" t="n"/>
+      <c r="I33" s="123" t="n"/>
+      <c r="J33" s="123" t="n"/>
+      <c r="K33" s="123" t="n"/>
+      <c r="L33" s="124" t="n"/>
+      <c r="M33" s="120" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="117" t="inlineStr">
+      <c r="A34" s="122" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="B34" s="117" t="inlineStr">
+      <c r="B34" s="122" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
       </c>
-      <c r="C34" s="117" t="inlineStr">
+      <c r="C34" s="122" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D34" s="117" t="inlineStr">
+      <c r="D34" s="122" t="inlineStr">
         <is>
           <t>PO USD</t>
         </is>
       </c>
-      <c r="E34" s="117" t="inlineStr">
+      <c r="E34" s="122" t="inlineStr">
         <is>
           <t>그룹총USD</t>
         </is>
       </c>
-      <c r="F34" s="117" t="inlineStr">
+      <c r="F34" s="122" t="inlineStr">
         <is>
           <t>배부비율</t>
         </is>
       </c>
-      <c r="G34" s="117" t="inlineStr">
+      <c r="G34" s="122" t="inlineStr">
         <is>
           <t>적용환율</t>
         </is>
       </c>
-      <c r="H34" s="117" t="inlineStr">
+      <c r="H34" s="122" t="inlineStr">
         <is>
           <t>원화환산액</t>
         </is>
       </c>
-      <c r="I34" s="117" t="inlineStr">
+      <c r="I34" s="122" t="inlineStr">
         <is>
           <t>중개수수료안분</t>
         </is>
       </c>
-      <c r="J34" s="117" t="inlineStr">
+      <c r="J34" s="122" t="inlineStr">
         <is>
           <t>수수료안분</t>
         </is>
       </c>
-      <c r="K34" s="117" t="inlineStr">
+      <c r="K34" s="122" t="inlineStr">
         <is>
           <t>전신료안분</t>
         </is>
       </c>
-      <c r="L34" s="117" t="inlineStr">
+      <c r="L34" s="122" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="M34" s="164" t="n"/>
+      <c r="M34" s="120" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -12168,7 +12145,7 @@
         <f>H35+I35+J35+K35</f>
         <v/>
       </c>
-      <c r="M35" s="165" t="n"/>
+      <c r="M35" s="121" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -12220,7 +12197,7 @@
         <f>H36+I36+J36+K36</f>
         <v/>
       </c>
-      <c r="M36" s="165" t="n"/>
+      <c r="M36" s="121" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -12272,7 +12249,7 @@
         <f>H37+I37+J37+K37</f>
         <v/>
       </c>
-      <c r="M37" s="165" t="n"/>
+      <c r="M37" s="121" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -12324,7 +12301,7 @@
         <f>H38+I38+J38+K38</f>
         <v/>
       </c>
-      <c r="M38" s="165" t="n"/>
+      <c r="M38" s="121" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -12376,7 +12353,7 @@
         <f>H39+I39+J39+K39</f>
         <v/>
       </c>
-      <c r="M39" s="165" t="n"/>
+      <c r="M39" s="121" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -12428,7 +12405,7 @@
         <f>H40+I40+J40+K40</f>
         <v/>
       </c>
-      <c r="M40" s="165" t="n"/>
+      <c r="M40" s="121" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -12480,7 +12457,7 @@
         <f>H41+I41+J41+K41</f>
         <v/>
       </c>
-      <c r="M41" s="165" t="n"/>
+      <c r="M41" s="121" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -12532,7 +12509,7 @@
         <f>H42+I42+J42+K42</f>
         <v/>
       </c>
-      <c r="M42" s="165" t="n"/>
+      <c r="M42" s="121" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -12584,7 +12561,7 @@
         <f>H43+I43+J43+K43</f>
         <v/>
       </c>
-      <c r="M43" s="165" t="n"/>
+      <c r="M43" s="121" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -12636,7 +12613,7 @@
         <f>H44+I44+J44+K44</f>
         <v/>
       </c>
-      <c r="M44" s="165" t="n"/>
+      <c r="M44" s="121" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -12688,7 +12665,7 @@
         <f>H45+I45+J45+K45</f>
         <v/>
       </c>
-      <c r="M45" s="165" t="n"/>
+      <c r="M45" s="121" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -12740,7 +12717,7 @@
         <f>H46+I46+J46+K46</f>
         <v/>
       </c>
-      <c r="M46" s="165" t="n"/>
+      <c r="M46" s="121" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -12792,7 +12769,7 @@
         <f>H47+I47+J47+K47</f>
         <v/>
       </c>
-      <c r="M47" s="165" t="n"/>
+      <c r="M47" s="121" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -12844,7 +12821,7 @@
         <f>H48+I48+J48+K48</f>
         <v/>
       </c>
-      <c r="M48" s="165" t="n"/>
+      <c r="M48" s="121" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -12896,7 +12873,7 @@
         <f>H49+I49+J49+K49</f>
         <v/>
       </c>
-      <c r="M49" s="165" t="n"/>
+      <c r="M49" s="121" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -12948,7 +12925,7 @@
         <f>H50+I50+J50+K50</f>
         <v/>
       </c>
-      <c r="M50" s="165" t="n"/>
+      <c r="M50" s="121" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -13000,7 +12977,7 @@
         <f>H51+I51+J51+K51</f>
         <v/>
       </c>
-      <c r="M51" s="165" t="n"/>
+      <c r="M51" s="121" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
@@ -13052,7 +13029,7 @@
         <f>H52+I52+J52+K52</f>
         <v/>
       </c>
-      <c r="M52" s="165" t="n"/>
+      <c r="M52" s="121" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -13104,7 +13081,7 @@
         <f>H53+I53+J53+K53</f>
         <v/>
       </c>
-      <c r="M53" s="165" t="n"/>
+      <c r="M53" s="121" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -13156,7 +13133,7 @@
         <f>H54+I54+J54+K54</f>
         <v/>
       </c>
-      <c r="M54" s="165" t="n"/>
+      <c r="M54" s="121" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -13208,7 +13185,7 @@
         <f>H55+I55+J55+K55</f>
         <v/>
       </c>
-      <c r="M55" s="165" t="n"/>
+      <c r="M55" s="121" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
@@ -13260,7 +13237,7 @@
         <f>H56+I56+J56+K56</f>
         <v/>
       </c>
-      <c r="M56" s="165" t="n"/>
+      <c r="M56" s="121" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -13312,7 +13289,7 @@
         <f>H57+I57+J57+K57</f>
         <v/>
       </c>
-      <c r="M57" s="165" t="n"/>
+      <c r="M57" s="121" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
@@ -13364,7 +13341,7 @@
         <f>H58+I58+J58+K58</f>
         <v/>
       </c>
-      <c r="M58" s="165" t="n"/>
+      <c r="M58" s="121" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -13416,7 +13393,7 @@
         <f>H59+I59+J59+K59</f>
         <v/>
       </c>
-      <c r="M59" s="165" t="n"/>
+      <c r="M59" s="121" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
@@ -13468,7 +13445,7 @@
         <f>H60+I60+J60+K60</f>
         <v/>
       </c>
-      <c r="M60" s="165" t="n"/>
+      <c r="M60" s="121" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -13520,7 +13497,7 @@
         <f>H61+I61+J61+K61</f>
         <v/>
       </c>
-      <c r="M61" s="165" t="n"/>
+      <c r="M61" s="121" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
@@ -13572,7 +13549,7 @@
         <f>H62+I62+J62+K62</f>
         <v/>
       </c>
-      <c r="M62" s="165" t="n"/>
+      <c r="M62" s="121" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -13624,7 +13601,7 @@
         <f>H63+I63+J63+K63</f>
         <v/>
       </c>
-      <c r="M63" s="165" t="n"/>
+      <c r="M63" s="121" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
@@ -13676,7 +13653,7 @@
         <f>H64+I64+J64+K64</f>
         <v/>
       </c>
-      <c r="M64" s="165" t="n"/>
+      <c r="M64" s="121" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -13728,7 +13705,7 @@
         <f>H65+I65+J65+K65</f>
         <v/>
       </c>
-      <c r="M65" s="165" t="n"/>
+      <c r="M65" s="121" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="102" t="inlineStr">
@@ -13780,7 +13757,7 @@
         <f>H66+I66+J66+K66</f>
         <v/>
       </c>
-      <c r="M66" s="165" t="n"/>
+      <c r="M66" s="121" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="102" t="inlineStr">
@@ -13832,7 +13809,7 @@
         <f>H67+I67+J67+K67</f>
         <v/>
       </c>
-      <c r="M67" s="165" t="n"/>
+      <c r="M67" s="121" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="102" t="inlineStr">
@@ -13884,22 +13861,22 @@
         <f>H68+I68+J68+K68</f>
         <v/>
       </c>
-      <c r="M68" s="165" t="n"/>
+      <c r="M68" s="121" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="165" t="n"/>
-      <c r="B69" s="165" t="n"/>
-      <c r="C69" s="165" t="n"/>
-      <c r="D69" s="165" t="n"/>
-      <c r="E69" s="165" t="n"/>
-      <c r="F69" s="165" t="n"/>
-      <c r="G69" s="165" t="n"/>
-      <c r="H69" s="165" t="n"/>
-      <c r="I69" s="165" t="n"/>
-      <c r="J69" s="165" t="n"/>
-      <c r="K69" s="165" t="n"/>
-      <c r="L69" s="165" t="n"/>
-      <c r="M69" s="165" t="n"/>
+      <c r="A69" s="121" t="n"/>
+      <c r="B69" s="121" t="n"/>
+      <c r="C69" s="121" t="n"/>
+      <c r="D69" s="121" t="n"/>
+      <c r="E69" s="121" t="n"/>
+      <c r="F69" s="121" t="n"/>
+      <c r="G69" s="121" t="n"/>
+      <c r="H69" s="121" t="n"/>
+      <c r="I69" s="121" t="n"/>
+      <c r="J69" s="121" t="n"/>
+      <c r="K69" s="121" t="n"/>
+      <c r="L69" s="121" t="n"/>
+      <c r="M69" s="121" t="n"/>
     </row>
     <row r="76">
       <c r="M76" s="40" t="n"/>
@@ -13924,47 +13901,47 @@
   <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="10" customWidth="1" style="130" min="1" max="1"/>
-    <col width="16" customWidth="1" style="130" min="2" max="3"/>
-    <col width="18" customWidth="1" style="130" min="4" max="4"/>
-    <col width="12" customWidth="1" style="130" min="5" max="5"/>
-    <col width="32" customWidth="1" style="130" min="6" max="6"/>
-    <col width="16.33203125" customWidth="1" style="130" min="7" max="8"/>
-    <col width="14.83203125" customWidth="1" style="130" min="9" max="9"/>
-    <col width="12" customWidth="1" style="130" min="10" max="10"/>
-    <col width="16" customWidth="1" style="130" min="11" max="11"/>
-    <col width="14.33203125" customWidth="1" style="130" min="12" max="12"/>
-    <col width="12" customWidth="1" style="130" min="13" max="14"/>
-    <col width="14" customWidth="1" style="130" min="15" max="15"/>
-    <col width="12" customWidth="1" style="130" min="16" max="16"/>
-    <col width="8.83203125" customWidth="1" style="130" min="17" max="19"/>
-    <col width="8.83203125" customWidth="1" style="130" min="20" max="16384"/>
+    <col width="10" customWidth="1" style="135" min="1" max="1"/>
+    <col width="16" customWidth="1" style="135" min="2" max="3"/>
+    <col width="18" customWidth="1" style="135" min="4" max="4"/>
+    <col width="12" customWidth="1" style="135" min="5" max="5"/>
+    <col width="32" customWidth="1" style="135" min="6" max="6"/>
+    <col width="16.33203125" customWidth="1" style="135" min="7" max="8"/>
+    <col width="14.83203125" customWidth="1" style="135" min="9" max="9"/>
+    <col width="12" customWidth="1" style="135" min="10" max="10"/>
+    <col width="16" customWidth="1" style="135" min="11" max="11"/>
+    <col width="14.33203125" customWidth="1" style="135" min="12" max="12"/>
+    <col width="12" customWidth="1" style="135" min="13" max="14"/>
+    <col width="14" customWidth="1" style="135" min="15" max="15"/>
+    <col width="12" customWidth="1" style="135" min="16" max="16"/>
+    <col width="8.83203125" customWidth="1" style="135" min="17" max="20"/>
+    <col width="8.83203125" customWidth="1" style="135" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="131" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>RNR 2026년 Usance L/C 상환 현황</t>
         </is>
       </c>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="118" t="n"/>
-      <c r="K1" s="118" t="n"/>
-      <c r="L1" s="118" t="n"/>
-      <c r="M1" s="118" t="n"/>
-      <c r="N1" s="118" t="n"/>
-      <c r="O1" s="118" t="n"/>
-      <c r="P1" s="119" t="n"/>
+      <c r="B1" s="123" t="n"/>
+      <c r="C1" s="123" t="n"/>
+      <c r="D1" s="123" t="n"/>
+      <c r="E1" s="123" t="n"/>
+      <c r="F1" s="123" t="n"/>
+      <c r="G1" s="123" t="n"/>
+      <c r="H1" s="123" t="n"/>
+      <c r="I1" s="123" t="n"/>
+      <c r="J1" s="123" t="n"/>
+      <c r="K1" s="123" t="n"/>
+      <c r="L1" s="123" t="n"/>
+      <c r="M1" s="123" t="n"/>
+      <c r="N1" s="123" t="n"/>
+      <c r="O1" s="123" t="n"/>
+      <c r="P1" s="124" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="133" t="inlineStr">
+      <c r="A2" s="138" t="inlineStr">
         <is>
           <t>기준일: 2026-04-20  |  미상환 건만 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
         </is>
@@ -13989,7 +13966,7 @@
       <c r="P3" s="43" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="137" t="inlineStr">
         <is>
           <t>&lt; 은행별 Usance L/C 한도 현황 &gt;</t>
         </is>
@@ -14133,14 +14110,14 @@
       <c r="F9" s="54" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="129" t="inlineStr">
+      <c r="A10" s="134" t="inlineStr">
         <is>
           <t>※ 현재 오픈 = 미상환 L/C(상환확정일 비어있는 건)의 개설금액 합계 → 상환 시 자동 반영</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="129" t="inlineStr">
+      <c r="A11" s="134" t="inlineStr">
         <is>
           <t>출처: 총 한도 – Slack 2024-11-19 / 활성 여부 – Slack 2026-03-16 도원석</t>
         </is>
@@ -14149,26 +14126,26 @@
     <row r="12" ht="18" customHeight="1"/>
     <row r="13" ht="18" customHeight="1"/>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>&lt; 미상환 L/C 현황 &gt;</t>
         </is>
       </c>
-      <c r="B14" s="118" t="n"/>
-      <c r="C14" s="118" t="n"/>
-      <c r="D14" s="118" t="n"/>
-      <c r="E14" s="118" t="n"/>
-      <c r="F14" s="118" t="n"/>
-      <c r="G14" s="118" t="n"/>
-      <c r="H14" s="118" t="n"/>
-      <c r="I14" s="118" t="n"/>
-      <c r="J14" s="118" t="n"/>
-      <c r="K14" s="118" t="n"/>
-      <c r="L14" s="118" t="n"/>
-      <c r="M14" s="118" t="n"/>
-      <c r="N14" s="118" t="n"/>
-      <c r="O14" s="118" t="n"/>
-      <c r="P14" s="119" t="n"/>
+      <c r="B14" s="123" t="n"/>
+      <c r="C14" s="123" t="n"/>
+      <c r="D14" s="123" t="n"/>
+      <c r="E14" s="123" t="n"/>
+      <c r="F14" s="123" t="n"/>
+      <c r="G14" s="123" t="n"/>
+      <c r="H14" s="123" t="n"/>
+      <c r="I14" s="123" t="n"/>
+      <c r="J14" s="123" t="n"/>
+      <c r="K14" s="123" t="n"/>
+      <c r="L14" s="123" t="n"/>
+      <c r="M14" s="123" t="n"/>
+      <c r="N14" s="123" t="n"/>
+      <c r="O14" s="123" t="n"/>
+      <c r="P14" s="124" t="n"/>
     </row>
     <row r="15" ht="15" customFormat="1" customHeight="1" s="73">
       <c r="A15" s="56" t="inlineStr">
@@ -14181,7 +14158,7 @@
           <t>PO No.</t>
         </is>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
@@ -14304,11 +14281,11 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="L16" s="173" t="n">
+      <c r="L16" s="165" t="n">
         <v>67</v>
       </c>
       <c r="M16" s="59" t="n"/>
-      <c r="N16" s="174" t="n"/>
+      <c r="N16" s="166" t="n"/>
       <c r="O16" s="63" t="n"/>
       <c r="P16" s="59" t="n"/>
     </row>
@@ -14364,11 +14341,11 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="L17" s="173" t="n">
+      <c r="L17" s="165" t="n">
         <v>60</v>
       </c>
       <c r="M17" s="59" t="n"/>
-      <c r="N17" s="174" t="n"/>
+      <c r="N17" s="166" t="n"/>
       <c r="O17" s="63" t="n"/>
       <c r="P17" s="59" t="n"/>
     </row>
@@ -14416,22 +14393,22 @@
       <c r="P19" s="65" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>&lt; 수입/통관 정보 &gt;</t>
         </is>
       </c>
-      <c r="B20" s="118" t="n"/>
-      <c r="C20" s="118" t="n"/>
-      <c r="D20" s="118" t="n"/>
-      <c r="E20" s="118" t="n"/>
-      <c r="F20" s="118" t="n"/>
-      <c r="G20" s="118" t="n"/>
-      <c r="H20" s="118" t="n"/>
-      <c r="I20" s="118" t="n"/>
-      <c r="J20" s="118" t="n"/>
-      <c r="K20" s="118" t="n"/>
-      <c r="L20" s="119" t="n"/>
+      <c r="B20" s="123" t="n"/>
+      <c r="C20" s="123" t="n"/>
+      <c r="D20" s="123" t="n"/>
+      <c r="E20" s="123" t="n"/>
+      <c r="F20" s="123" t="n"/>
+      <c r="G20" s="123" t="n"/>
+      <c r="H20" s="123" t="n"/>
+      <c r="I20" s="123" t="n"/>
+      <c r="J20" s="123" t="n"/>
+      <c r="K20" s="123" t="n"/>
+      <c r="L20" s="124" t="n"/>
       <c r="M20" s="43" t="n"/>
       <c r="N20" s="43" t="n"/>
       <c r="O20" s="43" t="n"/>
@@ -14448,7 +14425,7 @@
           <t>수입신고번호</t>
         </is>
       </c>
-      <c r="C21" s="128" t="inlineStr">
+      <c r="C21" s="133" t="inlineStr">
         <is>
           <t>수입신고 수리일자</t>
         </is>
@@ -14519,7 +14496,7 @@
           <t>2025-10-30</t>
         </is>
       </c>
-      <c r="D22" s="175" t="n">
+      <c r="D22" s="167" t="n">
         <v>1433</v>
       </c>
       <c r="E22" s="68" t="n">
@@ -14569,7 +14546,7 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="D23" s="175" t="n">
+      <c r="D23" s="167" t="n">
         <v>1465.2</v>
       </c>
       <c r="E23" s="68" t="n">
@@ -14938,22 +14915,22 @@
     <row r="46" ht="15.75" customHeight="1"/>
     <row r="47" ht="15.75" customHeight="1"/>
     <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="50" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="51" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="52" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="53" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="54" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="55" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="56" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="57" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="58" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="59" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="60" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="61" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="62" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="63" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="64" ht="15.75" customFormat="1" customHeight="1" s="130"/>
+    <row r="49" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="50" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="51" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="52" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="53" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="54" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="55" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="56" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="57" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="58" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="59" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="60" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="61" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="62" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="63" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="64" ht="15.75" customFormat="1" customHeight="1" s="135"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -14972,926 +14949,926 @@
     <row r="78" ht="15.75" customHeight="1"/>
     <row r="79" ht="15.75" customHeight="1"/>
     <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="82" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="83" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="84" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="85" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="86" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="87" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="88" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="89" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="90" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="91" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="92" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="93" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="94" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="95" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="96" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="97" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="98" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="99" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="100" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="101" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="102" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="103" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="104" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="105" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="106" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="107" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="108" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="109" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="110" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="111" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="112" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="113" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="114" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="115" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="116" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="117" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="118" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="119" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="120" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="121" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="122" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="123" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="124" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="125" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="126" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="127" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="128" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="129" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="130" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="131" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="132" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="133" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="134" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="135" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="136" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="137" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="138" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="139" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="140" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="141" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="142" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="143" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="144" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="145" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="146" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="147" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="148" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="149" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="150" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="151" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="152" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="153" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="154" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="155" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="156" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="157" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="158" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="159" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="160" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="161" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="162" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="163" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="164" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="165" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="166" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="167" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="168" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="169" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="170" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="171" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="172" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="173" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="174" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="175" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="176" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="177" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="178" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="179" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="180" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="181" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="182" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="183" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="184" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="185" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="186" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="187" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="188" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="189" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="190" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="191" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="192" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="193" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="194" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="195" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="196" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="197" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="198" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="199" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="200" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="201" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="202" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="203" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="204" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="205" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="206" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="207" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="208" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="209" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="210" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="211" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="212" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="213" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="214" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="215" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="216" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="217" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="218" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="219" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="220" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="221" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="222" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="223" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="224" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="225" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="226" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="227" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="228" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="229" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="230" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="231" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="232" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="233" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="234" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="235" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="236" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="237" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="238" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="239" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="240" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="241" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="242" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="243" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="244" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="245" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="246" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="247" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="248" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="249" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="250" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="251" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="252" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="253" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="254" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="255" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="256" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="257" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="258" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="259" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="260" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="261" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="262" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="263" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="264" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="265" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="266" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="267" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="268" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="269" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="270" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="271" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="272" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="273" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="274" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="275" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="276" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="277" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="278" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="279" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="280" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="281" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="282" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="283" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="284" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="285" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="286" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="287" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="288" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="289" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="290" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="291" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="292" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="293" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="294" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="295" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="296" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="297" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="298" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="299" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="300" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="301" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="302" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="303" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="304" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="305" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="306" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="307" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="308" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="309" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="310" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="311" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="312" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="313" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="314" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="315" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="316" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="317" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="318" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="319" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="320" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="321" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="322" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="323" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="324" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="325" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="326" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="327" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="328" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="329" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="330" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="331" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="332" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="333" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="334" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="335" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="336" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="337" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="338" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="339" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="340" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="341" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="342" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="343" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="344" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="345" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="346" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="347" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="348" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="349" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="350" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="351" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="352" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="353" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="354" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="355" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="356" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="357" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="358" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="359" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="360" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="361" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="362" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="363" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="364" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="365" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="366" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="367" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="368" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="369" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="370" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="371" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="372" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="373" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="374" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="375" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="376" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="377" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="378" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="379" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="380" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="381" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="382" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="383" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="384" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="385" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="386" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="387" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="388" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="389" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="390" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="391" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="392" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="393" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="394" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="395" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="396" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="397" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="398" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="399" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="400" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="401" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="402" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="403" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="404" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="405" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="406" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="407" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="408" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="409" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="410" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="411" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="412" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="413" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="414" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="415" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="416" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="417" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="418" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="419" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="420" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="421" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="422" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="423" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="424" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="425" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="426" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="427" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="428" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="429" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="430" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="431" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="432" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="433" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="434" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="435" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="436" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="437" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="438" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="439" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="440" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="441" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="442" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="443" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="444" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="445" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="446" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="447" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="448" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="449" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="450" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="451" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="452" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="453" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="454" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="455" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="456" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="457" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="458" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="459" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="460" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="461" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="462" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="463" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="464" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="465" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="466" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="467" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="468" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="469" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="470" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="471" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="472" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="473" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="474" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="475" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="476" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="477" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="478" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="479" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="480" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="481" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="482" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="483" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="484" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="485" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="486" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="487" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="488" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="489" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="490" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="491" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="492" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="493" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="494" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="495" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="496" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="497" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="498" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="499" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="500" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="501" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="502" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="503" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="504" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="505" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="506" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="507" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="508" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="509" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="510" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="511" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="512" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="513" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="514" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="515" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="516" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="517" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="518" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="519" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="520" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="521" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="522" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="523" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="524" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="525" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="526" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="527" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="528" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="529" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="530" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="531" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="532" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="533" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="534" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="535" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="536" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="537" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="538" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="539" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="540" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="541" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="542" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="543" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="544" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="545" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="546" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="547" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="548" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="549" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="550" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="551" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="552" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="553" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="554" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="555" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="556" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="557" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="558" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="559" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="560" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="561" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="562" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="563" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="564" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="565" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="566" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="567" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="568" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="569" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="570" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="571" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="572" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="573" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="574" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="575" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="576" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="577" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="578" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="579" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="580" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="581" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="582" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="583" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="584" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="585" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="586" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="587" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="588" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="589" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="590" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="591" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="592" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="593" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="594" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="595" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="596" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="597" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="598" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="599" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="600" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="601" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="602" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="603" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="604" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="605" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="606" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="607" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="608" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="609" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="610" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="611" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="612" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="613" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="614" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="615" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="616" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="617" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="618" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="619" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="620" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="621" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="622" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="623" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="624" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="625" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="626" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="627" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="628" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="629" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="630" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="631" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="632" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="633" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="634" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="635" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="636" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="637" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="638" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="639" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="640" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="641" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="642" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="643" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="644" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="645" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="646" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="647" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="648" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="649" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="650" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="651" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="652" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="653" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="654" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="655" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="656" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="657" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="658" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="659" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="660" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="661" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="662" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="663" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="664" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="665" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="666" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="667" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="668" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="669" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="670" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="671" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="672" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="673" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="674" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="675" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="676" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="677" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="678" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="679" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="680" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="681" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="682" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="683" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="684" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="685" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="686" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="687" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="688" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="689" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="690" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="691" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="692" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="693" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="694" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="695" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="696" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="697" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="698" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="699" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="700" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="701" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="702" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="703" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="704" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="705" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="706" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="707" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="708" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="709" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="710" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="711" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="712" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="713" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="714" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="715" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="716" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="717" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="718" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="719" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="720" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="721" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="722" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="723" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="724" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="725" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="726" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="727" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="728" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="729" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="730" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="731" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="732" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="733" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="734" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="735" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="736" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="737" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="738" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="739" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="740" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="741" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="742" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="743" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="744" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="745" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="746" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="747" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="748" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="749" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="750" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="751" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="752" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="753" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="754" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="755" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="756" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="757" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="758" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="759" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="760" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="761" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="762" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="763" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="764" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="765" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="766" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="767" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="768" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="769" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="770" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="771" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="772" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="773" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="774" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="775" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="776" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="777" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="778" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="779" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="780" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="781" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="782" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="783" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="784" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="785" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="786" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="787" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="788" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="789" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="790" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="791" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="792" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="793" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="794" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="795" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="796" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="797" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="798" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="799" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="800" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="801" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="802" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="803" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="804" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="805" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="806" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="807" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="808" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="809" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="810" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="811" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="812" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="813" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="814" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="815" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="816" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="817" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="818" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="819" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="820" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="821" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="822" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="823" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="824" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="825" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="826" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="827" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="828" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="829" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="830" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="831" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="832" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="833" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="834" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="835" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="836" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="837" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="838" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="839" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="840" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="841" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="842" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="843" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="844" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="845" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="846" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="847" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="848" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="849" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="850" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="851" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="852" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="853" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="854" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="855" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="856" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="857" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="858" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="859" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="860" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="861" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="862" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="863" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="864" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="865" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="866" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="867" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="868" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="869" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="870" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="871" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="872" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="873" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="874" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="875" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="876" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="877" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="878" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="879" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="880" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="881" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="882" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="883" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="884" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="885" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="886" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="887" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="888" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="889" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="890" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="891" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="892" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="893" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="894" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="895" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="896" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="897" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="898" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="899" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="900" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="901" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="902" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="903" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="904" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="905" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="906" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="907" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="908" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="909" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="910" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="911" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="912" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="913" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="914" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="915" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="916" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="917" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="918" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="919" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="920" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="921" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="922" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="923" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="924" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="925" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="926" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="927" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="928" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="929" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="930" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="931" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="932" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="933" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="934" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="935" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="936" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="937" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="938" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="939" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="940" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="941" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="942" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="943" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="944" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="945" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="946" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="947" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="948" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="949" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="950" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="951" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="952" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="953" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="954" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="955" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="956" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="957" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="958" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="959" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="960" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="961" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="962" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="963" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="964" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="965" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="966" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="967" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="968" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="969" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="970" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="971" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="972" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="973" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="974" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="975" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="976" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="977" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="978" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="979" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="980" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="981" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="982" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="983" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="984" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="985" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="986" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="987" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="988" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="989" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="990" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="991" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="992" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="993" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="994" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="995" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="996" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="997" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="998" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="999" ht="15.75" customFormat="1" customHeight="1" s="130"/>
-    <row r="1000" ht="15.75" customFormat="1" customHeight="1" s="130"/>
+    <row r="81" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="82" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="83" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="84" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="85" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="86" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="87" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="88" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="89" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="90" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="91" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="92" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="93" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="94" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="95" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="96" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="97" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="98" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="99" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="100" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="101" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="102" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="103" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="104" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="105" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="106" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="107" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="108" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="109" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="110" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="111" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="112" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="113" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="114" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="115" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="116" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="117" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="118" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="119" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="120" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="121" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="122" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="123" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="124" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="125" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="126" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="127" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="128" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="129" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="130" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="131" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="132" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="133" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="134" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="135" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="136" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="137" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="138" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="139" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="140" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="141" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="142" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="143" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="144" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="145" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="146" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="147" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="148" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="149" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="150" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="151" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="152" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="153" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="154" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="155" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="156" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="157" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="158" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="159" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="160" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="161" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="162" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="163" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="164" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="165" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="166" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="167" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="168" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="169" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="170" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="171" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="172" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="173" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="174" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="175" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="176" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="177" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="178" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="179" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="180" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="181" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="182" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="183" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="184" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="185" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="186" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="187" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="188" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="189" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="190" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="191" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="192" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="193" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="194" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="195" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="196" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="197" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="198" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="199" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="200" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="201" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="202" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="203" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="204" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="205" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="206" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="207" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="208" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="209" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="210" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="211" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="212" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="213" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="214" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="215" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="216" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="217" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="218" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="219" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="220" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="221" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="222" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="223" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="224" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="225" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="226" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="227" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="228" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="229" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="230" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="231" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="232" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="233" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="234" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="235" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="236" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="237" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="238" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="239" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="240" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="241" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="242" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="243" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="244" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="245" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="246" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="247" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="248" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="249" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="250" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="251" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="252" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="253" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="254" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="255" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="256" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="257" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="258" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="259" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="260" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="261" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="262" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="263" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="264" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="265" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="266" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="267" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="268" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="269" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="270" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="271" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="272" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="273" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="274" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="275" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="276" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="277" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="278" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="279" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="280" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="281" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="282" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="283" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="284" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="285" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="286" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="287" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="288" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="289" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="290" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="291" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="292" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="293" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="294" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="295" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="296" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="297" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="298" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="299" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="300" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="301" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="302" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="303" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="304" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="305" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="306" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="307" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="308" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="309" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="310" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="311" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="312" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="313" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="314" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="315" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="316" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="317" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="318" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="319" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="320" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="321" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="322" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="323" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="324" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="325" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="326" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="327" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="328" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="329" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="330" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="331" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="332" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="333" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="334" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="335" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="336" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="337" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="338" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="339" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="340" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="341" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="342" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="343" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="344" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="345" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="346" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="347" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="348" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="349" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="350" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="351" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="352" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="353" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="354" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="355" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="356" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="357" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="358" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="359" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="360" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="361" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="362" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="363" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="364" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="365" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="366" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="367" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="368" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="369" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="370" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="371" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="372" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="373" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="374" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="375" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="376" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="377" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="378" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="379" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="380" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="381" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="382" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="383" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="384" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="385" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="386" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="387" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="388" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="389" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="390" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="391" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="392" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="393" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="394" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="395" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="396" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="397" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="398" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="399" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="400" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="401" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="402" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="403" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="404" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="405" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="406" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="407" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="408" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="409" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="410" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="411" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="412" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="413" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="414" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="415" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="416" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="417" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="418" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="419" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="420" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="421" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="422" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="423" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="424" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="425" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="426" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="427" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="428" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="429" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="430" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="431" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="432" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="433" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="434" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="435" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="436" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="437" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="438" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="439" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="440" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="441" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="442" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="443" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="444" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="445" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="446" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="447" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="448" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="449" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="450" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="451" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="452" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="453" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="454" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="455" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="456" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="457" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="458" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="459" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="460" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="461" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="462" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="463" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="464" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="465" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="466" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="467" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="468" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="469" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="470" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="471" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="472" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="473" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="474" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="475" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="476" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="477" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="478" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="479" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="480" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="481" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="482" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="483" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="484" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="485" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="486" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="487" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="488" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="489" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="490" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="491" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="492" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="493" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="494" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="495" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="496" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="497" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="498" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="499" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="500" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="501" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="502" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="503" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="504" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="505" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="506" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="507" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="508" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="509" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="510" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="511" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="512" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="513" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="514" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="515" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="516" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="517" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="518" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="519" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="520" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="521" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="522" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="523" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="524" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="525" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="526" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="527" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="528" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="529" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="530" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="531" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="532" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="533" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="534" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="535" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="536" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="537" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="538" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="539" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="540" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="541" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="542" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="543" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="544" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="545" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="546" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="547" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="548" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="549" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="550" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="551" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="552" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="553" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="554" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="555" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="556" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="557" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="558" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="559" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="560" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="561" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="562" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="563" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="564" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="565" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="566" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="567" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="568" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="569" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="570" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="571" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="572" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="573" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="574" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="575" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="576" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="577" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="578" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="579" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="580" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="581" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="582" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="583" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="584" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="585" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="586" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="587" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="588" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="589" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="590" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="591" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="592" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="593" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="594" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="595" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="596" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="597" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="598" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="599" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="600" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="601" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="602" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="603" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="604" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="605" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="606" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="607" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="608" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="609" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="610" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="611" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="612" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="613" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="614" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="615" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="616" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="617" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="618" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="619" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="620" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="621" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="622" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="623" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="624" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="625" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="626" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="627" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="628" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="629" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="630" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="631" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="632" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="633" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="634" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="635" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="636" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="637" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="638" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="639" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="640" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="641" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="642" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="643" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="644" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="645" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="646" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="647" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="648" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="649" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="650" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="651" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="652" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="653" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="654" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="655" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="656" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="657" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="658" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="659" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="660" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="661" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="662" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="663" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="664" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="665" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="666" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="667" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="668" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="669" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="670" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="671" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="672" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="673" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="674" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="675" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="676" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="677" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="678" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="679" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="680" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="681" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="682" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="683" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="684" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="685" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="686" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="687" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="688" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="689" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="690" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="691" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="692" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="693" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="694" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="695" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="696" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="697" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="698" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="699" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="700" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="701" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="702" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="703" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="704" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="705" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="706" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="707" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="708" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="709" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="710" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="711" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="712" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="713" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="714" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="715" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="716" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="717" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="718" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="719" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="720" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="721" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="722" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="723" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="724" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="725" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="726" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="727" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="728" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="729" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="730" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="731" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="732" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="733" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="734" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="735" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="736" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="737" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="738" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="739" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="740" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="741" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="742" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="743" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="744" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="745" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="746" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="747" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="748" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="749" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="750" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="751" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="752" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="753" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="754" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="755" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="756" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="757" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="758" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="759" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="760" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="761" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="762" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="763" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="764" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="765" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="766" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="767" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="768" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="769" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="770" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="771" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="772" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="773" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="774" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="775" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="776" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="777" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="778" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="779" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="780" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="781" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="782" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="783" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="784" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="785" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="786" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="787" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="788" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="789" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="790" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="791" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="792" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="793" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="794" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="795" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="796" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="797" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="798" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="799" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="800" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="801" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="802" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="803" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="804" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="805" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="806" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="807" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="808" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="809" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="810" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="811" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="812" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="813" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="814" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="815" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="816" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="817" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="818" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="819" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="820" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="821" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="822" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="823" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="824" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="825" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="826" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="827" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="828" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="829" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="830" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="831" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="832" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="833" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="834" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="835" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="836" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="837" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="838" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="839" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="840" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="841" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="842" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="843" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="844" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="845" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="846" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="847" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="848" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="849" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="850" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="851" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="852" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="853" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="854" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="855" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="856" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="857" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="858" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="859" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="860" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="861" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="862" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="863" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="864" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="865" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="866" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="867" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="868" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="869" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="870" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="871" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="872" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="873" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="874" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="875" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="876" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="877" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="878" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="879" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="880" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="881" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="882" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="883" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="884" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="885" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="886" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="887" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="888" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="889" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="890" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="891" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="892" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="893" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="894" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="895" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="896" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="897" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="898" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="899" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="900" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="901" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="902" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="903" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="904" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="905" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="906" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="907" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="908" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="909" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="910" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="911" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="912" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="913" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="914" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="915" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="916" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="917" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="918" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="919" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="920" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="921" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="922" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="923" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="924" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="925" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="926" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="927" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="928" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="929" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="930" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="931" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="932" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="933" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="934" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="935" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="936" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="937" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="938" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="939" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="940" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="941" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="942" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="943" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="944" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="945" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="946" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="947" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="948" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="949" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="950" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="951" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="952" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="953" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="954" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="955" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="956" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="957" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="958" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="959" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="960" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="961" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="962" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="963" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="964" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="965" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="966" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="967" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="968" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="969" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="970" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="971" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="972" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="973" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="974" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="975" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="976" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="977" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="978" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="979" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="980" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="981" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="982" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="983" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="984" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="985" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="986" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="987" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="988" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="989" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="990" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="991" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="992" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="993" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="994" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="995" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="996" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="997" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="998" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="999" ht="15.75" customFormat="1" customHeight="1" s="135"/>
+    <row r="1000" ht="15.75" customFormat="1" customHeight="1" s="135"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A20:L20"/>
@@ -15919,49 +15896,49 @@
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
     <col width="9.5" customWidth="1" style="40" min="3" max="3"/>
     <col width="18" customWidth="1" style="40" min="4" max="4"/>
-    <col width="8.83203125" customWidth="1" style="40" min="5" max="7"/>
-    <col width="8.83203125" customWidth="1" style="40" min="8" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="40" min="5" max="8"/>
+    <col width="8.83203125" customWidth="1" style="40" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="134" t="inlineStr">
+      <c r="A1" s="139" t="inlineStr">
         <is>
           <t>관세청 주간 고시환율 (USD/KRW 수입환율)</t>
         </is>
       </c>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="119" t="n"/>
+      <c r="B1" s="123" t="n"/>
+      <c r="C1" s="123" t="n"/>
+      <c r="D1" s="124" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="136" t="inlineStr">
+      <c r="A2" s="141" t="inlineStr">
         <is>
           <t>출처: 관세청 관세법령정보포털 (CLIP) - 주간환율조회</t>
         </is>
       </c>
-      <c r="B2" s="118" t="n"/>
-      <c r="C2" s="118" t="n"/>
-      <c r="D2" s="119" t="n"/>
+      <c r="B2" s="123" t="n"/>
+      <c r="C2" s="123" t="n"/>
+      <c r="D2" s="124" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="136" t="inlineStr">
+      <c r="A3" s="141" t="inlineStr">
         <is>
           <t>관세법 제18조 기준: 수입신고일이 속하는 주의 전주 기준환율 평균 (매주 금요일 고시, 일~토 적용)</t>
         </is>
       </c>
-      <c r="B3" s="118" t="n"/>
-      <c r="C3" s="118" t="n"/>
-      <c r="D3" s="119" t="n"/>
+      <c r="B3" s="123" t="n"/>
+      <c r="C3" s="123" t="n"/>
+      <c r="D3" s="124" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="135" t="inlineStr">
+      <c r="A4" s="140" t="inlineStr">
         <is>
           <t>업데이트: 2026-04-20 (관세청 고시환율)</t>
         </is>
       </c>
-      <c r="B4" s="118" t="n"/>
-      <c r="C4" s="118" t="n"/>
-      <c r="D4" s="119" t="n"/>
+      <c r="B4" s="123" t="n"/>
+      <c r="C4" s="123" t="n"/>
+      <c r="D4" s="124" t="n"/>
     </row>
     <row r="5" ht="7.5" customHeight="1"/>
     <row r="6" ht="27.75" customHeight="1">
@@ -15987,10 +15964,10 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="145" t="n">
+      <c r="A7" s="144" t="n">
         <v>45935</v>
       </c>
-      <c r="B7" s="145" t="n">
+      <c r="B7" s="144" t="n">
         <v>45941</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -16003,10 +15980,10 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="145" t="n">
+      <c r="A8" s="144" t="n">
         <v>45942</v>
       </c>
-      <c r="B8" s="145" t="n">
+      <c r="B8" s="144" t="n">
         <v>45948</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -16019,10 +15996,10 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="145" t="n">
+      <c r="A9" s="144" t="n">
         <v>45949</v>
       </c>
-      <c r="B9" s="145" t="n">
+      <c r="B9" s="144" t="n">
         <v>45955</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -16035,10 +16012,10 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="145" t="n">
+      <c r="A10" s="144" t="n">
         <v>45956</v>
       </c>
-      <c r="B10" s="145" t="n">
+      <c r="B10" s="144" t="n">
         <v>45962</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -16051,10 +16028,10 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="145" t="n">
+      <c r="A11" s="144" t="n">
         <v>45963</v>
       </c>
-      <c r="B11" s="145" t="n">
+      <c r="B11" s="144" t="n">
         <v>45969</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -16067,10 +16044,10 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="145" t="n">
+      <c r="A12" s="144" t="n">
         <v>45970</v>
       </c>
-      <c r="B12" s="145" t="n">
+      <c r="B12" s="144" t="n">
         <v>45976</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -16083,10 +16060,10 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="145" t="n">
+      <c r="A13" s="144" t="n">
         <v>45977</v>
       </c>
-      <c r="B13" s="145" t="n">
+      <c r="B13" s="144" t="n">
         <v>45983</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -16099,10 +16076,10 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="145" t="n">
+      <c r="A14" s="144" t="n">
         <v>45984</v>
       </c>
-      <c r="B14" s="145" t="n">
+      <c r="B14" s="144" t="n">
         <v>45990</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -16115,10 +16092,10 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="145" t="n">
+      <c r="A15" s="144" t="n">
         <v>45991</v>
       </c>
-      <c r="B15" s="145" t="n">
+      <c r="B15" s="144" t="n">
         <v>45997</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -16131,10 +16108,10 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="145" t="n">
+      <c r="A16" s="144" t="n">
         <v>45998</v>
       </c>
-      <c r="B16" s="145" t="n">
+      <c r="B16" s="144" t="n">
         <v>46004</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -16147,10 +16124,10 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="145" t="n">
+      <c r="A17" s="144" t="n">
         <v>46005</v>
       </c>
-      <c r="B17" s="145" t="n">
+      <c r="B17" s="144" t="n">
         <v>46011</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -16163,10 +16140,10 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="145" t="n">
+      <c r="A18" s="144" t="n">
         <v>46012</v>
       </c>
-      <c r="B18" s="145" t="n">
+      <c r="B18" s="144" t="n">
         <v>46018</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -16179,10 +16156,10 @@
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="145" t="n">
+      <c r="A19" s="144" t="n">
         <v>46019</v>
       </c>
-      <c r="B19" s="145" t="n">
+      <c r="B19" s="144" t="n">
         <v>46025</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -16195,10 +16172,10 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="145" t="n">
+      <c r="A20" s="144" t="n">
         <v>46026</v>
       </c>
-      <c r="B20" s="145" t="n">
+      <c r="B20" s="144" t="n">
         <v>46032</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -16211,10 +16188,10 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="145" t="n">
+      <c r="A21" s="144" t="n">
         <v>46033</v>
       </c>
-      <c r="B21" s="145" t="n">
+      <c r="B21" s="144" t="n">
         <v>46039</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -16227,10 +16204,10 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="145" t="n">
+      <c r="A22" s="144" t="n">
         <v>46040</v>
       </c>
-      <c r="B22" s="145" t="n">
+      <c r="B22" s="144" t="n">
         <v>46046</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -16243,10 +16220,10 @@
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="145" t="n">
+      <c r="A23" s="144" t="n">
         <v>46047</v>
       </c>
-      <c r="B23" s="145" t="n">
+      <c r="B23" s="144" t="n">
         <v>46053</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -16259,10 +16236,10 @@
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="145" t="n">
+      <c r="A24" s="144" t="n">
         <v>46054</v>
       </c>
-      <c r="B24" s="145" t="n">
+      <c r="B24" s="144" t="n">
         <v>46060</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -16275,10 +16252,10 @@
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="145" t="n">
+      <c r="A25" s="144" t="n">
         <v>46061</v>
       </c>
-      <c r="B25" s="145" t="n">
+      <c r="B25" s="144" t="n">
         <v>46067</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -16291,10 +16268,10 @@
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="145" t="n">
+      <c r="A26" s="144" t="n">
         <v>46068</v>
       </c>
-      <c r="B26" s="145" t="n">
+      <c r="B26" s="144" t="n">
         <v>46074</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -16307,10 +16284,10 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="145" t="n">
+      <c r="A27" s="144" t="n">
         <v>46075</v>
       </c>
-      <c r="B27" s="145" t="n">
+      <c r="B27" s="144" t="n">
         <v>46081</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -16323,10 +16300,10 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="145" t="n">
+      <c r="A28" s="144" t="n">
         <v>46082</v>
       </c>
-      <c r="B28" s="145" t="n">
+      <c r="B28" s="144" t="n">
         <v>46088</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -16339,10 +16316,10 @@
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="145" t="n">
+      <c r="A29" s="144" t="n">
         <v>46089</v>
       </c>
-      <c r="B29" s="145" t="n">
+      <c r="B29" s="144" t="n">
         <v>46095</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -16355,10 +16332,10 @@
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="145" t="n">
+      <c r="A30" s="144" t="n">
         <v>46096</v>
       </c>
-      <c r="B30" s="145" t="n">
+      <c r="B30" s="144" t="n">
         <v>46102</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -16371,10 +16348,10 @@
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="145" t="n">
+      <c r="A31" s="144" t="n">
         <v>46103</v>
       </c>
-      <c r="B31" s="145" t="n">
+      <c r="B31" s="144" t="n">
         <v>46109</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -16387,10 +16364,10 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="145" t="n">
+      <c r="A32" s="144" t="n">
         <v>46110</v>
       </c>
-      <c r="B32" s="145" t="n">
+      <c r="B32" s="144" t="n">
         <v>46116</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -16403,10 +16380,10 @@
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="145" t="n">
+      <c r="A33" s="144" t="n">
         <v>46117</v>
       </c>
-      <c r="B33" s="145" t="n">
+      <c r="B33" s="144" t="n">
         <v>46123</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -16419,10 +16396,10 @@
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="145" t="n">
+      <c r="A34" s="144" t="n">
         <v>46124</v>
       </c>
-      <c r="B34" s="145" t="n">
+      <c r="B34" s="144" t="n">
         <v>46130</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -16435,10 +16412,10 @@
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="145" t="n">
+      <c r="A35" s="144" t="n">
         <v>46131</v>
       </c>
-      <c r="B35" s="145" t="n">
+      <c r="B35" s="144" t="n">
         <v>46137</v>
       </c>
       <c r="C35" s="3" t="inlineStr">

--- a/RNR_수입원가_2026_20260424.xlsx
+++ b/RNR_수입원가_2026_20260424.xlsx
@@ -979,10 +979,11 @@
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S14" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
-HS 8518/8543 디지털시네마장비</t>
+HS 8414.59 — Projector cooling fan
+(WTO 협정세율 0%)</t>
       </text>
     </comment>
     <comment ref="S15" authorId="0" shapeId="0">
